--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -4,13 +4,14 @@
   <sheets>
     <sheet name="Сравнение 7 Дней (4★ vs 5★)" sheetId="1" r:id="rId1"/>
     <sheet name="Смета 5 Дней (4★ Бутик)" sheetId="2" r:id="rId2"/>
-    <sheet name="Официальные ссылки и тарифы" sheetId="3" r:id="rId3"/>
+    <sheet name="Онлайн-сервисы для Валерия" sheetId="3" r:id="rId3"/>
+    <sheet name="Официальные ссылки и тарифы" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
@@ -528,6 +529,282 @@
     <t>8 500 € за тур на двоих</t>
   </si>
   <si>
+    <t>ОНЛАЙН-СЕРВИСЫ И ГОСПОШЛИНЫ «ПОД КЛЮЧ»: ПРОТОКОЛ ОРГАНИЗАТОРА (ВАЛЕРИЙ)</t>
+  </si>
+  <si>
+    <t>Пошаговый регламент оформления виз, сборов, деклараций и VIP-служб с прямыми ссылками</t>
+  </si>
+  <si>
+    <t>Сервис / Документ</t>
+  </si>
+  <si>
+    <t>Официальная ссылка</t>
+  </si>
+  <si>
+    <t>Когда оформлять (Тайминг)</t>
+  </si>
+  <si>
+    <t>Что нужно от гостий</t>
+  </si>
+  <si>
+    <t>Официальный тариф</t>
+  </si>
+  <si>
+    <t>Как оплатить онлайн</t>
+  </si>
+  <si>
+    <t>Что получается на выходе</t>
+  </si>
+  <si>
+    <t>Инструкция для Валерия</t>
+  </si>
+  <si>
+    <t>1. Электронная виза e-VOA (B1 Tourism)</t>
+  </si>
+  <si>
+    <t>https://evisa.imigrasi.go.id</t>
+  </si>
+  <si>
+    <t>За 5–14 дней до прилета</t>
+  </si>
+  <si>
+    <t>1) Четкое фото разворота паспорта (срок &gt; 6 мес)
+2) Фото на белом фоне (селфи)
+3) Номера рейсов</t>
+  </si>
+  <si>
+    <t>500 000 IDR (~32 €) + 3% шлюз</t>
+  </si>
+  <si>
+    <t>Зарубежной картой Visa/Mastercard</t>
+  </si>
+  <si>
+    <t>PDF-файл e-VOA на каждого гостя</t>
+  </si>
+  <si>
+    <t>Создать аккаунт на evisa.imigrasi.go.id, выбрать 'Tourism 30 Days B1', загрузить паспорта и фото, оплатить. Скачать готовые PDF-файлы виз.</t>
+  </si>
+  <si>
+    <t>2. Туристический налог Love Bali</t>
+  </si>
+  <si>
+    <t>https://lovebali.baliprov.go.id</t>
+  </si>
+  <si>
+    <t>За 3–7 дней до прилета</t>
+  </si>
+  <si>
+    <t>1) Номер паспорта
+2) Имя и фамилия
+3) Email
+4) Дата прилета</t>
+  </si>
+  <si>
+    <t>150 000 IDR (~9 € / ~10 CHF)</t>
+  </si>
+  <si>
+    <t>Картой Visa/Mastercard на портале</t>
+  </si>
+  <si>
+    <t>QR-код туристического ваучера (PDF)</t>
+  </si>
+  <si>
+    <t>Зайти на lovebali.baliprov.go.id, ввести данные 2 гостей, оплатить сбор 2 x 150 000 IDR. Сохранить полученные QR-коды.</t>
+  </si>
+  <si>
+    <t>3. Таможенная декларация e-CD</t>
+  </si>
+  <si>
+    <t>https://ecd.beacukai.go.id</t>
+  </si>
+  <si>
+    <t>Строго за 1–3 дня (открывается за 72ч)</t>
+  </si>
+  <si>
+    <t>1) Номер рейса прибытия в DPS
+2) Количество мест багажа
+3) Данные одного главного пассажира</t>
+  </si>
+  <si>
+    <t>Бесплатно (0 IDR)</t>
+  </si>
+  <si>
+    <t>Не требуется (государственная служба)</t>
+  </si>
+  <si>
+    <t>1 единый QR-код на группу (семью)</t>
+  </si>
+  <si>
+    <t>Заполняется онлайн за 3 дня до рейса на ecd.beacukai.go.id. Выбирается 1 заявитель + 1 спутник. На выходе генерируется QR-код для сканера таможни.</t>
+  </si>
+  <si>
+    <t>4. VIP Fast-Track прилет (JOUMPA Garuda)</t>
+  </si>
+  <si>
+    <t>https://www.joumpa.com</t>
+  </si>
+  <si>
+    <t>За 5–7 дней до прилета</t>
+  </si>
+  <si>
+    <t>1) Номера и время рейсов
+2) Имена для таблички встречи
+3) Копии паспортов</t>
+  </si>
+  <si>
+    <t>1 350 000 IDR/чел (~80 €)</t>
+  </si>
+  <si>
+    <t>Картой на joumpa.com или WhatsApp Gapura</t>
+  </si>
+  <si>
+    <t>Ваучер бронирования с контактом супервайзера</t>
+  </si>
+  <si>
+    <t>Выбрать услугу 'VIP Arrival Service (Meet &amp; Greet + Fast Track + Porter + Concordia Lounge)'. Указать табличку 'SWISS VIP GUESTS' или персональные имена.</t>
+  </si>
+  <si>
+    <t>5. Координация Путу (Toyota Innova Zenix)</t>
+  </si>
+  <si>
+    <t>WhatsApp Путу (прямой чат)</t>
+  </si>
+  <si>
+    <t>За 3 дня (финал) + в день прилета</t>
+  </si>
+  <si>
+    <t>Данные рейса для отслеживания на Flightradar24</t>
+  </si>
+  <si>
+    <t>1 100 000 IDR/день (с бензином)</t>
+  </si>
+  <si>
+    <t>Наличными рупиями Путу на месте</t>
+  </si>
+  <si>
+    <t>Подача чистого кондиционированного авто к выходу VIP</t>
+  </si>
+  <si>
+    <t>Отправить Путу точный рейс, скриншот брони JOUMPA и время посадки. Путу паркуется в VIP-зоне терминала за 30 мин до прилета.</t>
+  </si>
+  <si>
+    <t>6. Отель Plataran Ubud Hotel &amp; Spa 4★+</t>
+  </si>
+  <si>
+    <t>https://www.plataran.com/plataran-ubud/</t>
+  </si>
+  <si>
+    <t>За 14–30 дней до тура</t>
+  </si>
+  <si>
+    <t>Имена гостей, даты проживания (3 ночи)</t>
+  </si>
+  <si>
+    <t>5 500 000 IDR/ночь (~320 €/н)</t>
+  </si>
+  <si>
+    <t>Предоплата картой на сайте Plataran</t>
+  </si>
+  <si>
+    <t>Подтверждение брони Deluxe Suite</t>
+  </si>
+  <si>
+    <t>Забронировать номер категории Deluxe Suite с видом на террасы. Заказать заранее комплиментарную корзину фруктов и приветственный чай.</t>
+  </si>
+  <si>
+    <t>7. Глэмпинг Toteme Kintamani 4★+</t>
+  </si>
+  <si>
+    <t>https://totemeglamping.com</t>
+  </si>
+  <si>
+    <t>За 14–20 дней до тура</t>
+  </si>
+  <si>
+    <t>Даты проживания (1 ночь)</t>
+  </si>
+  <si>
+    <t>3 800 000 IDR/ночь (~220 €/н)</t>
+  </si>
+  <si>
+    <t>Картой на сайте или WhatsApp отеля</t>
+  </si>
+  <si>
+    <t>Подтверждение шатра с приватной купелью</t>
+  </si>
+  <si>
+    <t>Выбрать премиум-шатер с индивидуальной геотермальной минеральной ванной на террасе. Заказать растопку купели к моменту заезда (17:00).</t>
+  </si>
+  <si>
+    <t>8. Отель Renaissance Uluwatu 4★+</t>
+  </si>
+  <si>
+    <t>https://www.marriott.com</t>
+  </si>
+  <si>
+    <t>Имена гостей, даты проживания (2 ночи)</t>
+  </si>
+  <si>
+    <t>5 800 000 IDR/ночь (~340 €/н)</t>
+  </si>
+  <si>
+    <t>Картой на официальном сайте Marriott</t>
+  </si>
+  <si>
+    <t>Подтверждение Ocean View Suite</t>
+  </si>
+  <si>
+    <t>Забронировать люкс с панорамным видом на Индийский океан. Запросить высокий этаж и поздний выезд (Late Check-out) при необходимости.</t>
+  </si>
+  <si>
+    <t>9. Ресторан Mozaic Gastronomic (Убуд)</t>
+  </si>
+  <si>
+    <t>https://mozaic-bali.com</t>
+  </si>
+  <si>
+    <t>За 7–14 дней до тура</t>
+  </si>
+  <si>
+    <t>Количество гостей (2 чел), диетические ограничения</t>
+  </si>
+  <si>
+    <t>Дегустационный сет (~150 €/чел)</t>
+  </si>
+  <si>
+    <t>Депозит картой на сайте Chope/Mozaic</t>
+  </si>
+  <si>
+    <t>Бронь столика в саду шефа</t>
+  </si>
+  <si>
+    <t>Забронировать дегустационное меню Tasting Menu от шеф-повара Блейка Торнли. Указать вегетарианские/аллергические предпочтения гостий заранее.</t>
+  </si>
+  <si>
+    <t>10. Священник Манку (Мелукат и Агнихотра)</t>
+  </si>
+  <si>
+    <t>Прямой контакт Валерия</t>
+  </si>
+  <si>
+    <t>За 7 дней до тура</t>
+  </si>
+  <si>
+    <t>Дата проведения церемонии в Себату</t>
+  </si>
+  <si>
+    <t>3 400 000 IDR (~200 € за комплекс)</t>
+  </si>
+  <si>
+    <t>Наличными после завершения ритуала</t>
+  </si>
+  <si>
+    <t>Подготовленные подношения Чананг Сари и Агни-хотра</t>
+  </si>
+  <si>
+    <t>Согласовать с Манку утреннее приватное время (08:30) у источников водопада Genah Melukat до появления других людей.</t>
+  </si>
+  <si>
     <t>СПРАВОЧНИК ОФИЦИАЛЬНЫХ ТАРИФОВ И ПРЯМЫХ ССЫЛОК (БАЛИ 2026)</t>
   </si>
   <si>
@@ -570,9 +847,6 @@
     <t>80 €/чел</t>
   </si>
   <si>
-    <t>https://www.joumpa.com</t>
-  </si>
-  <si>
     <t>Meet &amp; Greet у рукава + дип-коридор + портье багажа + Concordia VIP Lounge</t>
   </si>
   <si>
@@ -594,9 +868,6 @@
     <t>32 €/чел</t>
   </si>
   <si>
-    <t>https://evisa.imigrasi.go.id</t>
-  </si>
-  <si>
     <t>Въездная туристическая виза на 30 дней</t>
   </si>
   <si>
@@ -618,9 +889,6 @@
     <t>9 €/чел</t>
   </si>
   <si>
-    <t>https://lovebali.baliprov.go.id</t>
-  </si>
-  <si>
     <t>Официальный туристический сбор</t>
   </si>
   <si>
@@ -636,12 +904,6 @@
     <t>Таможенная служба Индонезии (Beacukai)</t>
   </si>
   <si>
-    <t>Бесплатно (0 IDR)</t>
-  </si>
-  <si>
-    <t>https://ecd.beacukai.go.id</t>
-  </si>
-  <si>
     <t>Электронная декларация на багаж</t>
   </si>
   <si>
@@ -687,9 +949,6 @@
     <t>320 €/ночь</t>
   </si>
   <si>
-    <t>https://www.plataran.com/plataran-ubud/</t>
-  </si>
-  <si>
     <t>Deluxe Suite с видом на террасы + завтрак</t>
   </si>
   <si>
@@ -711,9 +970,6 @@
     <t>220 €/ночь</t>
   </si>
   <si>
-    <t>https://totemeglamping.com</t>
-  </si>
-  <si>
     <t>Шатер с термальной минеральной ванной на террасе</t>
   </si>
   <si>
@@ -735,9 +991,6 @@
     <t>340 €/ночь</t>
   </si>
   <si>
-    <t>https://www.marriott.com</t>
-  </si>
-  <si>
     <t>Ocean View Suite на утесе + завтраки</t>
   </si>
   <si>
@@ -817,9 +1070,6 @@
   </si>
   <si>
     <t>200 €</t>
-  </si>
-  <si>
-    <t>Прямой контакт Валерия</t>
   </si>
   <si>
     <t>Огненная ведическая пуджа и благословение</t>
@@ -883,7 +1133,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
@@ -918,8 +1168,14 @@
       <name val="Arial"/>
       <color rgb="FF008000"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <color rgb="FF1F497D"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -951,6 +1207,11 @@
         <fgColor rgb="FFEBF5EB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -977,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0"/>
@@ -986,6 +1247,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -2564,16 +2826,16 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="4">
+      <c r="A2" t="s" s="8">
         <v>173</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3">
       <c r="A3" s="0"/>
@@ -2700,108 +2962,108 @@
         <v>208</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>240</v>
@@ -2827,152 +3089,479 @@
         <v>246</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="4">
+        <v>262</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>263</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="D4" t="s" s="1">
+        <v>266</v>
+      </c>
+      <c r="E4" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="F4" t="s" s="1">
+        <v>268</v>
+      </c>
+      <c r="G4" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="H4" t="s" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>273</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>286</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>293</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>295</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>338</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>260</v>
+        <v>341</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>263</v>
+        <v>344</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>264</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>265</v>
+        <v>346</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>267</v>
+        <v>348</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>268</v>
+        <v>349</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>272</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>273</v>
+        <v>353</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>274</v>
+        <v>354</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>277</v>
+        <v>357</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>280</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>282</v>
+        <v>362</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>284</v>
+        <v>364</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>288</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -6,12 +6,14 @@
     <sheet name="Смета 5 Дней (4★ Бутик)" sheetId="2" r:id="rId2"/>
     <sheet name="Онлайн-сервисы для Валерия" sheetId="3" r:id="rId3"/>
     <sheet name="Официальные ссылки и тарифы" sheetId="4" r:id="rId4"/>
+    <sheet name="Бюджет Валерия (2 месяца)" sheetId="5" r:id="rId5"/>
+    <sheet name="Экспедиция на Яву (Прамбанан)" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
@@ -568,8 +570,8 @@
     <t>За 5–14 дней до прилета</t>
   </si>
   <si>
-    <t>1) Четкое фото разворота паспорта (срок &gt; 6 мес)
-2) Фото на белом фоне (селфи)
+    <t>1) Четкое фото паспорта (&gt;6 мес)
+2) Селфи на светлом фоне
 3) Номера рейсов</t>
   </si>
   <si>
@@ -623,7 +625,7 @@
   <si>
     <t>1) Номер рейса прибытия в DPS
 2) Количество мест багажа
-3) Данные одного главного пассажира</t>
+3) Данные одного пассажира</t>
   </si>
   <si>
     <t>Бесплатно (0 IDR)</t>
@@ -682,7 +684,7 @@
     <t>Наличными рупиями Путу на месте</t>
   </si>
   <si>
-    <t>Подача чистого кондиционированного авто к выходу VIP</t>
+    <t>Подача чистого авто к выходу VIP</t>
   </si>
   <si>
     <t>Отправить Путу точный рейс, скриншот брони JOUMPA и время посадки. Путу паркуется в VIP-зоне терминала за 30 мин до прилета.</t>
@@ -1127,13 +1129,411 @@
   </si>
   <si>
     <t>Королевский балийский уход</t>
+  </si>
+  <si>
+    <t>ЛИЧНЫЙ БЮДЖЕТ ПРЕБЫВАНИЯ ВАЛЕРИЯ НА БАЛИ: 2 МЕСЯЦА (60 ДНЕЙ)</t>
+  </si>
+  <si>
+    <t>Перелет (Qatar / Emirates) • Жилье в Убуде (8 млн IDR/мес) • Байк • Виза 60 дней • Быт</t>
+  </si>
+  <si>
+    <t>Срок / Объем</t>
+  </si>
+  <si>
+    <t>Эконом / Оптимум (€)</t>
+  </si>
+  <si>
+    <t>Бизнес / Премиум (€)</t>
+  </si>
+  <si>
+    <t>Авиакомпания / Контрагент</t>
+  </si>
+  <si>
+    <t>Оценка и рекомендации</t>
+  </si>
+  <si>
+    <t>1. Международный перелет</t>
+  </si>
+  <si>
+    <t>Qatar Airways (Москва SVO - Доха DOH - Бали DPS туда и обратно)</t>
+  </si>
+  <si>
+    <t>RT билет</t>
+  </si>
+  <si>
+    <t>Qatar Airways (qatarairways.com)</t>
+  </si>
+  <si>
+    <t>РЕКОМЕНДУЕТСЯ. Лучший сервис Skytrax #1, стыковка 2.5ч в Хамаде</t>
+  </si>
+  <si>
+    <t>Emirates (Москва DME - Дубай DXB - Бали DPS туда и обратно)</t>
+  </si>
+  <si>
+    <t>Emirates (emirates.com)</t>
+  </si>
+  <si>
+    <t>ОТЛИЧНЫЙ ВАРИАНТ. Просторный A380/B777, багаж 30 кг, сервис топ</t>
+  </si>
+  <si>
+    <t>Аэрофлот прямой рейс (Москва SVO - Бали DPS туда и обратно)</t>
+  </si>
+  <si>
+    <t>Аэрофлот (aeroflot.ru)</t>
+  </si>
+  <si>
+    <t>НЕ РЕКОМЕНДУЕТСЯ. 12.5 ч без посадки, тяжелый перелет, уставший салон</t>
+  </si>
+  <si>
+    <t>ИТОГО ПЕРЕЛЕТ (ВЫБОР: QATAR AIRWAYS)</t>
+  </si>
+  <si>
+    <t>Qatar Airways</t>
+  </si>
+  <si>
+    <t>Оптимальный баланс цены, комфорта и легкости стыковки</t>
+  </si>
+  <si>
+    <t>2. Виза в Индонезию</t>
+  </si>
+  <si>
+    <t>Виза 211A Tourism Single Entry (60 дней сразу при въезде)</t>
+  </si>
+  <si>
+    <t>60 дней</t>
+  </si>
+  <si>
+    <t>evisa.imigrasi.go.id</t>
+  </si>
+  <si>
+    <t>РЕКОМЕНДУЕТСЯ. Официальный госпортал, 60 дней без забот о продлении</t>
+  </si>
+  <si>
+    <t>Альтернатива: e-VOA B1 (30 дней) + онлайн продление на 30 дней</t>
+  </si>
+  <si>
+    <t>30 + 30 дней</t>
+  </si>
+  <si>
+    <t>Два платежа по 500 000 IDR онлайн, но нужно не забыть продлить</t>
+  </si>
+  <si>
+    <t>Официальный сбор провинции Love Bali Levy</t>
+  </si>
+  <si>
+    <t>Разово</t>
+  </si>
+  <si>
+    <t>lovebali.baliprov.go.id</t>
+  </si>
+  <si>
+    <t>Обязательный сбор провинции Бали</t>
+  </si>
+  <si>
+    <t>ИТОГО ВИЗА И СБОР НА 60 ДНЕЙ</t>
+  </si>
+  <si>
+    <t>Госпортал Индонезии</t>
+  </si>
+  <si>
+    <t>Полностью легально и онлайн</t>
+  </si>
+  <si>
+    <t>3. Проживание (Убуд)</t>
+  </si>
+  <si>
+    <t>Привычное жилье Валерия в Убуде (дом / апартаменты)</t>
+  </si>
+  <si>
+    <t>1-й месяц</t>
+  </si>
+  <si>
+    <t>Прямой контакт хозяина</t>
+  </si>
+  <si>
+    <t>8 000 000 IDR в месяц (проверенная локация)</t>
+  </si>
+  <si>
+    <t>2-й месяц</t>
+  </si>
+  <si>
+    <t>8 000 000 IDR в месяц</t>
+  </si>
+  <si>
+    <t>ИТОГО ЖИЛЬЕ В УБУДЕ НА 2 МЕСЯЦА</t>
+  </si>
+  <si>
+    <t>2 месяца</t>
+  </si>
+  <si>
+    <t>Аренда напрямую</t>
+  </si>
+  <si>
+    <t>Идеальная тихая база для творчества и работы</t>
+  </si>
+  <si>
+    <t>4. Транспорт (Скутер)</t>
+  </si>
+  <si>
+    <t>Аренда скутера Yamaha NMax 155cc / Honda PCX 160cc</t>
+  </si>
+  <si>
+    <t>Проверенный прокат Убуд</t>
+  </si>
+  <si>
+    <t>1 600 000 IDR/месяц, шлем, надежные тормоза</t>
+  </si>
+  <si>
+    <t>Бензин Pertamax (заправки Pertamina)</t>
+  </si>
+  <si>
+    <t>Pertamina SPBU</t>
+  </si>
+  <si>
+    <t>Около 75 000 IDR в неделю</t>
+  </si>
+  <si>
+    <t>ИТОГО ТРАНСПОРТ НА 2 МЕСЯЦА</t>
+  </si>
+  <si>
+    <t>Скутер NMax</t>
+  </si>
+  <si>
+    <t>Полная свобода перемещения по острову</t>
+  </si>
+  <si>
+    <t>5. Питание и быт</t>
+  </si>
+  <si>
+    <t>Ежедневное питание: любимые кафе Убуда, варунги, тропические фрукты, кокосы</t>
+  </si>
+  <si>
+    <t>Кафе Убуда и рынки</t>
+  </si>
+  <si>
+    <t>300 000 IDR/день (комфортное качественное питание)</t>
+  </si>
+  <si>
+    <t>Прачечная (Laundry), питьевая вода (Galon Aqua), хоз. расходы</t>
+  </si>
+  <si>
+    <t>Местные сервисы</t>
+  </si>
+  <si>
+    <t>Бытовой комфорт без забот</t>
+  </si>
+  <si>
+    <t>ИТОГО ПИТАНИЕ И БЫТ НА 2 МЕСЯЦА</t>
+  </si>
+  <si>
+    <t>Повседневные расходы</t>
+  </si>
+  <si>
+    <t>Здоровый и насыщенный рацион</t>
+  </si>
+  <si>
+    <t>6. Связь и тело</t>
+  </si>
+  <si>
+    <t>SIM/eSIM Telkomsel с пакетом 100 ГБ интернета на 60 дней</t>
+  </si>
+  <si>
+    <t>Telkomsel MyTelkomsel</t>
+  </si>
+  <si>
+    <t>Стабильный 4G/5G по всему Бали и Яве</t>
+  </si>
+  <si>
+    <t>Балийский традиционный массаж и телесная терапия (1 раз в неделю)</t>
+  </si>
+  <si>
+    <t>8 сессий</t>
+  </si>
+  <si>
+    <t>Проверенные мастера Убуда</t>
+  </si>
+  <si>
+    <t>300 000 IDR за сессию 1.5 часа</t>
+  </si>
+  <si>
+    <t>ИТОГО СВЯЗЬ И ЗДОРОВЬЕ</t>
+  </si>
+  <si>
+    <t>Здоровье и связь</t>
+  </si>
+  <si>
+    <t>Поддержание ресурса и энергии</t>
+  </si>
+  <si>
+    <t>ИТОГО 2 МЕСЯЦА ПРЕБЫВАНИЯ (С QATAR ЭКОНОМ)</t>
+  </si>
+  <si>
+    <t>Все включено: перелет Qatar, жилье 2 мес, байк, виза 60д, еда, быт</t>
+  </si>
+  <si>
+    <t>Qatar Airways Эконом</t>
+  </si>
+  <si>
+    <t>Гонорар от тура (7 200 €) покрывает поездку в 2 раза!</t>
+  </si>
+  <si>
+    <t>ИТОГО 2 МЕСЯЦА ПРЕБЫВАНИЯ (С QATAR БИЗНЕС)</t>
+  </si>
+  <si>
+    <t>Все включено с перелетом бизнес-классом Qatar Airways QSuite</t>
+  </si>
+  <si>
+    <t>Qatar Airways Бизнес</t>
+  </si>
+  <si>
+    <t>Даже с Бизнес-классом тур окупает поездку целиком!</t>
+  </si>
+  <si>
+    <t>ЭКСПЕДИЦИЯ НА ЯВУ: ПРАМБАНАН, ЧАНДИ ЧЕТО, СУКУХ И ПАНЧА ЯДНЯ</t>
+  </si>
+  <si>
+    <t>Сравнение сценариев: Быстрый авиаперелет (4-5 дней) vs Эпический Road Trip на байке (8-10 дней)</t>
+  </si>
+  <si>
+    <t>Статья расхода / Элемент маршрута</t>
+  </si>
+  <si>
+    <t>Сценарий А: Авиаперелет (4-5 дней) [€]</t>
+  </si>
+  <si>
+    <t>Сценарий Б: Байк Road Trip (8-10 дней) [€]</t>
+  </si>
+  <si>
+    <t>Стоимость А (IDR)</t>
+  </si>
+  <si>
+    <t>Стоимость Б (IDR)</t>
+  </si>
+  <si>
+    <t>Логистика и локации</t>
+  </si>
+  <si>
+    <t>Смысловая ценность и глубина</t>
+  </si>
+  <si>
+    <t>Рекомендация мастера</t>
+  </si>
+  <si>
+    <t>1. Транспорт до Джокьякарты и обратно</t>
+  </si>
+  <si>
+    <t>А: Прямой рейс DPS ⇄ YIA (1ч 15м) Lion/Citilink
+Б: Паром Gilimanuk-Ketapang RT (4€) + бензин на 1500 км (27€)</t>
+  </si>
+  <si>
+    <t>А: Экономия времени, прилетел свежим
+Б: Живая земля, вулкан Иджен, саванна Балуран, горы</t>
+  </si>
+  <si>
+    <t>Для духа и созерцания — Байк. Для тайминга — Самолет.</t>
+  </si>
+  <si>
+    <t>2. Передвижение на месте (в Джокье / в пути)</t>
+  </si>
+  <si>
+    <t>А: Аренда скутера в аэропорту Джокьи (5 дней x 5€)
+Б: Свой проверенный NMax из Убуда + замена масла (12€)</t>
+  </si>
+  <si>
+    <t>На своем байке посадка уже привычна, ехать комфортно</t>
+  </si>
+  <si>
+    <t>Надежный байк с хорошим светом и тормозами</t>
+  </si>
+  <si>
+    <t>3. Проживание (Отели / Гестхаусы)</t>
+  </si>
+  <si>
+    <t>А: 4 ночи в атмосферном бутик-отеле у Прамбанана (40€/н)
+Б: 8 ночей в пути: Баньюванги (Иджен), Бромо, Соло (Чето), Джокья</t>
+  </si>
+  <si>
+    <t>А: Базирование в одной точке
+Б: Каждая ночевка — новое место силы и рассвет в горах</t>
+  </si>
+  <si>
+    <t>В Соло остановиться у горы Лаву (прохлада 1400 м)</t>
+  </si>
+  <si>
+    <t>4. Входные билеты в храмы Явы</t>
+  </si>
+  <si>
+    <t>1) Прамбанан (Candi Prambanan) — индуистский триумф IX века
+2) Чанди Чето (Candi Cetho) — пирамида на горе Лаву
+3) Чанди Сукух (Candi Sukuh) — храм лингама XIV века</t>
+  </si>
+  <si>
+    <t>Панча Ядня (Pancha Yadnya): глубочайшее соприкосновение с доисламским шиваизмом Явы</t>
+  </si>
+  <si>
+    <t>Брать официальный комбо-билет на рассвете</t>
+  </si>
+  <si>
+    <t>5. Питание и кофе в путешествии</t>
+  </si>
+  <si>
+    <t>А: Кофейни и яванские рестораны в Джокьякарте (5 дней)
+Б: Домашние варунги Явы, свежий высокогорный кофе в горах (8 дней)</t>
+  </si>
+  <si>
+    <t>Яванская кухня (Gudeg, Nasi Liwet), аутентичный кофе колок</t>
+  </si>
+  <si>
+    <t>Пить местный высокогорный кофе прямо у плантаций</t>
+  </si>
+  <si>
+    <t>6. Проводники и сакральные подношения</t>
+  </si>
+  <si>
+    <t>Подношения духам предков у храма Чето, местный хранитель (Juru Kunci)</t>
+  </si>
+  <si>
+    <t>Позволяет войти во внутренние святилища террас Чето без толп</t>
+  </si>
+  <si>
+    <t>Уважение к местным духам горы Лаву</t>
+  </si>
+  <si>
+    <t>ИТОГО БЮДЖЕТ ЭКСПЕДИЦИИ НА ЯВУ</t>
+  </si>
+  <si>
+    <t>А: 460 € (Самолет, 5 дней) • Б: 443 € (Байк Road Trip, 8-10 дней)</t>
+  </si>
+  <si>
+    <t>По бюджету сценарии РАВНЫ (~450 € под ключ)</t>
+  </si>
+  <si>
+    <t>РЕКОМЕНДАЦИЯ: Поехать на байке — трансформирующий роадтрип!</t>
+  </si>
+  <si>
+    <t>МАРШРУТ ROAD TRIP НА БАЙКЕ (ПО ДНЯМ):</t>
+  </si>
+  <si>
+    <t>• День 1: Убуд → Западный Бали (Гилиманук) 130 км → Паром 45 мин на Яву (Кетапанг) → Баньюванги. Ночь у вулкана Иджен.</t>
+  </si>
+  <si>
+    <t>• День 2: Баньюванги → Саванна парка Балуран (яванская Африка) → Проболинго (180 км). Ночь с видом на вулкан Бромо.</t>
+  </si>
+  <si>
+    <t>• День 3: Проболинго → Маланг → Соло (Суракарта) 220 км. Подъем на гору Лаву (1400 м) к храмам Чанди Чето и Сукух. Ночь в горах.</t>
+  </si>
+  <si>
+    <t>• День 4-5: Спуск в Джокьякарту. Прамбанан на рассвете (культ Шивы, Брахмы, Вишну), храмы Севу и Плаосан. Вечерний яванский кофе.</t>
+  </si>
+  <si>
+    <t>• День 6-8: Неспешный обратный путь через южное побережье Явы, паром и возвращение на Бали в Убуд.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
@@ -1174,8 +1574,14 @@
       <name val="Arial"/>
       <color rgb="FF1F497D"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <color rgb="FFB22222"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1212,6 +1618,11 @@
         <fgColor rgb="FFEBF1F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1238,7 +1649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0"/>
@@ -1248,6 +1659,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -3566,4 +3978,994 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="8">
+        <v>370</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>371</v>
+      </c>
+      <c r="D4" t="s" s="1">
+        <v>372</v>
+      </c>
+      <c r="E4" t="s" s="1">
+        <v>373</v>
+      </c>
+      <c r="F4" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s" s="1">
+        <v>374</v>
+      </c>
+      <c r="H4" t="s" s="1">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1050</v>
+      </c>
+      <c r="E5" s="0">
+        <v>3800</v>
+      </c>
+      <c r="F5" s="0">
+        <v>17850000</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1150</v>
+      </c>
+      <c r="E6" s="0">
+        <v>4200</v>
+      </c>
+      <c r="F6" s="0">
+        <v>19550000</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="9">
+        <v>376</v>
+      </c>
+      <c r="B7" t="s" s="9">
+        <v>384</v>
+      </c>
+      <c r="C7" t="s" s="9">
+        <v>378</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1100</v>
+      </c>
+      <c r="E7" s="9">
+        <v>4600</v>
+      </c>
+      <c r="F7" s="9">
+        <v>18700000</v>
+      </c>
+      <c r="G7" t="s" s="9">
+        <v>385</v>
+      </c>
+      <c r="H7" t="s" s="9">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="5">
+        <v>376</v>
+      </c>
+      <c r="B8" t="s" s="5">
+        <v>387</v>
+      </c>
+      <c r="C8" t="s" s="5">
+        <v>378</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1050</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3800</v>
+      </c>
+      <c r="F8" s="5">
+        <v>17850000</v>
+      </c>
+      <c r="G8" t="s" s="5">
+        <v>388</v>
+      </c>
+      <c r="H8" t="s" s="5">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="D9" s="0">
+        <v>90</v>
+      </c>
+      <c r="E9" s="0">
+        <v>90</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1500000</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>395</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="D10" s="0">
+        <v>64</v>
+      </c>
+      <c r="E10" s="0">
+        <v>64</v>
+      </c>
+      <c r="F10" s="0">
+        <v>1000000</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="D11" s="0">
+        <v>9</v>
+      </c>
+      <c r="E11" s="0">
+        <v>9</v>
+      </c>
+      <c r="F11" s="0">
+        <v>150000</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="5">
+        <v>390</v>
+      </c>
+      <c r="B12" t="s" s="5">
+        <v>402</v>
+      </c>
+      <c r="C12" t="s" s="5">
+        <v>392</v>
+      </c>
+      <c r="D12" s="5">
+        <v>99</v>
+      </c>
+      <c r="E12" s="5">
+        <v>99</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1650000</v>
+      </c>
+      <c r="G12" t="s" s="5">
+        <v>403</v>
+      </c>
+      <c r="H12" t="s" s="5">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="D13" s="0">
+        <v>470</v>
+      </c>
+      <c r="E13" s="0">
+        <v>470</v>
+      </c>
+      <c r="F13" s="0">
+        <v>8000000</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>410</v>
+      </c>
+      <c r="D14" s="0">
+        <v>470</v>
+      </c>
+      <c r="E14" s="0">
+        <v>470</v>
+      </c>
+      <c r="F14" s="0">
+        <v>8000000</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="5">
+        <v>405</v>
+      </c>
+      <c r="B15" t="s" s="5">
+        <v>412</v>
+      </c>
+      <c r="C15" t="s" s="5">
+        <v>413</v>
+      </c>
+      <c r="D15" s="5">
+        <v>940</v>
+      </c>
+      <c r="E15" s="5">
+        <v>940</v>
+      </c>
+      <c r="F15" s="5">
+        <v>16000000</v>
+      </c>
+      <c r="G15" t="s" s="5">
+        <v>414</v>
+      </c>
+      <c r="H15" t="s" s="5">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>417</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>413</v>
+      </c>
+      <c r="D16" s="0">
+        <v>190</v>
+      </c>
+      <c r="E16" s="0">
+        <v>190</v>
+      </c>
+      <c r="F16" s="0">
+        <v>3200000</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>418</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>416</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>420</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>413</v>
+      </c>
+      <c r="D17" s="0">
+        <v>35</v>
+      </c>
+      <c r="E17" s="0">
+        <v>35</v>
+      </c>
+      <c r="F17" s="0">
+        <v>600000</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="5">
+        <v>416</v>
+      </c>
+      <c r="B18" t="s" s="5">
+        <v>423</v>
+      </c>
+      <c r="C18" t="s" s="5">
+        <v>413</v>
+      </c>
+      <c r="D18" s="5">
+        <v>225</v>
+      </c>
+      <c r="E18" s="5">
+        <v>225</v>
+      </c>
+      <c r="F18" s="5">
+        <v>3800000</v>
+      </c>
+      <c r="G18" t="s" s="5">
+        <v>424</v>
+      </c>
+      <c r="H18" t="s" s="5">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="D19" s="0">
+        <v>1060</v>
+      </c>
+      <c r="E19" s="0">
+        <v>1060</v>
+      </c>
+      <c r="F19" s="0">
+        <v>18000000</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="D20" s="0">
+        <v>70</v>
+      </c>
+      <c r="E20" s="0">
+        <v>70</v>
+      </c>
+      <c r="F20" s="0">
+        <v>1200000</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>431</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="5">
+        <v>426</v>
+      </c>
+      <c r="B21" t="s" s="5">
+        <v>433</v>
+      </c>
+      <c r="C21" t="s" s="5">
+        <v>392</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1130</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1130</v>
+      </c>
+      <c r="F21" s="5">
+        <v>19200000</v>
+      </c>
+      <c r="G21" t="s" s="5">
+        <v>434</v>
+      </c>
+      <c r="H21" t="s" s="5">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>437</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>413</v>
+      </c>
+      <c r="D22" s="0">
+        <v>35</v>
+      </c>
+      <c r="E22" s="0">
+        <v>35</v>
+      </c>
+      <c r="F22" s="0">
+        <v>600000</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>438</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>436</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>441</v>
+      </c>
+      <c r="D23" s="0">
+        <v>140</v>
+      </c>
+      <c r="E23" s="0">
+        <v>140</v>
+      </c>
+      <c r="F23" s="0">
+        <v>2400000</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>442</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="5">
+        <v>436</v>
+      </c>
+      <c r="B24" t="s" s="5">
+        <v>444</v>
+      </c>
+      <c r="C24" t="s" s="5">
+        <v>392</v>
+      </c>
+      <c r="D24" s="5">
+        <v>175</v>
+      </c>
+      <c r="E24" s="5">
+        <v>175</v>
+      </c>
+      <c r="F24" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="G24" t="s" s="5">
+        <v>445</v>
+      </c>
+      <c r="H24" t="s" s="5">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+      <c r="C25" s="0"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="7">
+        <v>447</v>
+      </c>
+      <c r="B26" t="s" s="7">
+        <v>448</v>
+      </c>
+      <c r="C26" t="s" s="7">
+        <v>392</v>
+      </c>
+      <c r="D26" s="7">
+        <v>3619</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3619</v>
+      </c>
+      <c r="F26" s="7">
+        <v>61500000</v>
+      </c>
+      <c r="G26" t="s" s="7">
+        <v>449</v>
+      </c>
+      <c r="H26" t="s" s="7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="7">
+        <v>451</v>
+      </c>
+      <c r="B27" t="s" s="7">
+        <v>452</v>
+      </c>
+      <c r="C27" t="s" s="7">
+        <v>392</v>
+      </c>
+      <c r="D27" s="7">
+        <v>6369</v>
+      </c>
+      <c r="E27" s="7">
+        <v>6369</v>
+      </c>
+      <c r="F27" s="7">
+        <v>108250000</v>
+      </c>
+      <c r="G27" t="s" s="7">
+        <v>453</v>
+      </c>
+      <c r="H27" t="s" s="7">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="8">
+        <v>456</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>457</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>459</v>
+      </c>
+      <c r="D4" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="E4" t="s" s="1">
+        <v>461</v>
+      </c>
+      <c r="F4" t="s" s="1">
+        <v>462</v>
+      </c>
+      <c r="G4" t="s" s="1">
+        <v>463</v>
+      </c>
+      <c r="H4" t="s" s="1">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="B5" s="0">
+        <v>105</v>
+      </c>
+      <c r="C5" s="0">
+        <v>31</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1800000</v>
+      </c>
+      <c r="E5" s="0">
+        <v>530000</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="B6" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" s="0">
+        <v>12</v>
+      </c>
+      <c r="D6" s="0">
+        <v>400000</v>
+      </c>
+      <c r="E6" s="0">
+        <v>200000</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>470</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>471</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="B7" s="0">
+        <v>165</v>
+      </c>
+      <c r="C7" s="0">
+        <v>210</v>
+      </c>
+      <c r="D7" s="0">
+        <v>2800000</v>
+      </c>
+      <c r="E7" s="0">
+        <v>3600000</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="B8" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" s="0">
+        <v>55</v>
+      </c>
+      <c r="D8" s="0">
+        <v>950000</v>
+      </c>
+      <c r="E8" s="0">
+        <v>950000</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>478</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>479</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>481</v>
+      </c>
+      <c r="B9" s="0">
+        <v>70</v>
+      </c>
+      <c r="C9" s="0">
+        <v>95</v>
+      </c>
+      <c r="D9" s="0">
+        <v>1200000</v>
+      </c>
+      <c r="E9" s="0">
+        <v>1600000</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>482</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>483</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="B10" s="0">
+        <v>40</v>
+      </c>
+      <c r="C10" s="0">
+        <v>40</v>
+      </c>
+      <c r="D10" s="0">
+        <v>700000</v>
+      </c>
+      <c r="E10" s="0">
+        <v>700000</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>486</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>487</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="7">
+        <v>489</v>
+      </c>
+      <c r="B12" s="7">
+        <v>460</v>
+      </c>
+      <c r="C12" s="7">
+        <v>443</v>
+      </c>
+      <c r="D12" s="7">
+        <v>7850000</v>
+      </c>
+      <c r="E12" s="7">
+        <v>7580000</v>
+      </c>
+      <c r="F12" t="s" s="7">
+        <v>490</v>
+      </c>
+      <c r="G12" t="s" s="7">
+        <v>491</v>
+      </c>
+      <c r="H12" t="s" s="7">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="4">
+        <v>494</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>495</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="4">
+        <v>496</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>497</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="4">
+        <v>498</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="537">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
@@ -295,6 +295,33 @@
   </si>
   <si>
     <t>Fine-art фотосессия для гостий</t>
+  </si>
+  <si>
+    <t>Интеллектуальный салон: встреча с д-ром Лоуренсом Блэром («Ring of Fire»)</t>
+  </si>
+  <si>
+    <t>1 встреча</t>
+  </si>
+  <si>
+    <t>Эксклюзивный доступ автора (35 лет экспедиций)</t>
+  </si>
+  <si>
+    <t>Частный визит в резиденцию Брюса Карпентера (сакральные крисы и маски)</t>
+  </si>
+  <si>
+    <t>1 визит</t>
+  </si>
+  <si>
+    <t>Эксперт Christie's / автор монографий</t>
+  </si>
+  <si>
+    <t>Арт-маршрут Убуда: музей Бланко, Neka Art Museum (павильон крисов), ARMA</t>
+  </si>
+  <si>
+    <t>1 день</t>
+  </si>
+  <si>
+    <t>Билеты включены в общую сакральную программу</t>
   </si>
   <si>
     <t>Непрерывное кураторство 24/7 (индонезийский и английский языки)</t>
@@ -1129,6 +1156,93 @@
   </si>
   <si>
     <t>Королевский балийский уход</t>
+  </si>
+  <si>
+    <t>The Blanco Renaissance Museum</t>
+  </si>
+  <si>
+    <t>Семья Антонио Бланко</t>
+  </si>
+  <si>
+    <t>https://blancomuseum.com</t>
+  </si>
+  <si>
+    <t>Вход в музей, сад попугаев, галерея</t>
+  </si>
+  <si>
+    <t>В кассе музея</t>
+  </si>
+  <si>
+    <t>Балийский Сальвадор Дали над р. Чампуан</t>
+  </si>
+  <si>
+    <t>Neka Art Museum</t>
+  </si>
+  <si>
+    <t>Suteja Neka Foundation</t>
+  </si>
+  <si>
+    <t>https://museumneka.com</t>
+  </si>
+  <si>
+    <t>Академическая коллекция + Павильон Крисов</t>
+  </si>
+  <si>
+    <t>Сакральные метеоритные клинки и Pita Maha</t>
+  </si>
+  <si>
+    <t>ARMA Museum (Agung Rai)</t>
+  </si>
+  <si>
+    <t>Agung Rai Foundation</t>
+  </si>
+  <si>
+    <t>https://armabali.com</t>
+  </si>
+  <si>
+    <t>Музей-усадьба, подлинники Вальтера Шписа</t>
+  </si>
+  <si>
+    <t>Живой музей в рисовых полях</t>
+  </si>
+  <si>
+    <t>Д-р Лоуренс Блэр (Ring of Fire)</t>
+  </si>
+  <si>
+    <t>Dr. Lawrence Blair (личный контакт)</t>
+  </si>
+  <si>
+    <t>Приватный салон</t>
+  </si>
+  <si>
+    <t>Включено в тур</t>
+  </si>
+  <si>
+    <t>Личный контакт Валерия</t>
+  </si>
+  <si>
+    <t>Камерная беседа об экспедициях, вино/чай</t>
+  </si>
+  <si>
+    <t>Организуется Валерием</t>
+  </si>
+  <si>
+    <t>35 лет экспедиций по диким островам</t>
+  </si>
+  <si>
+    <t>Брюс Карпентер (Bruce Carpenter)</t>
+  </si>
+  <si>
+    <t>Bruce W. Carpenter (личный контакт)</t>
+  </si>
+  <si>
+    <t>Частный визит</t>
+  </si>
+  <si>
+    <t>Сессия по сакральным крисам, маскам и золоту</t>
+  </si>
+  <si>
+    <t>Ведущий мировой эксперт Christie's</t>
   </si>
   <si>
     <t>ЛИЧНЫЙ БЮДЖЕТ ПРЕБЫВАНИЯ ВАЛЕРИЯ НА БАЛИ: 2 МЕСЯЦА (60 ДНЕЙ)</t>
@@ -2359,7 +2473,7 @@
         <v>94</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="D29" s="0">
         <v>0</v>
@@ -2374,7 +2488,890 @@
         <v>89</v>
       </c>
       <c r="H29" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="0"/>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s" s="3">
+        <v>106</v>
+      </c>
+      <c r="C34" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="D34" s="3">
+        <v>7188</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F34" s="3">
+        <v>81800000</v>
+      </c>
+      <c r="G34" t="s" s="3">
+        <v>107</v>
+      </c>
+      <c r="H34" t="s" s="3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="7">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s" s="7">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s" s="7">
+        <v>29</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2512</v>
+      </c>
+      <c r="E35" s="7">
+        <v>7200</v>
+      </c>
+      <c r="F35" s="7">
+        <v>122700000</v>
+      </c>
+      <c r="G35" t="s" s="7">
+        <v>111</v>
+      </c>
+      <c r="H35" t="s" s="7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2">
+        <v>9700</v>
+      </c>
+      <c r="E36" s="2">
+        <v>12000</v>
+      </c>
+      <c r="F36" s="2">
+        <v>204500000</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="4">
+        <v>118</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0"/>
+      <c r="B3" s="0"/>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s" s="1">
+        <v>119</v>
+      </c>
+      <c r="E4" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s" s="1">
+        <v>120</v>
+      </c>
+      <c r="H4" t="s" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1700</v>
+      </c>
+      <c r="E5" s="0">
+        <v>640</v>
+      </c>
+      <c r="F5" s="0">
+        <v>11000000</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" s="0">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="0">
+        <v>680</v>
+      </c>
+      <c r="F6" s="0">
+        <v>11600000</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="5">
+        <v>121</v>
+      </c>
+      <c r="B7" t="s" s="5">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s" s="5">
+        <v>129</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3700</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1320</v>
+      </c>
+      <c r="F7" s="5">
+        <v>22600000</v>
+      </c>
+      <c r="G7" t="s" s="5">
+        <v>130</v>
+      </c>
+      <c r="H7" t="s" s="5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D8" s="0">
+        <v>400</v>
+      </c>
+      <c r="E8" s="0">
+        <v>320</v>
+      </c>
+      <c r="F8" s="0">
+        <v>5500000</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D9" s="0">
+        <v>100</v>
+      </c>
+      <c r="E9" s="0">
+        <v>105</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1800000</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="5">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s" s="5">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s" s="5">
+        <v>133</v>
+      </c>
+      <c r="D10" s="5">
+        <v>500</v>
+      </c>
+      <c r="E10" s="5">
+        <v>425</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7300000</v>
+      </c>
+      <c r="G10" t="s" s="5">
+        <v>140</v>
+      </c>
+      <c r="H10" t="s" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D11" s="0">
+        <v>50</v>
+      </c>
+      <c r="E11" s="0">
+        <v>160</v>
+      </c>
+      <c r="F11" s="0">
+        <v>2700000</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D12" s="0">
+        <v>60</v>
+      </c>
+      <c r="E12" s="0">
+        <v>64</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1000000</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D13" s="0">
+        <v>18</v>
+      </c>
+      <c r="E13" s="0">
+        <v>18</v>
+      </c>
+      <c r="F13" s="0">
+        <v>300000</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s" s="5">
+        <v>146</v>
+      </c>
+      <c r="C14" t="s" s="5">
+        <v>40</v>
+      </c>
+      <c r="D14" s="5">
+        <v>128</v>
+      </c>
+      <c r="E14" s="5">
+        <v>242</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4000000</v>
+      </c>
+      <c r="G14" t="s" s="5">
+        <v>147</v>
+      </c>
+      <c r="H14" t="s" s="5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D15" s="0">
+        <v>200</v>
+      </c>
+      <c r="E15" s="0">
+        <v>190</v>
+      </c>
+      <c r="F15" s="0">
+        <v>3200000</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D16" s="0">
+        <v>100</v>
+      </c>
+      <c r="E16" s="0">
+        <v>100</v>
+      </c>
+      <c r="F16" s="0">
+        <v>1700000</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="5">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s" s="5">
+        <v>153</v>
+      </c>
+      <c r="C17" t="s" s="5">
+        <v>61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>300</v>
+      </c>
+      <c r="E17" s="5">
+        <v>290</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4900000</v>
+      </c>
+      <c r="G17" t="s" s="5">
+        <v>154</v>
+      </c>
+      <c r="H17" t="s" s="5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D18" s="0">
+        <v>120</v>
+      </c>
+      <c r="E18" s="0">
+        <v>105</v>
+      </c>
+      <c r="F18" s="0">
+        <v>1800000</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D19" s="0">
+        <v>50</v>
+      </c>
+      <c r="E19" s="0">
+        <v>50</v>
+      </c>
+      <c r="F19" s="0">
+        <v>850000</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="5">
+        <v>160</v>
+      </c>
+      <c r="C20" t="s" s="5">
+        <v>61</v>
+      </c>
+      <c r="D20" s="5">
+        <v>170</v>
+      </c>
+      <c r="E20" s="5">
+        <v>155</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2650000</v>
+      </c>
+      <c r="G20" t="s" s="5">
+        <v>161</v>
+      </c>
+      <c r="H20" t="s" s="5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D21" s="0">
+        <v>150</v>
+      </c>
+      <c r="E21" s="0">
+        <v>150</v>
+      </c>
+      <c r="F21" s="0">
+        <v>2550000</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D22" s="0">
+        <v>250</v>
+      </c>
+      <c r="E22" s="0">
+        <v>250</v>
+      </c>
+      <c r="F22" s="0">
+        <v>4250000</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D23" s="0">
+        <v>200</v>
+      </c>
+      <c r="E23" s="0">
+        <v>200</v>
+      </c>
+      <c r="F23" s="0">
+        <v>3400000</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="5">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s" s="5">
+        <v>172</v>
+      </c>
+      <c r="C24" t="s" s="5">
+        <v>61</v>
+      </c>
+      <c r="D24" s="5">
+        <v>600</v>
+      </c>
+      <c r="E24" s="5">
+        <v>600</v>
+      </c>
+      <c r="F24" s="5">
+        <v>10200000</v>
+      </c>
+      <c r="G24" t="s" s="5">
+        <v>173</v>
+      </c>
+      <c r="H24" t="s" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s" s="0">
         <v>95</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>104</v>
       </c>
     </row>
     <row r="30">
@@ -2389,92 +3386,92 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s" s="3">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="C31" t="s" s="3">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="D31" s="3">
-        <v>7188</v>
+        <v>5398</v>
       </c>
       <c r="E31" s="3">
-        <v>4800</v>
+        <v>3400</v>
       </c>
       <c r="F31" s="3">
-        <v>81800000</v>
+        <v>57950000</v>
       </c>
       <c r="G31" t="s" s="3">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="H31" t="s" s="3">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="7">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s" s="7">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s" s="7">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="D32" s="7">
-        <v>2512</v>
+        <v>2102</v>
       </c>
       <c r="E32" s="7">
-        <v>7200</v>
+        <v>5100</v>
       </c>
       <c r="F32" s="7">
-        <v>122700000</v>
+        <v>86925000</v>
       </c>
       <c r="G32" t="s" s="7">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="H32" t="s" s="7">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="D33" s="2">
-        <v>9700</v>
+        <v>7500</v>
       </c>
       <c r="E33" s="2">
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="F33" s="2">
-        <v>204500000</v>
+        <v>144875000</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2485,16 +3482,16 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="4">
-        <v>109</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" t="s" s="8">
+        <v>182</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3">
       <c r="A3" s="0"/>
@@ -2508,726 +3505,300 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>7</v>
+        <v>188</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D5" s="0">
-        <v>1700</v>
-      </c>
-      <c r="E5" s="0">
-        <v>640</v>
-      </c>
-      <c r="F5" s="0">
-        <v>11000000</v>
+        <v>193</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>196</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>115</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D6" s="0">
-        <v>2000</v>
-      </c>
-      <c r="E6" s="0">
-        <v>680</v>
-      </c>
-      <c r="F6" s="0">
-        <v>11600000</v>
+        <v>201</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>204</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>118</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="5">
-        <v>112</v>
-      </c>
-      <c r="B7" t="s" s="5">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s" s="5">
-        <v>120</v>
-      </c>
-      <c r="D7" s="5">
-        <v>3700</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1320</v>
-      </c>
-      <c r="F7" s="5">
-        <v>22600000</v>
-      </c>
-      <c r="G7" t="s" s="5">
-        <v>121</v>
-      </c>
-      <c r="H7" t="s" s="5">
-        <v>122</v>
+      <c r="A7" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D8" s="0">
-        <v>400</v>
-      </c>
-      <c r="E8" s="0">
-        <v>320</v>
-      </c>
-      <c r="F8" s="0">
-        <v>5500000</v>
+        <v>217</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>220</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>125</v>
+        <v>221</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>126</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D9" s="0">
-        <v>100</v>
-      </c>
-      <c r="E9" s="0">
-        <v>105</v>
-      </c>
-      <c r="F9" s="0">
-        <v>1800000</v>
+        <v>225</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>228</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>129</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="5">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s" s="5">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s" s="5">
-        <v>124</v>
-      </c>
-      <c r="D10" s="5">
-        <v>500</v>
-      </c>
-      <c r="E10" s="5">
-        <v>425</v>
-      </c>
-      <c r="F10" s="5">
-        <v>7300000</v>
-      </c>
-      <c r="G10" t="s" s="5">
-        <v>131</v>
-      </c>
-      <c r="H10" t="s" s="5">
-        <v>37</v>
+      <c r="A10" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>38</v>
+        <v>239</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D11" s="0">
-        <v>50</v>
-      </c>
-      <c r="E11" s="0">
-        <v>160</v>
-      </c>
-      <c r="F11" s="0">
-        <v>2700000</v>
+        <v>241</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>244</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>133</v>
+        <v>245</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>134</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>38</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>43</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D12" s="0">
-        <v>60</v>
-      </c>
-      <c r="E12" s="0">
-        <v>64</v>
-      </c>
-      <c r="F12" s="0">
-        <v>1000000</v>
+        <v>233</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>251</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>135</v>
+        <v>252</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>45</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>46</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D13" s="0">
-        <v>18</v>
-      </c>
-      <c r="E13" s="0">
-        <v>18</v>
-      </c>
-      <c r="F13" s="0">
-        <v>300000</v>
+        <v>256</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>259</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>48</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="5">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s" s="5">
-        <v>137</v>
-      </c>
-      <c r="C14" t="s" s="5">
-        <v>40</v>
-      </c>
-      <c r="D14" s="5">
-        <v>128</v>
-      </c>
-      <c r="E14" s="5">
-        <v>242</v>
-      </c>
-      <c r="F14" s="5">
-        <v>4000000</v>
-      </c>
-      <c r="G14" t="s" s="5">
-        <v>138</v>
-      </c>
-      <c r="H14" t="s" s="5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D15" s="0">
-        <v>200</v>
-      </c>
-      <c r="E15" s="0">
-        <v>190</v>
-      </c>
-      <c r="F15" s="0">
-        <v>3200000</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D16" s="0">
-        <v>100</v>
-      </c>
-      <c r="E16" s="0">
-        <v>100</v>
-      </c>
-      <c r="F16" s="0">
-        <v>1700000</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="5">
-        <v>139</v>
-      </c>
-      <c r="B17" t="s" s="5">
-        <v>144</v>
-      </c>
-      <c r="C17" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D17" s="5">
-        <v>300</v>
-      </c>
-      <c r="E17" s="5">
-        <v>290</v>
-      </c>
-      <c r="F17" s="5">
-        <v>4900000</v>
-      </c>
-      <c r="G17" t="s" s="5">
-        <v>145</v>
-      </c>
-      <c r="H17" t="s" s="5">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D18" s="0">
-        <v>120</v>
-      </c>
-      <c r="E18" s="0">
-        <v>105</v>
-      </c>
-      <c r="F18" s="0">
-        <v>1800000</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D19" s="0">
-        <v>50</v>
-      </c>
-      <c r="E19" s="0">
-        <v>50</v>
-      </c>
-      <c r="F19" s="0">
-        <v>850000</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="5">
-        <v>64</v>
-      </c>
-      <c r="B20" t="s" s="5">
-        <v>151</v>
-      </c>
-      <c r="C20" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D20" s="5">
-        <v>170</v>
-      </c>
-      <c r="E20" s="5">
-        <v>155</v>
-      </c>
-      <c r="F20" s="5">
-        <v>2650000</v>
-      </c>
-      <c r="G20" t="s" s="5">
-        <v>152</v>
-      </c>
-      <c r="H20" t="s" s="5">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D21" s="0">
-        <v>150</v>
-      </c>
-      <c r="E21" s="0">
-        <v>150</v>
-      </c>
-      <c r="F21" s="0">
-        <v>2550000</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>155</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>157</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D22" s="0">
-        <v>250</v>
-      </c>
-      <c r="E22" s="0">
-        <v>250</v>
-      </c>
-      <c r="F22" s="0">
-        <v>4250000</v>
-      </c>
-      <c r="G22" t="s" s="0">
-        <v>158</v>
-      </c>
-      <c r="H22" t="s" s="0">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>160</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D23" s="0">
-        <v>200</v>
-      </c>
-      <c r="E23" s="0">
-        <v>200</v>
-      </c>
-      <c r="F23" s="0">
-        <v>3400000</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="H23" t="s" s="0">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="5">
-        <v>77</v>
-      </c>
-      <c r="B24" t="s" s="5">
-        <v>163</v>
-      </c>
-      <c r="C24" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D24" s="5">
-        <v>600</v>
-      </c>
-      <c r="E24" s="5">
-        <v>600</v>
-      </c>
-      <c r="F24" s="5">
-        <v>10200000</v>
-      </c>
-      <c r="G24" t="s" s="5">
-        <v>164</v>
-      </c>
-      <c r="H24" t="s" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>165</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D25" s="0">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0">
-        <v>0</v>
-      </c>
-      <c r="F25" s="0">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="H25" t="s" s="0">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D26" s="0">
-        <v>0</v>
-      </c>
-      <c r="E26" s="0">
-        <v>0</v>
-      </c>
-      <c r="F26" s="0">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="H26" t="s" s="0">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D27" s="0">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0">
-        <v>0</v>
-      </c>
-      <c r="F27" s="0">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="H27" t="s" s="0">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0"/>
-      <c r="B28" s="0"/>
-      <c r="C28" s="0"/>
-      <c r="D28" s="0"/>
-      <c r="E28" s="0"/>
-      <c r="F28" s="0"/>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="3">
-        <v>96</v>
-      </c>
-      <c r="B29" t="s" s="3">
-        <v>167</v>
-      </c>
-      <c r="C29" t="s" s="3">
-        <v>124</v>
-      </c>
-      <c r="D29" s="3">
-        <v>5398</v>
-      </c>
-      <c r="E29" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F29" s="3">
-        <v>57950000</v>
-      </c>
-      <c r="G29" t="s" s="3">
-        <v>168</v>
-      </c>
-      <c r="H29" t="s" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="7">
-        <v>100</v>
-      </c>
-      <c r="B30" t="s" s="7">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s" s="7">
-        <v>124</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2102</v>
-      </c>
-      <c r="E30" s="7">
-        <v>5100</v>
-      </c>
-      <c r="F30" s="7">
-        <v>86925000</v>
-      </c>
-      <c r="G30" t="s" s="7">
-        <v>169</v>
-      </c>
-      <c r="H30" t="s" s="7">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="D31" s="2">
-        <v>7500</v>
-      </c>
-      <c r="E31" s="2">
-        <v>8500</v>
-      </c>
-      <c r="F31" s="2">
-        <v>144875000</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>171</v>
+      <c r="A14" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3238,16 +3809,16 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="8">
-        <v>173</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="A2" t="s" s="4">
+        <v>271</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="0"/>
@@ -3261,300 +3832,534 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>176</v>
+        <v>274</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>178</v>
+        <v>276</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>181</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>182</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>183</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>185</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>189</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>193</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>194</v>
-      </c>
       <c r="F6" t="s" s="0">
-        <v>195</v>
+        <v>291</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>197</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>198</v>
+        <v>294</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>199</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="D7" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>202</v>
-      </c>
       <c r="F7" t="s" s="0">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>205</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>206</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>207</v>
+        <v>302</v>
       </c>
       <c r="C8" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="D8" t="s" s="0">
-        <v>209</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>210</v>
-      </c>
       <c r="F8" t="s" s="0">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>212</v>
+        <v>304</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>213</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>214</v>
+        <v>306</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>215</v>
+        <v>307</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>221</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>223</v>
+        <v>315</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>225</v>
+        <v>317</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>227</v>
+        <v>318</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>229</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>231</v>
+        <v>322</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>232</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>233</v>
+        <v>324</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>235</v>
+        <v>325</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>237</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>239</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>240</v>
+        <v>331</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>242</v>
+        <v>332</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>243</v>
+        <v>333</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>244</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>246</v>
+        <v>336</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>249</v>
+        <v>337</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>252</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>257</v>
+        <v>337</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>259</v>
+        <v>346</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>260</v>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>371</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>390</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>395</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>396</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>397</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>402</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>397</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>261</v>
+        <v>407</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3565,16 +4370,16 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="4">
-        <v>262</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" t="s" s="8">
+        <v>408</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3">
       <c r="A3" s="0"/>
@@ -3588,404 +4393,622 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>264</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>265</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>266</v>
+        <v>410</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>268</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>269</v>
+        <v>412</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>270</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>271</v>
+        <v>414</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>272</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>273</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>274</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>275</v>
+        <v>416</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1050</v>
+      </c>
+      <c r="E5" s="0">
+        <v>3800</v>
+      </c>
+      <c r="F5" s="0">
+        <v>17850000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>276</v>
+        <v>417</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>277</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>278</v>
+        <v>414</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>279</v>
+        <v>419</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>280</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>281</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>183</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>282</v>
+        <v>416</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1150</v>
+      </c>
+      <c r="E6" s="0">
+        <v>4200</v>
+      </c>
+      <c r="F6" s="0">
+        <v>19550000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>283</v>
+        <v>420</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>284</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>285</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>286</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>287</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>289</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>290</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>291</v>
+      <c r="A7" t="s" s="9">
+        <v>414</v>
+      </c>
+      <c r="B7" t="s" s="9">
+        <v>422</v>
+      </c>
+      <c r="C7" t="s" s="9">
+        <v>416</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1100</v>
+      </c>
+      <c r="E7" s="9">
+        <v>4600</v>
+      </c>
+      <c r="F7" s="9">
+        <v>18700000</v>
+      </c>
+      <c r="G7" t="s" s="9">
+        <v>423</v>
+      </c>
+      <c r="H7" t="s" s="9">
+        <v>424</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>292</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>293</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>294</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>295</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>296</v>
+      <c r="A8" t="s" s="5">
+        <v>414</v>
+      </c>
+      <c r="B8" t="s" s="5">
+        <v>425</v>
+      </c>
+      <c r="C8" t="s" s="5">
+        <v>416</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1050</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3800</v>
+      </c>
+      <c r="F8" s="5">
+        <v>17850000</v>
+      </c>
+      <c r="G8" t="s" s="5">
+        <v>426</v>
+      </c>
+      <c r="H8" t="s" s="5">
+        <v>427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>297</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>298</v>
+        <v>429</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>299</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>300</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>301</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>302</v>
+        <v>430</v>
+      </c>
+      <c r="D9" s="0">
+        <v>90</v>
+      </c>
+      <c r="E9" s="0">
+        <v>90</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1500000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>303</v>
+        <v>431</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>304</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>305</v>
+        <v>428</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>306</v>
+        <v>433</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>307</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>308</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>309</v>
+        <v>434</v>
+      </c>
+      <c r="D10" s="0">
+        <v>64</v>
+      </c>
+      <c r="E10" s="0">
+        <v>64</v>
+      </c>
+      <c r="F10" s="0">
+        <v>1000000</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>310</v>
+        <v>431</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>311</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>313</v>
+        <v>436</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>314</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>315</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>316</v>
+        <v>437</v>
+      </c>
+      <c r="D11" s="0">
+        <v>9</v>
+      </c>
+      <c r="E11" s="0">
+        <v>9</v>
+      </c>
+      <c r="F11" s="0">
+        <v>150000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>317</v>
+        <v>438</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>318</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>319</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>320</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>321</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>322</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>323</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>324</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>325</v>
+      <c r="A12" t="s" s="5">
+        <v>428</v>
+      </c>
+      <c r="B12" t="s" s="5">
+        <v>440</v>
+      </c>
+      <c r="C12" t="s" s="5">
+        <v>430</v>
+      </c>
+      <c r="D12" s="5">
+        <v>99</v>
+      </c>
+      <c r="E12" s="5">
+        <v>99</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1650000</v>
+      </c>
+      <c r="G12" t="s" s="5">
+        <v>441</v>
+      </c>
+      <c r="H12" t="s" s="5">
+        <v>442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>326</v>
+        <v>443</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>327</v>
+        <v>444</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>287</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>328</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>329</v>
+        <v>445</v>
+      </c>
+      <c r="D13" s="0">
+        <v>470</v>
+      </c>
+      <c r="E13" s="0">
+        <v>470</v>
+      </c>
+      <c r="F13" s="0">
+        <v>8000000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>330</v>
+        <v>446</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>331</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>332</v>
+        <v>443</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>333</v>
+        <v>444</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>334</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>335</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>328</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>336</v>
+        <v>448</v>
+      </c>
+      <c r="D14" s="0">
+        <v>470</v>
+      </c>
+      <c r="E14" s="0">
+        <v>470</v>
+      </c>
+      <c r="F14" s="0">
+        <v>8000000</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>337</v>
+        <v>446</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>338</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>339</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>341</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>342</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>328</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>343</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>344</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>345</v>
+      <c r="A15" t="s" s="5">
+        <v>443</v>
+      </c>
+      <c r="B15" t="s" s="5">
+        <v>450</v>
+      </c>
+      <c r="C15" t="s" s="5">
+        <v>451</v>
+      </c>
+      <c r="D15" s="5">
+        <v>940</v>
+      </c>
+      <c r="E15" s="5">
+        <v>940</v>
+      </c>
+      <c r="F15" s="5">
+        <v>16000000</v>
+      </c>
+      <c r="G15" t="s" s="5">
+        <v>452</v>
+      </c>
+      <c r="H15" t="s" s="5">
+        <v>453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>348</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>349</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>350</v>
+        <v>451</v>
+      </c>
+      <c r="D16" s="0">
+        <v>190</v>
+      </c>
+      <c r="E16" s="0">
+        <v>190</v>
+      </c>
+      <c r="F16" s="0">
+        <v>3200000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>352</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>353</v>
+        <v>454</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>357</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>358</v>
+        <v>451</v>
+      </c>
+      <c r="D17" s="0">
+        <v>35</v>
+      </c>
+      <c r="E17" s="0">
+        <v>35</v>
+      </c>
+      <c r="F17" s="0">
+        <v>600000</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>359</v>
+        <v>459</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>360</v>
+        <v>460</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>361</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>362</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>363</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>364</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>365</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>366</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>367</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>368</v>
+      <c r="A18" t="s" s="5">
+        <v>454</v>
+      </c>
+      <c r="B18" t="s" s="5">
+        <v>461</v>
+      </c>
+      <c r="C18" t="s" s="5">
+        <v>451</v>
+      </c>
+      <c r="D18" s="5">
+        <v>225</v>
+      </c>
+      <c r="E18" s="5">
+        <v>225</v>
+      </c>
+      <c r="F18" s="5">
+        <v>3800000</v>
+      </c>
+      <c r="G18" t="s" s="5">
+        <v>462</v>
+      </c>
+      <c r="H18" t="s" s="5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>465</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="D19" s="0">
+        <v>1060</v>
+      </c>
+      <c r="E19" s="0">
+        <v>1060</v>
+      </c>
+      <c r="F19" s="0">
+        <v>18000000</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="D20" s="0">
+        <v>70</v>
+      </c>
+      <c r="E20" s="0">
+        <v>70</v>
+      </c>
+      <c r="F20" s="0">
+        <v>1200000</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="5">
+        <v>464</v>
+      </c>
+      <c r="B21" t="s" s="5">
+        <v>471</v>
+      </c>
+      <c r="C21" t="s" s="5">
+        <v>430</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1130</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1130</v>
+      </c>
+      <c r="F21" s="5">
+        <v>19200000</v>
+      </c>
+      <c r="G21" t="s" s="5">
+        <v>472</v>
+      </c>
+      <c r="H21" t="s" s="5">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>451</v>
+      </c>
+      <c r="D22" s="0">
+        <v>35</v>
+      </c>
+      <c r="E22" s="0">
+        <v>35</v>
+      </c>
+      <c r="F22" s="0">
+        <v>600000</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>476</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>478</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>479</v>
+      </c>
+      <c r="D23" s="0">
+        <v>140</v>
+      </c>
+      <c r="E23" s="0">
+        <v>140</v>
+      </c>
+      <c r="F23" s="0">
+        <v>2400000</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="5">
+        <v>474</v>
+      </c>
+      <c r="B24" t="s" s="5">
+        <v>482</v>
+      </c>
+      <c r="C24" t="s" s="5">
+        <v>430</v>
+      </c>
+      <c r="D24" s="5">
+        <v>175</v>
+      </c>
+      <c r="E24" s="5">
+        <v>175</v>
+      </c>
+      <c r="F24" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="G24" t="s" s="5">
+        <v>483</v>
+      </c>
+      <c r="H24" t="s" s="5">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0"/>
+      <c r="B25" s="0"/>
+      <c r="C25" s="0"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="7">
+        <v>485</v>
+      </c>
+      <c r="B26" t="s" s="7">
+        <v>486</v>
+      </c>
+      <c r="C26" t="s" s="7">
+        <v>430</v>
+      </c>
+      <c r="D26" s="7">
+        <v>3619</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3619</v>
+      </c>
+      <c r="F26" s="7">
+        <v>61500000</v>
+      </c>
+      <c r="G26" t="s" s="7">
+        <v>487</v>
+      </c>
+      <c r="H26" t="s" s="7">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="7">
+        <v>489</v>
+      </c>
+      <c r="B27" t="s" s="7">
+        <v>490</v>
+      </c>
+      <c r="C27" t="s" s="7">
+        <v>430</v>
+      </c>
+      <c r="D27" s="7">
+        <v>6369</v>
+      </c>
+      <c r="E27" s="7">
+        <v>6369</v>
+      </c>
+      <c r="F27" s="7">
+        <v>108250000</v>
+      </c>
+      <c r="G27" t="s" s="7">
+        <v>491</v>
+      </c>
+      <c r="H27" t="s" s="7">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>369</v>
+        <v>493</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3997,7 +5020,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>370</v>
+        <v>494</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4019,812 +5042,163 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>2</v>
+        <v>495</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>3</v>
+        <v>496</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>371</v>
+        <v>497</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>372</v>
+        <v>498</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>373</v>
+        <v>499</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>7</v>
+        <v>500</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>374</v>
+        <v>501</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>375</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>377</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>378</v>
+        <v>503</v>
+      </c>
+      <c r="B5" s="0">
+        <v>105</v>
+      </c>
+      <c r="C5" s="0">
+        <v>31</v>
       </c>
       <c r="D5" s="0">
-        <v>1050</v>
+        <v>1800000</v>
       </c>
       <c r="E5" s="0">
-        <v>3800</v>
-      </c>
-      <c r="F5" s="0">
-        <v>17850000</v>
+        <v>530000</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>504</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>379</v>
+        <v>505</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>380</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>381</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>378</v>
+        <v>507</v>
+      </c>
+      <c r="B6" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" s="0">
+        <v>12</v>
       </c>
       <c r="D6" s="0">
-        <v>1150</v>
+        <v>400000</v>
       </c>
       <c r="E6" s="0">
-        <v>4200</v>
-      </c>
-      <c r="F6" s="0">
-        <v>19550000</v>
+        <v>200000</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>508</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>382</v>
+        <v>509</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>383</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="9">
-        <v>376</v>
-      </c>
-      <c r="B7" t="s" s="9">
-        <v>384</v>
-      </c>
-      <c r="C7" t="s" s="9">
-        <v>378</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1100</v>
-      </c>
-      <c r="E7" s="9">
-        <v>4600</v>
-      </c>
-      <c r="F7" s="9">
-        <v>18700000</v>
-      </c>
-      <c r="G7" t="s" s="9">
-        <v>385</v>
-      </c>
-      <c r="H7" t="s" s="9">
-        <v>386</v>
+      <c r="A7" t="s" s="0">
+        <v>511</v>
+      </c>
+      <c r="B7" s="0">
+        <v>165</v>
+      </c>
+      <c r="C7" s="0">
+        <v>210</v>
+      </c>
+      <c r="D7" s="0">
+        <v>2800000</v>
+      </c>
+      <c r="E7" s="0">
+        <v>3600000</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>512</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>513</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>514</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="5">
-        <v>376</v>
-      </c>
-      <c r="B8" t="s" s="5">
-        <v>387</v>
-      </c>
-      <c r="C8" t="s" s="5">
-        <v>378</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1050</v>
-      </c>
-      <c r="E8" s="5">
-        <v>3800</v>
-      </c>
-      <c r="F8" s="5">
-        <v>17850000</v>
-      </c>
-      <c r="G8" t="s" s="5">
-        <v>388</v>
-      </c>
-      <c r="H8" t="s" s="5">
-        <v>389</v>
+      <c r="A8" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="B8" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" s="0">
+        <v>55</v>
+      </c>
+      <c r="D8" s="0">
+        <v>950000</v>
+      </c>
+      <c r="E8" s="0">
+        <v>950000</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>516</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>517</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>391</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>392</v>
+        <v>519</v>
+      </c>
+      <c r="B9" s="0">
+        <v>70</v>
+      </c>
+      <c r="C9" s="0">
+        <v>95</v>
       </c>
       <c r="D9" s="0">
-        <v>90</v>
+        <v>1200000</v>
       </c>
       <c r="E9" s="0">
-        <v>90</v>
-      </c>
-      <c r="F9" s="0">
-        <v>1500000</v>
+        <v>1600000</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>520</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>393</v>
+        <v>521</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>394</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>395</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>396</v>
-      </c>
-      <c r="D10" s="0">
-        <v>64</v>
-      </c>
-      <c r="E10" s="0">
-        <v>64</v>
-      </c>
-      <c r="F10" s="0">
-        <v>1000000</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>393</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>399</v>
-      </c>
-      <c r="D11" s="0">
-        <v>9</v>
-      </c>
-      <c r="E11" s="0">
-        <v>9</v>
-      </c>
-      <c r="F11" s="0">
-        <v>150000</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="5">
-        <v>390</v>
-      </c>
-      <c r="B12" t="s" s="5">
-        <v>402</v>
-      </c>
-      <c r="C12" t="s" s="5">
-        <v>392</v>
-      </c>
-      <c r="D12" s="5">
-        <v>99</v>
-      </c>
-      <c r="E12" s="5">
-        <v>99</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1650000</v>
-      </c>
-      <c r="G12" t="s" s="5">
-        <v>403</v>
-      </c>
-      <c r="H12" t="s" s="5">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>407</v>
-      </c>
-      <c r="D13" s="0">
-        <v>470</v>
-      </c>
-      <c r="E13" s="0">
-        <v>470</v>
-      </c>
-      <c r="F13" s="0">
-        <v>8000000</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>410</v>
-      </c>
-      <c r="D14" s="0">
-        <v>470</v>
-      </c>
-      <c r="E14" s="0">
-        <v>470</v>
-      </c>
-      <c r="F14" s="0">
-        <v>8000000</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="5">
-        <v>405</v>
-      </c>
-      <c r="B15" t="s" s="5">
-        <v>412</v>
-      </c>
-      <c r="C15" t="s" s="5">
-        <v>413</v>
-      </c>
-      <c r="D15" s="5">
-        <v>940</v>
-      </c>
-      <c r="E15" s="5">
-        <v>940</v>
-      </c>
-      <c r="F15" s="5">
-        <v>16000000</v>
-      </c>
-      <c r="G15" t="s" s="5">
-        <v>414</v>
-      </c>
-      <c r="H15" t="s" s="5">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>416</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>417</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>413</v>
-      </c>
-      <c r="D16" s="0">
-        <v>190</v>
-      </c>
-      <c r="E16" s="0">
-        <v>190</v>
-      </c>
-      <c r="F16" s="0">
-        <v>3200000</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>418</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>416</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>420</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>413</v>
-      </c>
-      <c r="D17" s="0">
-        <v>35</v>
-      </c>
-      <c r="E17" s="0">
-        <v>35</v>
-      </c>
-      <c r="F17" s="0">
-        <v>600000</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="5">
-        <v>416</v>
-      </c>
-      <c r="B18" t="s" s="5">
-        <v>423</v>
-      </c>
-      <c r="C18" t="s" s="5">
-        <v>413</v>
-      </c>
-      <c r="D18" s="5">
-        <v>225</v>
-      </c>
-      <c r="E18" s="5">
-        <v>225</v>
-      </c>
-      <c r="F18" s="5">
-        <v>3800000</v>
-      </c>
-      <c r="G18" t="s" s="5">
-        <v>424</v>
-      </c>
-      <c r="H18" t="s" s="5">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>427</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>392</v>
-      </c>
-      <c r="D19" s="0">
-        <v>1060</v>
-      </c>
-      <c r="E19" s="0">
-        <v>1060</v>
-      </c>
-      <c r="F19" s="0">
-        <v>18000000</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>430</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>392</v>
-      </c>
-      <c r="D20" s="0">
-        <v>70</v>
-      </c>
-      <c r="E20" s="0">
-        <v>70</v>
-      </c>
-      <c r="F20" s="0">
-        <v>1200000</v>
-      </c>
-      <c r="G20" t="s" s="0">
-        <v>431</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="5">
-        <v>426</v>
-      </c>
-      <c r="B21" t="s" s="5">
-        <v>433</v>
-      </c>
-      <c r="C21" t="s" s="5">
-        <v>392</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1130</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1130</v>
-      </c>
-      <c r="F21" s="5">
-        <v>19200000</v>
-      </c>
-      <c r="G21" t="s" s="5">
-        <v>434</v>
-      </c>
-      <c r="H21" t="s" s="5">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>437</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>413</v>
-      </c>
-      <c r="D22" s="0">
-        <v>35</v>
-      </c>
-      <c r="E22" s="0">
-        <v>35</v>
-      </c>
-      <c r="F22" s="0">
-        <v>600000</v>
-      </c>
-      <c r="G22" t="s" s="0">
-        <v>438</v>
-      </c>
-      <c r="H22" t="s" s="0">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>436</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="D23" s="0">
-        <v>140</v>
-      </c>
-      <c r="E23" s="0">
-        <v>140</v>
-      </c>
-      <c r="F23" s="0">
-        <v>2400000</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>442</v>
-      </c>
-      <c r="H23" t="s" s="0">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="5">
-        <v>436</v>
-      </c>
-      <c r="B24" t="s" s="5">
-        <v>444</v>
-      </c>
-      <c r="C24" t="s" s="5">
-        <v>392</v>
-      </c>
-      <c r="D24" s="5">
-        <v>175</v>
-      </c>
-      <c r="E24" s="5">
-        <v>175</v>
-      </c>
-      <c r="F24" s="5">
-        <v>3000000</v>
-      </c>
-      <c r="G24" t="s" s="5">
-        <v>445</v>
-      </c>
-      <c r="H24" t="s" s="5">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="7">
-        <v>447</v>
-      </c>
-      <c r="B26" t="s" s="7">
-        <v>448</v>
-      </c>
-      <c r="C26" t="s" s="7">
-        <v>392</v>
-      </c>
-      <c r="D26" s="7">
-        <v>3619</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3619</v>
-      </c>
-      <c r="F26" s="7">
-        <v>61500000</v>
-      </c>
-      <c r="G26" t="s" s="7">
-        <v>449</v>
-      </c>
-      <c r="H26" t="s" s="7">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="7">
-        <v>451</v>
-      </c>
-      <c r="B27" t="s" s="7">
-        <v>452</v>
-      </c>
-      <c r="C27" t="s" s="7">
-        <v>392</v>
-      </c>
-      <c r="D27" s="7">
-        <v>6369</v>
-      </c>
-      <c r="E27" s="7">
-        <v>6369</v>
-      </c>
-      <c r="F27" s="7">
-        <v>108250000</v>
-      </c>
-      <c r="G27" t="s" s="7">
-        <v>453</v>
-      </c>
-      <c r="H27" t="s" s="7">
-        <v>454</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="8">
-        <v>456</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-      <c r="B3" s="0"/>
-      <c r="C3" s="0"/>
-      <c r="D3" s="0"/>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="1">
-        <v>457</v>
-      </c>
-      <c r="B4" t="s" s="1">
-        <v>458</v>
-      </c>
-      <c r="C4" t="s" s="1">
-        <v>459</v>
-      </c>
-      <c r="D4" t="s" s="1">
-        <v>460</v>
-      </c>
-      <c r="E4" t="s" s="1">
-        <v>461</v>
-      </c>
-      <c r="F4" t="s" s="1">
-        <v>462</v>
-      </c>
-      <c r="G4" t="s" s="1">
-        <v>463</v>
-      </c>
-      <c r="H4" t="s" s="1">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="B5" s="0">
-        <v>105</v>
-      </c>
-      <c r="C5" s="0">
-        <v>31</v>
-      </c>
-      <c r="D5" s="0">
-        <v>1800000</v>
-      </c>
-      <c r="E5" s="0">
-        <v>530000</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>466</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>467</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>469</v>
-      </c>
-      <c r="B6" s="0">
-        <v>25</v>
-      </c>
-      <c r="C6" s="0">
-        <v>12</v>
-      </c>
-      <c r="D6" s="0">
-        <v>400000</v>
-      </c>
-      <c r="E6" s="0">
-        <v>200000</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>470</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>471</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>473</v>
-      </c>
-      <c r="B7" s="0">
-        <v>165</v>
-      </c>
-      <c r="C7" s="0">
-        <v>210</v>
-      </c>
-      <c r="D7" s="0">
-        <v>2800000</v>
-      </c>
-      <c r="E7" s="0">
-        <v>3600000</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>474</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>475</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>477</v>
-      </c>
-      <c r="B8" s="0">
-        <v>55</v>
-      </c>
-      <c r="C8" s="0">
-        <v>55</v>
-      </c>
-      <c r="D8" s="0">
-        <v>950000</v>
-      </c>
-      <c r="E8" s="0">
-        <v>950000</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>478</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>479</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>481</v>
-      </c>
-      <c r="B9" s="0">
-        <v>70</v>
-      </c>
-      <c r="C9" s="0">
-        <v>95</v>
-      </c>
-      <c r="D9" s="0">
-        <v>1200000</v>
-      </c>
-      <c r="E9" s="0">
-        <v>1600000</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>482</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>483</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>485</v>
+        <v>523</v>
       </c>
       <c r="B10" s="0">
         <v>40</v>
@@ -4839,13 +5213,13 @@
         <v>700000</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>488</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11">
@@ -4860,7 +5234,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="7">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="B12" s="7">
         <v>460</v>
@@ -4875,13 +5249,13 @@
         <v>7580000</v>
       </c>
       <c r="F12" t="s" s="7">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="G12" t="s" s="7">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="H12" t="s" s="7">
-        <v>492</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13">
@@ -4896,7 +5270,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4908,7 +5282,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="4">
-        <v>494</v>
+        <v>532</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -4920,7 +5294,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4932,7 +5306,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>496</v>
+        <v>534</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4944,7 +5318,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4956,7 +5330,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>

--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
@@ -36,345 +36,348 @@
     <t>Актуально (Швейцария, 4★) [€]</t>
   </si>
   <si>
+    <t>Стоимость in IDR</t>
+  </si>
+  <si>
+    <t>Разница / Экономия [€]</t>
+  </si>
+  <si>
+    <t>Официальный источник / Ссылка</t>
+  </si>
+  <si>
+    <t>1. Размещение</t>
+  </si>
+  <si>
+    <t>Убуд: Plataran Ubud Hotel &amp; Spa (Deluxe Suite, 320 €/н) vs The Kayon Jungle (850 €/н)</t>
+  </si>
+  <si>
+    <t>3 ночи</t>
+  </si>
+  <si>
+    <t>-1 590 € (экономия)</t>
+  </si>
+  <si>
+    <t>plataran.com/plataran-ubud</t>
+  </si>
+  <si>
+    <t>Кинтамани: Toteme Glamping &amp; Hot Springs (Шатер с купелью, 220 €) vs Faro Cabin (350 €)</t>
+  </si>
+  <si>
+    <t>1 ночь</t>
+  </si>
+  <si>
+    <t>-130 € (экономия)</t>
+  </si>
+  <si>
+    <t>totemeglamping.com</t>
+  </si>
+  <si>
+    <t>Побережье: Приватная вилла у пляжа (Paradise Beach / Санур, 340 €/н) vs Bulgari / Six Senses (1 000 €/н)</t>
+  </si>
+  <si>
+    <t>2 ночи</t>
+  </si>
+  <si>
+    <t>-1 320 € (экономия)</t>
+  </si>
+  <si>
+    <t>Приватная бутик-вилла на первой линии</t>
+  </si>
+  <si>
+    <t>ИТОГО ПРОЖИВАНИЕ (6 ночей, средняя 310 €/ночь против 815 €/ночь)</t>
+  </si>
+  <si>
+    <t>6 ночей</t>
+  </si>
+  <si>
+    <t>-3 040 € (экономия)</t>
+  </si>
+  <si>
+    <t>Экономия перенаправлена в маржу</t>
+  </si>
+  <si>
+    <t>2. Логистика и авто</t>
+  </si>
+  <si>
+    <t>Личный водитель Путу &amp; Toyota Innova Zenix 24/7 (с бензином и ожиданием)</t>
+  </si>
+  <si>
+    <t>7 дней</t>
+  </si>
+  <si>
+    <t>-110 € (выгодный тариф)</t>
+  </si>
+  <si>
+    <t>1 100 000 IDR/день (Путу WhatsApp)</t>
+  </si>
+  <si>
+    <t>Встречи/проводы, ночные переезды, парковки, платные хайвеи Bali Mandara</t>
+  </si>
+  <si>
+    <t>+10 €</t>
+  </si>
+  <si>
+    <t>Фактические дорожные сборы</t>
+  </si>
+  <si>
+    <t>ИТОГО ТРАНСПОРТ И ПУТУ НА ВЕСЬ МАРШРУТ</t>
+  </si>
+  <si>
+    <t>-100 € (экономия)</t>
+  </si>
+  <si>
+    <t>100% готовность и безопасность</t>
+  </si>
+  <si>
+    <t>3. VIP Аэропорт и въезд</t>
+  </si>
+  <si>
+    <t>VIP Fast-Track (JOUMPA Garuda): Meet &amp; Greet у трапа, дип-коридор, портье багажа, VIP Lounge</t>
+  </si>
+  <si>
+    <t>2 чел</t>
+  </si>
+  <si>
+    <t>+110 € (полный VIP)</t>
+  </si>
+  <si>
+    <t>joumpa.com (80 €/чел за полный VIP)</t>
+  </si>
+  <si>
+    <t>Электронная виза e-VOA B1 (официальный портал Иммиграции)</t>
+  </si>
+  <si>
+    <t>+4 € (курс)</t>
+  </si>
+  <si>
+    <t>evisa.imigrasi.go.id (500 000 IDR/чел)</t>
+  </si>
+  <si>
+    <t>Официальный туристический сбор Бали (Love Bali Tourist Levy)</t>
+  </si>
+  <si>
+    <t>0 €</t>
+  </si>
+  <si>
+    <t>lovebali.baliprov.go.id (150 000 IDR/чел)</t>
+  </si>
+  <si>
+    <t>ИТОГО ВЪЕЗДНЫЕ СБОРЫ И VIP ПРИЛЕТ (ВКЛЮЧАЯ ПОРТЬЕ И ЛАУНЖ)</t>
+  </si>
+  <si>
+    <t>+114 € (премиум комфорт)</t>
+  </si>
+  <si>
+    <t>Оформляется организатором заранее</t>
+  </si>
+  <si>
+    <t>4. Спа и релаксация</t>
+  </si>
+  <si>
+    <t>3-часовой ритуал: ванна из роз, скраб Lulur, травяной уход (Padma Spa Plataran)</t>
+  </si>
+  <si>
+    <t>-10 €</t>
+  </si>
+  <si>
+    <t>Фирменный спа Plataran</t>
+  </si>
+  <si>
+    <t>Восстанавливающие балийские массажи и релакс-терапия</t>
+  </si>
+  <si>
+    <t>2 чел х 2 раза</t>
+  </si>
+  <si>
+    <t>+50 €</t>
+  </si>
+  <si>
+    <t>Сертифицированные мастера</t>
+  </si>
+  <si>
+    <t>ИТОГО СПА-ПРОГРАММА</t>
+  </si>
+  <si>
+    <t>Комплекс</t>
+  </si>
+  <si>
+    <t>+40 €</t>
+  </si>
+  <si>
+    <t>Глубокая телесная перезагрузка</t>
+  </si>
+  <si>
+    <t>5. Места Силы &amp; Обряды</t>
+  </si>
+  <si>
+    <t>Церемония Мелукат у священника Манку + подношения (каньон Себату)</t>
+  </si>
+  <si>
+    <t>-15 €</t>
+  </si>
+  <si>
+    <t>Скрытый водопад Genah Melukat</t>
+  </si>
+  <si>
+    <t>Агни-хотра (огненная ведическая пуджа) с потомственным священником</t>
+  </si>
+  <si>
+    <t>Сессия</t>
+  </si>
+  <si>
+    <t>+20 €</t>
+  </si>
+  <si>
+    <t>Индивидуальный сакральный обряд</t>
+  </si>
+  <si>
+    <t>Билеты в храмы: Бесаких, Батукару, Себату, термы Батур, Ботанический сад</t>
+  </si>
+  <si>
+    <t>Входные билеты, саронги, шаттлы</t>
+  </si>
+  <si>
+    <t>ИТОГО САКРАЛЬНАЯ ПРОГРАММА</t>
+  </si>
+  <si>
+    <t>+15 €</t>
+  </si>
+  <si>
+    <t>Закрытый доступ без толп туристов</t>
+  </si>
+  <si>
+    <t>6. Гастрономия</t>
+  </si>
+  <si>
+    <t>Приветственный ужин на вилле + тропические фрукты ежедневно (мангостины, маракуйя)</t>
+  </si>
+  <si>
+    <t>Ежедневная свежая экзотика</t>
+  </si>
+  <si>
+    <t>Авторский дегустационный сет от шефа (Mozaic / Locavore NXT)</t>
+  </si>
+  <si>
+    <t>Гастрономический флагман Азии</t>
+  </si>
+  <si>
+    <t>Праздничный закатный ужин морепродуктов на берегу океана (Санур)</t>
+  </si>
+  <si>
+    <t>Свежий улов дня у самой воды</t>
+  </si>
+  <si>
+    <t>ИТОГО ПИТАНИЕ И НАПИТКИ</t>
+  </si>
+  <si>
+    <t>Отобранные шеф-локации</t>
+  </si>
+  <si>
+    <t>7. Проводник &amp; Арт</t>
+  </si>
+  <si>
+    <t>Звукотерапия тибетскими чашами от Валерия на вилле (2 сессии)</t>
+  </si>
+  <si>
+    <t>2 сессии</t>
+  </si>
+  <si>
+    <t>Включено</t>
+  </si>
+  <si>
+    <t>Авторская практика мастера</t>
+  </si>
+  <si>
+    <t>Авторская fine-art портретная фотосъемка на закатном побережье</t>
+  </si>
+  <si>
+    <t>1 сессия</t>
+  </si>
+  <si>
+    <t>Fine-art фотосессия для гостий от Валерия</t>
+  </si>
+  <si>
+    <t>Интеллектуальный салон: встреча с д-ром Лоуренсом Блэром («Ring of Fire»)</t>
+  </si>
+  <si>
+    <t>1 встреча</t>
+  </si>
+  <si>
+    <t>Эксклюзивный доступ автора (35 лет экспедиций)</t>
+  </si>
+  <si>
+    <t>Частный визит в резиденцию Брюса Карпентера (сакральные крисы и маски)</t>
+  </si>
+  <si>
+    <t>1 визит</t>
+  </si>
+  <si>
+    <t>Эксперт Christie's / автор монографий</t>
+  </si>
+  <si>
+    <t>Арт-маршрут Убуда: музей Бланко, Neka Art Museum (павильон крисов), ARMA</t>
+  </si>
+  <si>
+    <t>1 день</t>
+  </si>
+  <si>
+    <t>Билеты включены в общую сакральную программу</t>
+  </si>
+  <si>
+    <t>Непрерывное кураторство 24/7 (индонезийский и английский языки)</t>
+  </si>
+  <si>
+    <t>Личное ведение без посредников</t>
+  </si>
+  <si>
+    <t>ИТОГО ОПЕРАЦИОННАЯ СЕБЕСТОИМОСТЬ (40%)</t>
+  </si>
+  <si>
+    <t>Прямые расходы на 2 гостей (отели 4★+, авто, спа, храмы, еда, VIP)</t>
+  </si>
+  <si>
+    <t>-2 388 € (чистая экономия)</t>
+  </si>
+  <si>
+    <t>40% от общей суммы пакета</t>
+  </si>
+  <si>
+    <t>ГОНОРАР МАСТЕРА ВАЛЕРИЯ ЛАТЫПОВА (60%)</t>
+  </si>
+  <si>
+    <t>Чистый гонорар за организацию, режиссуру тура и личное ведение</t>
+  </si>
+  <si>
+    <t>+4 688 € (рост гонорара)</t>
+  </si>
+  <si>
+    <t>60% чистая маржа автора</t>
+  </si>
+  <si>
+    <t>ИТОГОВАЯ СТОИМОСТЬ ПАКЕТА (ДЛЯ 2 ГОСТЕЙ)</t>
+  </si>
+  <si>
+    <t>Полный пакет «под ключ» (без международных авиабилетов)</t>
+  </si>
+  <si>
+    <t>+2 300 € (премиум Швейцария)</t>
+  </si>
+  <si>
+    <t>12 000 € за тур на двоих</t>
+  </si>
+  <si>
+    <t>СМЕТА ТУРА «BALI SANCTUARY»: 5 ДНЕЙ / 4 НОЧИ (ГОСТЬИ ИЗ ШВЕЙЦАРИИ)</t>
+  </si>
+  <si>
+    <t>Камерные бутик-отели 4★+ (300–400 €/ночь) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
+  </si>
+  <si>
+    <t>Базовый расчет 5★ [€]</t>
+  </si>
+  <si>
     <t>Стоимость в IDR</t>
   </si>
   <si>
-    <t>Разница / Экономия [€]</t>
-  </si>
-  <si>
-    <t>Официальный источник / Ссылка</t>
-  </si>
-  <si>
-    <t>1. Размещение</t>
-  </si>
-  <si>
-    <t>Убуд: Plataran Ubud Hotel &amp; Spa (Deluxe Suite, 320 €/н) vs The Kayon Jungle (850 €/н)</t>
-  </si>
-  <si>
-    <t>3 ночи</t>
-  </si>
-  <si>
-    <t>-1 590 € (экономия)</t>
-  </si>
-  <si>
-    <t>plataran.com/plataran-ubud</t>
-  </si>
-  <si>
-    <t>Кинтамани: Toteme Glamping &amp; Hot Springs (Шатер с купелью, 220 €) vs Faro Cabin (350 €)</t>
-  </si>
-  <si>
-    <t>1 ночь</t>
-  </si>
-  <si>
-    <t>-130 € (экономия)</t>
-  </si>
-  <si>
-    <t>totemeglamping.com</t>
-  </si>
-  <si>
-    <t>Улувату: Renaissance Uluwatu (Ocean Suite, 340 €/н) vs Bulgari / Six Senses (1 000 €/н)</t>
-  </si>
-  <si>
-    <t>2 ночи</t>
-  </si>
-  <si>
-    <t>-1 320 € (экономия)</t>
-  </si>
-  <si>
-    <t>marriott.com/renaissance-bali</t>
-  </si>
-  <si>
-    <t>ИТОГО ПРОЖИВАНИЕ (6 ночей, средняя 310 €/ночь против 815 €/ночь)</t>
-  </si>
-  <si>
-    <t>6 ночей</t>
-  </si>
-  <si>
-    <t>-3 040 € (экономия)</t>
-  </si>
-  <si>
-    <t>Экономия перенаправлена в маржу</t>
-  </si>
-  <si>
-    <t>2. Логистика и авто</t>
-  </si>
-  <si>
-    <t>Личный водитель Путу &amp; Toyota Innova Zenix 24/7 (с бензином и ожиданием)</t>
-  </si>
-  <si>
-    <t>7 дней</t>
-  </si>
-  <si>
-    <t>-110 € (выгодный тариф)</t>
-  </si>
-  <si>
-    <t>1 100 000 IDR/день (Путу WhatsApp)</t>
-  </si>
-  <si>
-    <t>Встречи/проводы, ночные переезды, парковки, платные хайвеи Bali Mandara</t>
-  </si>
-  <si>
-    <t>+10 €</t>
-  </si>
-  <si>
-    <t>Фактические дорожные сборы</t>
-  </si>
-  <si>
-    <t>ИТОГО ТРАНСПОРТ И ПУТУ НА ВЕСЬ МАРШРУТ</t>
-  </si>
-  <si>
-    <t>-100 € (экономия)</t>
-  </si>
-  <si>
-    <t>100% готовность и безопасность</t>
-  </si>
-  <si>
-    <t>3. VIP Аэропорт и въезд</t>
-  </si>
-  <si>
-    <t>VIP Fast-Track (JOUMPA Garuda): Meet &amp; Greet у трапа, дип-коридор, портье багажа, VIP Lounge</t>
-  </si>
-  <si>
-    <t>2 чел</t>
-  </si>
-  <si>
-    <t>+110 € (полный VIP)</t>
-  </si>
-  <si>
-    <t>joumpa.com (80 €/чел за полный VIP)</t>
-  </si>
-  <si>
-    <t>Электронная виза e-VOA B1 (официальный портал Иммиграции)</t>
-  </si>
-  <si>
-    <t>+4 € (курс)</t>
-  </si>
-  <si>
-    <t>evisa.imigrasi.go.id (500 000 IDR/чел)</t>
-  </si>
-  <si>
-    <t>Официальный туристический сбор Бали (Love Bali Tourist Levy)</t>
-  </si>
-  <si>
-    <t>0 €</t>
-  </si>
-  <si>
-    <t>lovebali.baliprov.go.id (150 000 IDR/чел)</t>
-  </si>
-  <si>
-    <t>ИТОГО ВЪЕЗДНЫЕ СБОРЫ И VIP ПРИЛЕТ (ВКЛЮЧАЯ ПОРТЬЕ И ЛАУНЖ)</t>
-  </si>
-  <si>
-    <t>+114 € (премиум комфорт)</t>
-  </si>
-  <si>
-    <t>Оформляется организатором заранее</t>
-  </si>
-  <si>
-    <t>4. Спа и релаксация</t>
-  </si>
-  <si>
-    <t>3-часовой ритуал: ванна из роз, скраб Lulur, травяной уход (Padma Spa Plataran)</t>
-  </si>
-  <si>
-    <t>-10 €</t>
-  </si>
-  <si>
-    <t>Фирменный спа Plataran</t>
-  </si>
-  <si>
-    <t>Восстанавливающие балийские массажи и релакс-терапия</t>
-  </si>
-  <si>
-    <t>2 чел х 2 раза</t>
-  </si>
-  <si>
-    <t>+50 €</t>
-  </si>
-  <si>
-    <t>Сертифицированные мастера</t>
-  </si>
-  <si>
-    <t>ИТОГО СПА-ПРОГРАММА</t>
-  </si>
-  <si>
-    <t>Комплекс</t>
-  </si>
-  <si>
-    <t>+40 €</t>
-  </si>
-  <si>
-    <t>Глубокая телесная перезагрузка</t>
-  </si>
-  <si>
-    <t>5. Места Силы &amp; Обряды</t>
-  </si>
-  <si>
-    <t>Церемония Мелукат у священника Манку + подношения (каньон Себату)</t>
-  </si>
-  <si>
-    <t>-15 €</t>
-  </si>
-  <si>
-    <t>Скрытый водопад Genah Melukat</t>
-  </si>
-  <si>
-    <t>Агни-хотра (огненная ведическая пуджа) с потомственным священником</t>
-  </si>
-  <si>
-    <t>Сессия</t>
-  </si>
-  <si>
-    <t>+20 €</t>
-  </si>
-  <si>
-    <t>Индивидуальный сакральный обряд</t>
-  </si>
-  <si>
-    <t>Билеты в храмы: Бесаких, Батукару, Себату, термы Батур, Ботанический сад</t>
-  </si>
-  <si>
-    <t>Входные билеты, саронги, шаттлы</t>
-  </si>
-  <si>
-    <t>ИТОГО САКРАЛЬНАЯ ПРОГРАММА</t>
-  </si>
-  <si>
-    <t>+15 €</t>
-  </si>
-  <si>
-    <t>Закрытый доступ без толп туристов</t>
-  </si>
-  <si>
-    <t>6. Гастрономия</t>
-  </si>
-  <si>
-    <t>Приветственный ужин на вилле + тропические фрукты ежедневно (мангостины, маракуйя)</t>
-  </si>
-  <si>
-    <t>Ежедневная свежая экзотика</t>
-  </si>
-  <si>
-    <t>Авторский дегустационный сет от шефа (Mozaic / Locavore NXT)</t>
-  </si>
-  <si>
-    <t>Гастрономический флагман Азии</t>
-  </si>
-  <si>
-    <t>Панорамный закатный ужин морепродуктов на утесах Улувату</t>
-  </si>
-  <si>
-    <t>Океанский вид и свежий улов</t>
-  </si>
-  <si>
-    <t>ИТОГО ПИТАНИЕ И НАПИТКИ</t>
-  </si>
-  <si>
-    <t>Отобранные шеф-локации</t>
-  </si>
-  <si>
-    <t>7. Проводник &amp; Арт</t>
-  </si>
-  <si>
-    <t>Звукотерапия тибетскими чашами от Валерия на вилле (2 сессии)</t>
-  </si>
-  <si>
-    <t>2 сессии</t>
-  </si>
-  <si>
-    <t>Включено</t>
-  </si>
-  <si>
-    <t>Авторская практика мастера</t>
-  </si>
-  <si>
-    <t>Алхимическая портретная фотосъемка на утесах Улувату</t>
-  </si>
-  <si>
-    <t>1 сессия</t>
-  </si>
-  <si>
-    <t>Fine-art фотосессия для гостий</t>
-  </si>
-  <si>
-    <t>Интеллектуальный салон: встреча с д-ром Лоуренсом Блэром («Ring of Fire»)</t>
-  </si>
-  <si>
-    <t>1 встреча</t>
-  </si>
-  <si>
-    <t>Эксклюзивный доступ автора (35 лет экспедиций)</t>
-  </si>
-  <si>
-    <t>Частный визит в резиденцию Брюса Карпентера (сакральные крисы и маски)</t>
-  </si>
-  <si>
-    <t>1 визит</t>
-  </si>
-  <si>
-    <t>Эксперт Christie's / автор монографий</t>
-  </si>
-  <si>
-    <t>Арт-маршрут Убуда: музей Бланко, Neka Art Museum (павильон крисов), ARMA</t>
-  </si>
-  <si>
-    <t>1 день</t>
-  </si>
-  <si>
-    <t>Билеты включены в общую сакральную программу</t>
-  </si>
-  <si>
-    <t>Непрерывное кураторство 24/7 (индонезийский и английский языки)</t>
-  </si>
-  <si>
-    <t>Личное ведение без посредников</t>
-  </si>
-  <si>
-    <t>ИТОГО ОПЕРАЦИОННАЯ СЕБЕСТОИМОСТЬ (40%)</t>
-  </si>
-  <si>
-    <t>Прямые расходы на 2 гостей (отели 4★+, авто, спа, храмы, еда, VIP)</t>
-  </si>
-  <si>
-    <t>-2 388 € (чистая экономия)</t>
-  </si>
-  <si>
-    <t>40% от общей суммы пакета</t>
-  </si>
-  <si>
-    <t>ГОНОРАР МАСТЕРА ВАЛЕРИЯ ЛАТЫПОВА (60%)</t>
-  </si>
-  <si>
-    <t>Чистый гонорар за организацию, режиссуру тура и личное ведение</t>
-  </si>
-  <si>
-    <t>+4 688 € (рост гонорара)</t>
-  </si>
-  <si>
-    <t>60% чистая маржа автора</t>
-  </si>
-  <si>
-    <t>ИТОГОВАЯ СТОИМОСТЬ ПАКЕТА (ДЛЯ 2 ГОСТЕЙ)</t>
-  </si>
-  <si>
-    <t>Полный пакет «под ключ» (без международных авиабилетов)</t>
-  </si>
-  <si>
-    <t>+2 300 € (премиум Швейцария)</t>
-  </si>
-  <si>
-    <t>12 000 € за тур на двоих</t>
-  </si>
-  <si>
-    <t>СМЕТА ТУРА «BALI SANCTUARY»: 5 ДНЕЙ / 4 НОЧИ (ГОСТЬИ ИЗ ШВЕЙЦАРИИ)</t>
-  </si>
-  <si>
-    <t>Камерные бутик-отели 4★+ (300–400 €/ночь) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
-  </si>
-  <si>
-    <t>Базовый расчет 5★ [€]</t>
-  </si>
-  <si>
     <t>Структура расходов</t>
   </si>
   <si>
@@ -390,13 +393,13 @@
     <t>plataran.com/plataran-ubud (320 €/н)</t>
   </si>
   <si>
-    <t>Renaissance Bali Uluwatu Resort (Ocean View Suite)</t>
+    <t>Приватная вилла у океана (Paradise Beach / Санур, 1-я линия)</t>
   </si>
   <si>
     <t>20.0% от бюджета</t>
   </si>
   <si>
-    <t>marriott.com (340 €/н)</t>
+    <t>Бутик-вилла у лагуны (340 €/н)</t>
   </si>
   <si>
     <t>Итого проживание (4 ночи, в пределах 300–400 €/ночь)</t>
@@ -522,13 +525,13 @@
     <t>Mozaic / Locavore NXT</t>
   </si>
   <si>
-    <t>Закатный панорамный ужин на скалах Улувату</t>
+    <t>Закатный праздничный ужин морепродуктов у океана (Санур)</t>
   </si>
   <si>
     <t>Морепродукты</t>
   </si>
   <si>
-    <t>Свежий улов и закат</t>
+    <t>Свежий улов и закат у воды</t>
   </si>
   <si>
     <t>Итого питание и напитки</t>
@@ -765,10 +768,10 @@
     <t>Выбрать премиум-шатер с индивидуальной геотермальной минеральной ванной на террасе. Заказать растопку купели к моменту заезда (17:00).</t>
   </si>
   <si>
-    <t>8. Отель Renaissance Uluwatu 4★+</t>
-  </si>
-  <si>
-    <t>https://www.marriott.com</t>
+    <t>8. Приватная вилла у пляжа (Санур)</t>
+  </si>
+  <si>
+    <t>Прямой контракт / Букинг виллы</t>
   </si>
   <si>
     <t>Имена гостей, даты проживания (2 ночи)</t>
@@ -777,13 +780,13 @@
     <t>5 800 000 IDR/ночь (~340 €/н)</t>
   </si>
   <si>
-    <t>Картой на официальном сайте Marriott</t>
-  </si>
-  <si>
-    <t>Подтверждение Ocean View Suite</t>
-  </si>
-  <si>
-    <t>Забронировать люкс с панорамным видом на Индийский океан. Запросить высокий этаж и поздний выезд (Late Check-out) при необходимости.</t>
+    <t>Предоплата картой или банковский перевод</t>
+  </si>
+  <si>
+    <t>Подтверждение приватной пляжной виллы</t>
+  </si>
+  <si>
+    <t>Забронировать виллу на первой линии с приватным садом и прямым выходом к спокойной лагуне для купания без волн.</t>
   </si>
   <si>
     <t>9. Ресторан Mozaic Gastronomic (Убуд)</t>
@@ -1008,10 +1011,10 @@
     <t>Вулканические горячие источники 38-40°C</t>
   </si>
   <si>
-    <t>Отель Renaissance Uluwatu 4★+</t>
-  </si>
-  <si>
-    <t>Marriott International</t>
+    <t>Приватная вилла у пляжа (Санур)</t>
+  </si>
+  <si>
+    <t>Бутик-коллекция Sanur Beachfront</t>
   </si>
   <si>
     <t>5 800 000 IDR/ночь</t>
@@ -1020,13 +1023,16 @@
     <t>340 €/ночь</t>
   </si>
   <si>
-    <t>Ocean View Suite на утесе + завтраки</t>
-  </si>
-  <si>
-    <t>Marriott Bonvoy / Прямой сайт</t>
-  </si>
-  <si>
-    <t>Панорамный бассейн над океаном</t>
+    <t>Бутик-вилла у кромки воды</t>
+  </si>
+  <si>
+    <t>Вилла с садом у лагуны + завтраки от шефа</t>
+  </si>
+  <si>
+    <t>Прямой контракт / Депозит</t>
+  </si>
+  <si>
+    <t>Тихий океан без волн, 20 мин до аэропорта DPS</t>
   </si>
   <si>
     <t>Храм Пура Бесаких</t>
@@ -2715,10 +2721,10 @@
         <v>6</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H4" t="s" s="1">
         <v>9</v>
@@ -2726,10 +2732,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>20</v>
@@ -2744,18 +2750,18 @@
         <v>11000000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>20</v>
@@ -2770,21 +2776,21 @@
         <v>11600000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="5">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s" s="5">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" s="5">
         <v>3700</v>
@@ -2796,10 +2802,10 @@
         <v>22600000</v>
       </c>
       <c r="G7" t="s" s="5">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s" s="5">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -2807,10 +2813,10 @@
         <v>27</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="0">
         <v>400</v>
@@ -2822,10 +2828,10 @@
         <v>5500000</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
@@ -2833,10 +2839,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D9" s="0">
         <v>100</v>
@@ -2848,10 +2854,10 @@
         <v>1800000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -2859,10 +2865,10 @@
         <v>27</v>
       </c>
       <c r="B10" t="s" s="5">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s" s="5">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" s="5">
         <v>500</v>
@@ -2874,7 +2880,7 @@
         <v>7300000</v>
       </c>
       <c r="G10" t="s" s="5">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H10" t="s" s="5">
         <v>37</v>
@@ -2885,7 +2891,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>40</v>
@@ -2900,10 +2906,10 @@
         <v>2700000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -2926,7 +2932,7 @@
         <v>1000000</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>45</v>
@@ -2952,7 +2958,7 @@
         <v>300000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>48</v>
@@ -2963,7 +2969,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s" s="5">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s" s="5">
         <v>40</v>
@@ -2978,7 +2984,7 @@
         <v>4000000</v>
       </c>
       <c r="G14" t="s" s="5">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H14" t="s" s="5">
         <v>51</v>
@@ -2986,10 +2992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>40</v>
@@ -3004,7 +3010,7 @@
         <v>3200000</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>55</v>
@@ -3012,10 +3018,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>40</v>
@@ -3030,7 +3036,7 @@
         <v>1700000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>59</v>
@@ -3038,10 +3044,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="5">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s" s="5">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s" s="5">
         <v>61</v>
@@ -3056,7 +3062,7 @@
         <v>4900000</v>
       </c>
       <c r="G17" t="s" s="5">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H17" t="s" s="5">
         <v>63</v>
@@ -3067,7 +3073,7 @@
         <v>64</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>40</v>
@@ -3082,7 +3088,7 @@
         <v>1800000</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>67</v>
@@ -3093,7 +3099,7 @@
         <v>64</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>40</v>
@@ -3108,10 +3114,10 @@
         <v>850000</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
@@ -3119,7 +3125,7 @@
         <v>64</v>
       </c>
       <c r="B20" t="s" s="5">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s" s="5">
         <v>61</v>
@@ -3134,10 +3140,10 @@
         <v>2650000</v>
       </c>
       <c r="G20" t="s" s="5">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H20" t="s" s="5">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21">
@@ -3145,10 +3151,10 @@
         <v>77</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D21" s="0">
         <v>150</v>
@@ -3160,10 +3166,10 @@
         <v>2550000</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22">
@@ -3171,7 +3177,7 @@
         <v>77</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>40</v>
@@ -3186,10 +3192,10 @@
         <v>4250000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23">
@@ -3197,7 +3203,7 @@
         <v>77</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>40</v>
@@ -3212,10 +3218,10 @@
         <v>3400000</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24">
@@ -3223,7 +3229,7 @@
         <v>77</v>
       </c>
       <c r="B24" t="s" s="5">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="5">
         <v>61</v>
@@ -3238,7 +3244,7 @@
         <v>10200000</v>
       </c>
       <c r="G24" t="s" s="5">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s" s="5">
         <v>85</v>
@@ -3249,7 +3255,7 @@
         <v>86</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>92</v>
@@ -3353,10 +3359,10 @@
         <v>86</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="0">
         <v>0</v>
@@ -3389,10 +3395,10 @@
         <v>105</v>
       </c>
       <c r="B31" t="s" s="3">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s" s="3">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3">
         <v>5398</v>
@@ -3404,7 +3410,7 @@
         <v>57950000</v>
       </c>
       <c r="G31" t="s" s="3">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H31" t="s" s="3">
         <v>108</v>
@@ -3418,7 +3424,7 @@
         <v>110</v>
       </c>
       <c r="C32" t="s" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" s="7">
         <v>2102</v>
@@ -3430,7 +3436,7 @@
         <v>86925000</v>
       </c>
       <c r="G32" t="s" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" t="s" s="7">
         <v>112</v>
@@ -3444,7 +3450,7 @@
         <v>114</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" s="2">
         <v>7500</v>
@@ -3456,10 +3462,10 @@
         <v>144875000</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3471,7 +3477,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3483,7 +3489,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3505,288 +3511,288 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -3798,7 +3804,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3810,7 +3816,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3832,522 +3838,522 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>47</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>248</v>
+        <v>333</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="G20" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>296</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>297</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="F20" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="G20" t="s" s="0">
-        <v>382</v>
-      </c>
       <c r="H20" t="s" s="0">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>399</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="G23" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>403</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>397</v>
-      </c>
-      <c r="E23" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="F23" t="s" s="0">
-        <v>405</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>400</v>
-      </c>
       <c r="H23" t="s" s="0">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4359,7 +4365,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4371,7 +4377,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4399,33 +4405,33 @@
         <v>3</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D5" s="0">
         <v>1050</v>
@@ -4437,21 +4443,21 @@
         <v>17850000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D6" s="0">
         <v>1150</v>
@@ -4463,21 +4469,21 @@
         <v>19550000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C7" t="s" s="9">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D7" s="9">
         <v>1100</v>
@@ -4489,21 +4495,21 @@
         <v>18700000</v>
       </c>
       <c r="G7" t="s" s="9">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H7" t="s" s="9">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="5">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B8" t="s" s="5">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C8" t="s" s="5">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D8" s="5">
         <v>1050</v>
@@ -4515,21 +4521,21 @@
         <v>17850000</v>
       </c>
       <c r="G8" t="s" s="5">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H8" t="s" s="5">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D9" s="0">
         <v>90</v>
@@ -4541,21 +4547,21 @@
         <v>1500000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D10" s="0">
         <v>64</v>
@@ -4567,21 +4573,21 @@
         <v>1000000</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D11" s="0">
         <v>9</v>
@@ -4593,21 +4599,21 @@
         <v>150000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="5">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B12" t="s" s="5">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C12" t="s" s="5">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D12" s="5">
         <v>99</v>
@@ -4619,21 +4625,21 @@
         <v>1650000</v>
       </c>
       <c r="G12" t="s" s="5">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H12" t="s" s="5">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D13" s="0">
         <v>470</v>
@@ -4645,21 +4651,21 @@
         <v>8000000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D14" s="0">
         <v>470</v>
@@ -4671,21 +4677,21 @@
         <v>8000000</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="5">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B15" t="s" s="5">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C15" t="s" s="5">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D15" s="5">
         <v>940</v>
@@ -4697,21 +4703,21 @@
         <v>16000000</v>
       </c>
       <c r="G15" t="s" s="5">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H15" t="s" s="5">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D16" s="0">
         <v>190</v>
@@ -4723,21 +4729,21 @@
         <v>3200000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D17" s="0">
         <v>35</v>
@@ -4749,21 +4755,21 @@
         <v>600000</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="5">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B18" t="s" s="5">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C18" t="s" s="5">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D18" s="5">
         <v>225</v>
@@ -4775,21 +4781,21 @@
         <v>3800000</v>
       </c>
       <c r="G18" t="s" s="5">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H18" t="s" s="5">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D19" s="0">
         <v>1060</v>
@@ -4801,21 +4807,21 @@
         <v>18000000</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D20" s="0">
         <v>70</v>
@@ -4827,21 +4833,21 @@
         <v>1200000</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="5">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B21" t="s" s="5">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C21" t="s" s="5">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D21" s="5">
         <v>1130</v>
@@ -4853,21 +4859,21 @@
         <v>19200000</v>
       </c>
       <c r="G21" t="s" s="5">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D22" s="0">
         <v>35</v>
@@ -4879,21 +4885,21 @@
         <v>600000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D23" s="0">
         <v>140</v>
@@ -4905,21 +4911,21 @@
         <v>2400000</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="5">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B24" t="s" s="5">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C24" t="s" s="5">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D24" s="5">
         <v>175</v>
@@ -4931,10 +4937,10 @@
         <v>3000000</v>
       </c>
       <c r="G24" t="s" s="5">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H24" t="s" s="5">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25">
@@ -4949,13 +4955,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="7">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B26" t="s" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C26" t="s" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D26" s="7">
         <v>3619</v>
@@ -4967,21 +4973,21 @@
         <v>61500000</v>
       </c>
       <c r="G26" t="s" s="7">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H26" t="s" s="7">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C27" t="s" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D27" s="7">
         <v>6369</v>
@@ -4993,10 +4999,10 @@
         <v>108250000</v>
       </c>
       <c r="G27" t="s" s="7">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H27" t="s" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -5008,7 +5014,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5020,7 +5026,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5042,33 +5048,33 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B5" s="0">
         <v>105</v>
@@ -5083,18 +5089,18 @@
         <v>530000</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B6" s="0">
         <v>25</v>
@@ -5109,18 +5115,18 @@
         <v>200000</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B7" s="0">
         <v>165</v>
@@ -5135,18 +5141,18 @@
         <v>3600000</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B8" s="0">
         <v>55</v>
@@ -5161,18 +5167,18 @@
         <v>950000</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B9" s="0">
         <v>70</v>
@@ -5187,18 +5193,18 @@
         <v>1600000</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B10" s="0">
         <v>40</v>
@@ -5213,13 +5219,13 @@
         <v>700000</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11">
@@ -5234,7 +5240,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="7">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B12" s="7">
         <v>460</v>
@@ -5249,13 +5255,13 @@
         <v>7580000</v>
       </c>
       <c r="F12" t="s" s="7">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G12" t="s" s="7">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H12" t="s" s="7">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13">
@@ -5270,7 +5276,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -5282,7 +5288,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="4">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -5294,7 +5300,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5306,7 +5312,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5318,7 +5324,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5330,7 +5336,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>

--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
@@ -183,13 +183,22 @@
     <t>Фирменный спа Plataran</t>
   </si>
   <si>
+    <t>Pyramids of Chi: Light Sound Vibration (LSV) на акустических водных кроватях</t>
+  </si>
+  <si>
+    <t>+90 € (акустические пирамиды)</t>
+  </si>
+  <si>
+    <t>pyramidsofchi.com (водные кровати)</t>
+  </si>
+  <si>
     <t>Восстанавливающие балийские массажи и релакс-терапия</t>
   </si>
   <si>
     <t>2 чел х 2 раза</t>
   </si>
   <si>
-    <t>+50 €</t>
+    <t>-40 €</t>
   </si>
   <si>
     <t>Сертифицированные мастера</t>
@@ -469,6 +478,12 @@
   </si>
   <si>
     <t>Премиум спа</t>
+  </si>
+  <si>
+    <t>Водные кровати</t>
+  </si>
+  <si>
+    <t>pyramidsofchi.com (пирамиды звука)</t>
   </si>
   <si>
     <t>Восстанавливающий массаж после перелета для 2 гостей</t>
@@ -837,6 +852,27 @@
     <t>Согласовать с Манку утреннее приватное время (08:30) у источников водопада Genah Melukat до появления других людей.</t>
   </si>
   <si>
+    <t>11. Pyramids of Chi (Сессия на водных кроватях)</t>
+  </si>
+  <si>
+    <t>https://pyramidsofchi.com</t>
+  </si>
+  <si>
+    <t>Имена 2 гостей, выбор сессии LSV</t>
+  </si>
+  <si>
+    <t>750 000 IDR/чел (~45 €)</t>
+  </si>
+  <si>
+    <t>Онлайн картой на сайте pyramidsofchi.com</t>
+  </si>
+  <si>
+    <t>Билеты/ваучер на Light Sound Vibration</t>
+  </si>
+  <si>
+    <t>Зайти на сайт pyramidsofchi.com, раздел Sound Healing -&gt; Light Sound Vibration (LSV). Забронировать 2 акустические водные кровати на согласованное время.</t>
+  </si>
+  <si>
     <t>СПРАВОЧНИК ОФИЦИАЛЬНЫХ ТАРИФОВ И ПРЯМЫХ ССЫЛОК (БАЛИ 2026)</t>
   </si>
   <si>
@@ -1162,6 +1198,27 @@
   </si>
   <si>
     <t>Королевский балийский уход</t>
+  </si>
+  <si>
+    <t>Pyramids of Chi (LSV на водных кроватях)</t>
+  </si>
+  <si>
+    <t>Pyramids of Chi Bali</t>
+  </si>
+  <si>
+    <t>750 000 IDR/чел</t>
+  </si>
+  <si>
+    <t>45 €/чел</t>
+  </si>
+  <si>
+    <t>Light Sound Vibration (LSV) на подогреваемых акустических водных матрасах</t>
+  </si>
+  <si>
+    <t>Онлайн на сайте картой</t>
+  </si>
+  <si>
+    <t>Сакральная геометрия, акустический резонанс через воду прямо в ткани тела</t>
   </si>
   <si>
     <t>The Blanco Renaissance Museum</t>
@@ -2167,293 +2224,293 @@
         <v>56</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0">
+        <v>90</v>
+      </c>
+      <c r="F17" s="0">
+        <v>1500000</v>
+      </c>
+      <c r="G17" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D17" s="0">
+      <c r="H17" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D18" s="0">
         <v>150</v>
       </c>
-      <c r="E17" s="0">
-        <v>200</v>
-      </c>
-      <c r="F17" s="0">
-        <v>3400000</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="5">
+      <c r="E18" s="0">
+        <v>110</v>
+      </c>
+      <c r="F18" s="0">
+        <v>1900000</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="5">
         <v>52</v>
       </c>
-      <c r="B18" t="s" s="5">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="B19" t="s" s="5">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="D19" s="5">
         <v>350</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="5">
         <v>390</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F19" s="5">
         <v>6600000</v>
       </c>
-      <c r="G18" t="s" s="5">
-        <v>62</v>
-      </c>
-      <c r="H18" t="s" s="5">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s" s="0">
+      <c r="G19" t="s" s="5">
         <v>65</v>
       </c>
-      <c r="C19" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D19" s="0">
-        <v>120</v>
-      </c>
-      <c r="E19" s="0">
-        <v>105</v>
-      </c>
-      <c r="F19" s="0">
-        <v>1800000</v>
-      </c>
-      <c r="G19" t="s" s="0">
+      <c r="H19" t="s" s="5">
         <v>66</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>68</v>
       </c>
       <c r="C20" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D20" s="0">
+        <v>120</v>
+      </c>
+      <c r="E20" s="0">
+        <v>105</v>
+      </c>
+      <c r="F20" s="0">
+        <v>1800000</v>
+      </c>
+      <c r="G20" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="D20" s="0">
-        <v>180</v>
-      </c>
-      <c r="E20" s="0">
-        <v>200</v>
-      </c>
-      <c r="F20" s="0">
-        <v>3400000</v>
-      </c>
-      <c r="G20" t="s" s="0">
+      <c r="H20" t="s" s="0">
         <v>70</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D21" s="0">
+        <v>180</v>
+      </c>
+      <c r="E21" s="0">
+        <v>200</v>
+      </c>
+      <c r="F21" s="0">
+        <v>3400000</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D22" s="0">
+        <v>60</v>
+      </c>
+      <c r="E22" s="0">
+        <v>70</v>
+      </c>
+      <c r="F22" s="0">
+        <v>1200000</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="5">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s" s="5">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s" s="5">
         <v>64</v>
       </c>
-      <c r="B21" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D21" s="0">
-        <v>60</v>
-      </c>
-      <c r="E21" s="0">
-        <v>70</v>
-      </c>
-      <c r="F21" s="0">
-        <v>1200000</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="5">
-        <v>64</v>
-      </c>
-      <c r="B22" t="s" s="5">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="D23" s="5">
         <v>360</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E23" s="5">
         <v>375</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F23" s="5">
         <v>6400000</v>
       </c>
-      <c r="G22" t="s" s="5">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="5">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="B23" t="s" s="0">
+      <c r="G23" t="s" s="5">
         <v>78</v>
       </c>
-      <c r="C23" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="D23" s="0">
-        <v>200</v>
-      </c>
-      <c r="E23" s="0">
-        <v>200</v>
-      </c>
-      <c r="F23" s="0">
-        <v>3400000</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="H23" t="s" s="0">
+      <c r="H23" t="s" s="5">
         <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D24" s="0">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E24" s="0">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F24" s="0">
-        <v>5100000</v>
+        <v>3400000</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>47</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>40</v>
       </c>
       <c r="D25" s="0">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E25" s="0">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F25" s="0">
-        <v>4250000</v>
+        <v>5100000</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>47</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="5">
-        <v>77</v>
-      </c>
-      <c r="B26" t="s" s="5">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="A26" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D26" s="0">
+        <v>250</v>
+      </c>
+      <c r="E26" s="0">
+        <v>250</v>
+      </c>
+      <c r="F26" s="0">
+        <v>4250000</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="5">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="5">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="D27" s="5">
         <v>750</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>750</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F27" s="5">
         <v>12750000</v>
       </c>
-      <c r="G26" t="s" s="5">
+      <c r="G27" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="H26" t="s" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s" s="0">
+      <c r="H27" t="s" s="5">
         <v>88</v>
-      </c>
-      <c r="D27" s="0">
-        <v>0</v>
-      </c>
-      <c r="E27" s="0">
-        <v>0</v>
-      </c>
-      <c r="F27" s="0">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="H27" t="s" s="0">
-        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>92</v>
       </c>
       <c r="D28" s="0">
         <v>0</v>
@@ -2465,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>93</v>
@@ -2473,7 +2530,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>94</v>
@@ -2491,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>96</v>
@@ -2499,7 +2556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>97</v>
@@ -2517,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>99</v>
@@ -2525,7 +2582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>100</v>
@@ -2543,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>102</v>
@@ -2551,13 +2608,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>103</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="D32" s="0">
         <v>0</v>
@@ -2569,98 +2626,124 @@
         <v>0</v>
       </c>
       <c r="G32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="H32" t="s" s="0">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0"/>
-      <c r="B33" s="0"/>
-      <c r="C33" s="0"/>
-      <c r="D33" s="0"/>
-      <c r="E33" s="0"/>
-      <c r="F33" s="0"/>
-      <c r="G33" s="0"/>
-      <c r="H33" s="0"/>
+      <c r="B33" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>107</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="3">
-        <v>105</v>
-      </c>
-      <c r="B34" t="s" s="3">
-        <v>106</v>
-      </c>
-      <c r="C34" t="s" s="3">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+      <c r="C34" s="0"/>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>7188</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E35" s="3">
         <v>4800</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F35" s="3">
         <v>81800000</v>
       </c>
-      <c r="G34" t="s" s="3">
-        <v>107</v>
-      </c>
-      <c r="H34" t="s" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="7">
-        <v>109</v>
-      </c>
-      <c r="B35" t="s" s="7">
+      <c r="G35" t="s" s="3">
         <v>110</v>
       </c>
-      <c r="C35" t="s" s="7">
+      <c r="H35" t="s" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="7">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s" s="7">
+        <v>113</v>
+      </c>
+      <c r="C36" t="s" s="7">
         <v>29</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D36" s="7">
         <v>2512</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E36" s="7">
         <v>7200</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F36" s="7">
         <v>122700000</v>
       </c>
-      <c r="G35" t="s" s="7">
-        <v>111</v>
-      </c>
-      <c r="H35" t="s" s="7">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="B36" t="s" s="2">
+      <c r="G36" t="s" s="7">
         <v>114</v>
       </c>
-      <c r="C36" t="s" s="2">
+      <c r="H36" t="s" s="7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D37" s="2">
         <v>9700</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E37" s="2">
         <v>12000</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F37" s="2">
         <v>204500000</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>116</v>
+      <c r="G37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2684,7 +2767,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2715,16 +2798,16 @@
         <v>4</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s" s="1">
         <v>6</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s" s="1">
         <v>9</v>
@@ -2732,10 +2815,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>20</v>
@@ -2750,18 +2833,18 @@
         <v>11000000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>20</v>
@@ -2776,21 +2859,21 @@
         <v>11600000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="5">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s" s="5">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D7" s="5">
         <v>3700</v>
@@ -2802,10 +2885,10 @@
         <v>22600000</v>
       </c>
       <c r="G7" t="s" s="5">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H7" t="s" s="5">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -2813,10 +2896,10 @@
         <v>27</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D8" s="0">
         <v>400</v>
@@ -2828,10 +2911,10 @@
         <v>5500000</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -2839,10 +2922,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>137</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>134</v>
       </c>
       <c r="D9" s="0">
         <v>100</v>
@@ -2854,10 +2937,10 @@
         <v>1800000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -2865,10 +2948,10 @@
         <v>27</v>
       </c>
       <c r="B10" t="s" s="5">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s" s="5">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D10" s="5">
         <v>500</v>
@@ -2880,7 +2963,7 @@
         <v>7300000</v>
       </c>
       <c r="G10" t="s" s="5">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H10" t="s" s="5">
         <v>37</v>
@@ -2891,7 +2974,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>40</v>
@@ -2906,10 +2989,10 @@
         <v>2700000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
@@ -2932,7 +3015,7 @@
         <v>1000000</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>45</v>
@@ -2958,7 +3041,7 @@
         <v>300000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>48</v>
@@ -2969,7 +3052,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s" s="5">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C14" t="s" s="5">
         <v>40</v>
@@ -2984,7 +3067,7 @@
         <v>4000000</v>
       </c>
       <c r="G14" t="s" s="5">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H14" t="s" s="5">
         <v>51</v>
@@ -2992,10 +3075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>40</v>
@@ -3004,13 +3087,13 @@
         <v>200</v>
       </c>
       <c r="E15" s="0">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="F15" s="0">
-        <v>3200000</v>
+        <v>2550000</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>55</v>
@@ -3018,273 +3101,273 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>40</v>
       </c>
       <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0">
+        <v>90</v>
+      </c>
+      <c r="F16" s="0">
+        <v>1500000</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D17" s="0">
         <v>100</v>
       </c>
-      <c r="E16" s="0">
-        <v>100</v>
-      </c>
-      <c r="F16" s="0">
-        <v>1700000</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="5">
-        <v>149</v>
-      </c>
-      <c r="B17" t="s" s="5">
-        <v>154</v>
-      </c>
-      <c r="C17" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="E17" s="0">
+        <v>50</v>
+      </c>
+      <c r="F17" s="0">
+        <v>850000</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="5">
+        <v>152</v>
+      </c>
+      <c r="B18" t="s" s="5">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="D18" s="5">
         <v>300</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E18" s="5">
         <v>290</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F18" s="5">
         <v>4900000</v>
       </c>
-      <c r="G17" t="s" s="5">
-        <v>155</v>
-      </c>
-      <c r="H17" t="s" s="5">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="D18" s="0">
-        <v>120</v>
-      </c>
-      <c r="E18" s="0">
-        <v>105</v>
-      </c>
-      <c r="F18" s="0">
-        <v>1800000</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>157</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>67</v>
+      <c r="G18" t="s" s="5">
+        <v>160</v>
+      </c>
+      <c r="H18" t="s" s="5">
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>40</v>
       </c>
       <c r="D19" s="0">
+        <v>120</v>
+      </c>
+      <c r="E19" s="0">
+        <v>105</v>
+      </c>
+      <c r="F19" s="0">
+        <v>1800000</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D20" s="0">
         <v>50</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E20" s="0">
         <v>50</v>
       </c>
-      <c r="F19" s="0">
+      <c r="F20" s="0">
         <v>850000</v>
       </c>
-      <c r="G19" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="5">
+      <c r="G20" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="5">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s" s="5">
+        <v>166</v>
+      </c>
+      <c r="C21" t="s" s="5">
         <v>64</v>
       </c>
-      <c r="B20" t="s" s="5">
-        <v>161</v>
-      </c>
-      <c r="C20" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="D21" s="5">
         <v>170</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E21" s="5">
         <v>155</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F21" s="5">
         <v>2650000</v>
       </c>
-      <c r="G20" t="s" s="5">
-        <v>162</v>
-      </c>
-      <c r="H20" t="s" s="5">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>134</v>
-      </c>
-      <c r="D21" s="0">
-        <v>150</v>
-      </c>
-      <c r="E21" s="0">
-        <v>150</v>
-      </c>
-      <c r="F21" s="0">
-        <v>2550000</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>165</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>166</v>
+      <c r="G21" t="s" s="5">
+        <v>167</v>
+      </c>
+      <c r="H21" t="s" s="5">
+        <v>168</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="D22" s="0">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E22" s="0">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="F22" s="0">
-        <v>4250000</v>
+        <v>2550000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>40</v>
       </c>
       <c r="D23" s="0">
+        <v>250</v>
+      </c>
+      <c r="E23" s="0">
+        <v>250</v>
+      </c>
+      <c r="F23" s="0">
+        <v>4250000</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D24" s="0">
         <v>200</v>
       </c>
-      <c r="E23" s="0">
+      <c r="E24" s="0">
         <v>200</v>
       </c>
-      <c r="F23" s="0">
+      <c r="F24" s="0">
         <v>3400000</v>
       </c>
-      <c r="G23" t="s" s="0">
-        <v>171</v>
-      </c>
-      <c r="H23" t="s" s="0">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="5">
-        <v>77</v>
-      </c>
-      <c r="B24" t="s" s="5">
-        <v>173</v>
-      </c>
-      <c r="C24" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="G24" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="5">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s" s="5">
+        <v>178</v>
+      </c>
+      <c r="C25" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="D25" s="5">
         <v>600</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E25" s="5">
         <v>600</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F25" s="5">
         <v>10200000</v>
       </c>
-      <c r="G24" t="s" s="5">
-        <v>174</v>
-      </c>
-      <c r="H24" t="s" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="D25" s="0">
-        <v>0</v>
-      </c>
-      <c r="E25" s="0">
-        <v>0</v>
-      </c>
-      <c r="F25" s="0">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="H25" t="s" s="0">
-        <v>90</v>
+      <c r="G25" t="s" s="5">
+        <v>179</v>
+      </c>
+      <c r="H25" t="s" s="5">
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D26" s="0">
         <v>0</v>
@@ -3296,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>93</v>
@@ -3304,7 +3387,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>94</v>
@@ -3322,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>96</v>
@@ -3330,7 +3413,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>97</v>
@@ -3348,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>99</v>
@@ -3356,13 +3439,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="D29" s="0">
         <v>0</v>
@@ -3374,98 +3457,124 @@
         <v>0</v>
       </c>
       <c r="G29" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="H29" t="s" s="0">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0"/>
-      <c r="B30" s="0"/>
-      <c r="C30" s="0"/>
-      <c r="D30" s="0"/>
-      <c r="E30" s="0"/>
-      <c r="F30" s="0"/>
-      <c r="G30" s="0"/>
-      <c r="H30" s="0"/>
+      <c r="B30" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>107</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="3">
-        <v>105</v>
-      </c>
-      <c r="B31" t="s" s="3">
-        <v>177</v>
-      </c>
-      <c r="C31" t="s" s="3">
-        <v>134</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s" s="3">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="D32" s="3">
         <v>5398</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F32" s="3">
         <v>57950000</v>
       </c>
-      <c r="G31" t="s" s="3">
-        <v>178</v>
-      </c>
-      <c r="H31" t="s" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="7">
-        <v>109</v>
-      </c>
-      <c r="B32" t="s" s="7">
-        <v>110</v>
-      </c>
-      <c r="C32" t="s" s="7">
-        <v>134</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="G32" t="s" s="3">
+        <v>183</v>
+      </c>
+      <c r="H32" t="s" s="3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="7">
+        <v>112</v>
+      </c>
+      <c r="B33" t="s" s="7">
+        <v>113</v>
+      </c>
+      <c r="C33" t="s" s="7">
+        <v>137</v>
+      </c>
+      <c r="D33" s="7">
         <v>2102</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="7">
         <v>5100</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="7">
         <v>86925000</v>
       </c>
-      <c r="G32" t="s" s="7">
-        <v>179</v>
-      </c>
-      <c r="H32" t="s" s="7">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="G33" t="s" s="7">
+        <v>184</v>
+      </c>
+      <c r="H33" t="s" s="7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="D34" s="2">
         <v>7500</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <v>8500</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="2">
         <v>144875000</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>181</v>
+      <c r="G34" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3477,7 +3586,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3489,7 +3598,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3511,288 +3620,314 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>270</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3804,7 +3939,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3816,7 +3951,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3838,522 +3973,548 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>47</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>321</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="E15" t="s" s="0">
         <v>351</v>
       </c>
-      <c r="C15" t="s" s="0">
-        <v>352</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>353</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>339</v>
-      </c>
       <c r="F15" t="s" s="0">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>297</v>
+        <v>394</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>298</v>
+        <v>395</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>382</v>
+        <v>277</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>390</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>398</v>
+        <v>309</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>403</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>408</v>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>424</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>425</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>418</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>421</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4365,7 +4526,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4377,7 +4538,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4405,33 +4566,33 @@
         <v>3</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>415</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="D5" s="0">
         <v>1050</v>
@@ -4443,21 +4604,21 @@
         <v>17850000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>420</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="D6" s="0">
         <v>1150</v>
@@ -4469,21 +4630,21 @@
         <v>19550000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>423</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="C7" t="s" s="9">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="D7" s="9">
         <v>1100</v>
@@ -4495,21 +4656,21 @@
         <v>18700000</v>
       </c>
       <c r="G7" t="s" s="9">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="H7" t="s" s="9">
-        <v>426</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="5">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B8" t="s" s="5">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="C8" t="s" s="5">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="D8" s="5">
         <v>1050</v>
@@ -4521,21 +4682,21 @@
         <v>17850000</v>
       </c>
       <c r="G8" t="s" s="5">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="H8" t="s" s="5">
-        <v>429</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D9" s="0">
         <v>90</v>
@@ -4547,21 +4708,21 @@
         <v>1500000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>434</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="D10" s="0">
         <v>64</v>
@@ -4573,21 +4734,21 @@
         <v>1000000</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>437</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="D11" s="0">
         <v>9</v>
@@ -4599,21 +4760,21 @@
         <v>150000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>441</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="5">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B12" t="s" s="5">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C12" t="s" s="5">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D12" s="5">
         <v>99</v>
@@ -4625,21 +4786,21 @@
         <v>1650000</v>
       </c>
       <c r="G12" t="s" s="5">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="H12" t="s" s="5">
-        <v>444</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D13" s="0">
         <v>470</v>
@@ -4651,21 +4812,21 @@
         <v>8000000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>449</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="D14" s="0">
         <v>470</v>
@@ -4677,21 +4838,21 @@
         <v>8000000</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>451</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="5">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="B15" t="s" s="5">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="C15" t="s" s="5">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D15" s="5">
         <v>940</v>
@@ -4703,21 +4864,21 @@
         <v>16000000</v>
       </c>
       <c r="G15" t="s" s="5">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="H15" t="s" s="5">
-        <v>455</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D16" s="0">
         <v>190</v>
@@ -4729,21 +4890,21 @@
         <v>3200000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D17" s="0">
         <v>35</v>
@@ -4755,21 +4916,21 @@
         <v>600000</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>462</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="5">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B18" t="s" s="5">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="C18" t="s" s="5">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D18" s="5">
         <v>225</v>
@@ -4781,21 +4942,21 @@
         <v>3800000</v>
       </c>
       <c r="G18" t="s" s="5">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="H18" t="s" s="5">
-        <v>465</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D19" s="0">
         <v>1060</v>
@@ -4807,21 +4968,21 @@
         <v>18000000</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>469</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D20" s="0">
         <v>70</v>
@@ -4833,21 +4994,21 @@
         <v>1200000</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>472</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="5">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B21" t="s" s="5">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="C21" t="s" s="5">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D21" s="5">
         <v>1130</v>
@@ -4859,21 +5020,21 @@
         <v>19200000</v>
       </c>
       <c r="G21" t="s" s="5">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>475</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D22" s="0">
         <v>35</v>
@@ -4885,21 +5046,21 @@
         <v>600000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>479</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="D23" s="0">
         <v>140</v>
@@ -4911,21 +5072,21 @@
         <v>2400000</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>483</v>
+        <v>502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="5">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B24" t="s" s="5">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="C24" t="s" s="5">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D24" s="5">
         <v>175</v>
@@ -4937,10 +5098,10 @@
         <v>3000000</v>
       </c>
       <c r="G24" t="s" s="5">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="H24" t="s" s="5">
-        <v>486</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25">
@@ -4955,13 +5116,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="7">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="B26" t="s" s="7">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="C26" t="s" s="7">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D26" s="7">
         <v>3619</v>
@@ -4973,21 +5134,21 @@
         <v>61500000</v>
       </c>
       <c r="G26" t="s" s="7">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="H26" t="s" s="7">
-        <v>490</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="7">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="C27" t="s" s="7">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D27" s="7">
         <v>6369</v>
@@ -4999,10 +5160,10 @@
         <v>108250000</v>
       </c>
       <c r="G27" t="s" s="7">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="H27" t="s" s="7">
-        <v>494</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -5014,7 +5175,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5026,7 +5187,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5048,33 +5209,33 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>504</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="B5" s="0">
         <v>105</v>
@@ -5089,18 +5250,18 @@
         <v>530000</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>508</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="B6" s="0">
         <v>25</v>
@@ -5115,18 +5276,18 @@
         <v>200000</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>512</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="B7" s="0">
         <v>165</v>
@@ -5141,18 +5302,18 @@
         <v>3600000</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>516</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="B8" s="0">
         <v>55</v>
@@ -5167,18 +5328,18 @@
         <v>950000</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>520</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="B9" s="0">
         <v>70</v>
@@ -5193,18 +5354,18 @@
         <v>1600000</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>524</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="B10" s="0">
         <v>40</v>
@@ -5219,13 +5380,13 @@
         <v>700000</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>528</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11">
@@ -5240,7 +5401,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="7">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="B12" s="7">
         <v>460</v>
@@ -5255,13 +5416,13 @@
         <v>7580000</v>
       </c>
       <c r="F12" t="s" s="7">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="G12" t="s" s="7">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="H12" t="s" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13">
@@ -5276,7 +5437,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -5288,7 +5449,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="4">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -5300,7 +5461,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5312,7 +5473,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5324,7 +5485,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5336,7 +5497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>

--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="614">
   <si>
     <t>СРАВНИТЕЛЬНАЯ СМЕТА: ИСХОДНАЯ СМЕТА (МАРАТ 5★) vs АКТУАЛЬНАЯ (ШВЕЙЦАРИЯ 4★+)</t>
   </si>
   <si>
-    <t>7 Дней / 6 Ночей • Оптимизация отелей (300-400 €) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
+    <t>7 Дней / 6 Ночей • Камерные резиденции 4★ Superior (300-400 €) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
   </si>
   <si>
     <t>Категория расходов</t>
@@ -48,7 +48,7 @@
     <t>1. Размещение</t>
   </si>
   <si>
-    <t>Убуд: Plataran Ubud Hotel &amp; Spa (Deluxe Suite, 320 €/н) vs The Kayon Jungle (850 €/н)</t>
+    <t>Убуд: Камерная резиденция среди садов (Suite с видом на террасы, 320 €/н) vs Прежний 5★ люкс (850 €/н)</t>
   </si>
   <si>
     <t>3 ночи</t>
@@ -57,10 +57,10 @@
     <t>-1 590 € (экономия)</t>
   </si>
   <si>
-    <t>plataran.com/plataran-ubud</t>
-  </si>
-  <si>
-    <t>Кинтамани: Toteme Glamping &amp; Hot Springs (Шатер с купелью, 220 €) vs Faro Cabin (350 €)</t>
+    <t>Камерный ретрит в садах Убуда</t>
+  </si>
+  <si>
+    <t>Кинтамани: Приватный вулканический лодж с термами (Сьют с купелью, 220 €) vs Массовый глэмпинг (350 €)</t>
   </si>
   <si>
     <t>1 ночь</t>
@@ -69,10 +69,10 @@
     <t>-130 € (экономия)</t>
   </si>
   <si>
-    <t>totemeglamping.com</t>
-  </si>
-  <si>
-    <t>Побережье: Приватная вилла у пляжа (Paradise Beach / Санур, 340 €/н) vs Bulgari / Six Senses (1 000 €/н)</t>
+    <t>Вулканический лодж у озера Батур</t>
+  </si>
+  <si>
+    <t>Побережье: Приватная вилла у океана (Санур, первая линия, лагуна, 340 €/н) vs Сетевой 5★ люкс (1 000 €/н)</t>
   </si>
   <si>
     <t>2 ночи</t>
@@ -81,7 +81,7 @@
     <t>-1 320 € (экономия)</t>
   </si>
   <si>
-    <t>Приватная бутик-вилла на первой линии</t>
+    <t>Приватная вилла у спокойной лагуны</t>
   </si>
   <si>
     <t>ИТОГО ПРОЖИВАНИЕ (6 ночей, средняя 310 €/ночь против 815 €/ночь)</t>
@@ -174,13 +174,13 @@
     <t>4. Спа и релаксация</t>
   </si>
   <si>
-    <t>3-часовой ритуал: ванна из роз, скраб Lulur, травяной уход (Padma Spa Plataran)</t>
+    <t>3-часовой ритуал: ванна из сотен роз, скраб Lulur, травяной уход</t>
   </si>
   <si>
     <t>-10 €</t>
   </si>
   <si>
-    <t>Фирменный спа Plataran</t>
+    <t>Спа-санктуарий в тропических садах</t>
   </si>
   <si>
     <t>Pyramids of Chi: Light Sound Vibration (LSV) на акустических водных кроватях</t>
@@ -339,10 +339,34 @@
     <t>Личное ведение без посредников</t>
   </si>
   <si>
+    <t>8. Живые ремесла</t>
+  </si>
+  <si>
+    <t>Вудкарвинг: династическая мастерская сакральной резьбы по дереву (Мас)</t>
+  </si>
+  <si>
+    <t>По желанию</t>
+  </si>
+  <si>
+    <t>Потомственные резчики Мас (визит без очередей)</t>
+  </si>
+  <si>
+    <t>Батик (Batik Tulis): мастер-класс живой росписи горячим воском и крашения шелка</t>
+  </si>
+  <si>
+    <t>Традиционная студия Тохпати / Убуд</t>
+  </si>
+  <si>
+    <t>Урок игры на балийском гамелане: сакральная полиритмия котекан с оркестром секехе</t>
+  </si>
+  <si>
+    <t>Павильон мастеров гамелана секехе</t>
+  </si>
+  <si>
     <t>ИТОГО ОПЕРАЦИОННАЯ СЕБЕСТОИМОСТЬ (40%)</t>
   </si>
   <si>
-    <t>Прямые расходы на 2 гостей (отели 4★+, авто, спа, храмы, еда, VIP)</t>
+    <t>Прямые расходы на 2 гостей (резиденции 4★+, авто, спа, храмы, еда, VIP)</t>
   </si>
   <si>
     <t>-2 388 € (чистая экономия)</t>
@@ -378,7 +402,7 @@
     <t>СМЕТА ТУРА «BALI SANCTUARY»: 5 ДНЕЙ / 4 НОЧИ (ГОСТЬИ ИЗ ШВЕЙЦАРИИ)</t>
   </si>
   <si>
-    <t>Камерные бутик-отели 4★+ (300–400 €/ночь) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
+    <t>Камерные резиденции 4★+ (300–400 €/ночь) • Полный VIP Fast-Track • Гонорар мастера 60%</t>
   </si>
   <si>
     <t>Базовый расчет 5★ [€]</t>
@@ -393,22 +417,22 @@
     <t>1. Размещение (4★+)</t>
   </si>
   <si>
-    <t>Plataran Ubud Hotel &amp; Spa (Deluxe Suite с видом на террасы)</t>
+    <t>Убуд: Камерная резиденция среди садов (Suite с видом на террасы)</t>
   </si>
   <si>
     <t>18.8% от бюджета</t>
   </si>
   <si>
-    <t>plataran.com/plataran-ubud (320 €/н)</t>
-  </si>
-  <si>
-    <t>Приватная вилла у океана (Paradise Beach / Санур, 1-я линия)</t>
+    <t>Садовый ретрит Убуда (320 €/н)</t>
+  </si>
+  <si>
+    <t>Санур: Приватная вилла у спокойной лагуны (1-я линия океана)</t>
   </si>
   <si>
     <t>20.0% от бюджета</t>
   </si>
   <si>
-    <t>Бутик-вилла у лагуны (340 €/н)</t>
+    <t>Океанская вилла с садом (340 €/н)</t>
   </si>
   <si>
     <t>Итого проживание (4 ночи, в пределах 300–400 €/ночь)</t>
@@ -474,12 +498,15 @@
     <t>4. Спа и тело</t>
   </si>
   <si>
-    <t>3-часовой ритуал: ванна из роз, скраб Lulur (Padma Spa Plataran)</t>
+    <t>3-часовой ритуал: ванна из роз, скраб Lulur, уход лепестками</t>
   </si>
   <si>
     <t>Премиум спа</t>
   </si>
   <si>
+    <t>Спа-санктуарий в садах Убуда</t>
+  </si>
+  <si>
     <t>Водные кровати</t>
   </si>
   <si>
@@ -561,7 +588,7 @@
     <t>Непрерывное кураторство 24/7 (индонезийский язык)</t>
   </si>
   <si>
-    <t>Все прямые расходы на 2 гостей (отели 4★+, авто, спа, храмы, еда, VIP)</t>
+    <t>Все прямые расходы на 2 гостей (резиденции 4★+, авто, спа, храмы, еда, VIP)</t>
   </si>
   <si>
     <t>40% от общей суммы</t>
@@ -735,322 +762,394 @@
     <t>Отправить Путу точный рейс, скриншот брони JOUMPA и время посадки. Путу паркуется в VIP-зоне терминала за 30 мин до прилета.</t>
   </si>
   <si>
-    <t>6. Отель Plataran Ubud Hotel &amp; Spa 4★+</t>
+    <t>6. Камерная резиденция среди садов Убуда</t>
+  </si>
+  <si>
+    <t>Прямое бронирование сьюта</t>
+  </si>
+  <si>
+    <t>За 14–30 дней до тура</t>
+  </si>
+  <si>
+    <t>Имена гостей, даты проживания (3 ночи)</t>
+  </si>
+  <si>
+    <t>5 500 000 IDR/ночь (~320 €/н)</t>
+  </si>
+  <si>
+    <t>Предоплата картой организатора</t>
+  </si>
+  <si>
+    <t>Подтверждение брони Deluxe Suite</t>
+  </si>
+  <si>
+    <t>Забронировать просторный сьют с террасой с видом на сады и террасы. Заказать заранее комплиментарную корзину фруктов и приветственный травяной сбор.</t>
+  </si>
+  <si>
+    <t>7. Вулканический геотермальный лодж (Кинтамани)</t>
+  </si>
+  <si>
+    <t>Прямой контракт / сайт лоджа</t>
+  </si>
+  <si>
+    <t>За 14–20 дней до тура</t>
+  </si>
+  <si>
+    <t>Даты проживания (1 ночь)</t>
+  </si>
+  <si>
+    <t>3 800 000 IDR/ночь (~220 €/н)</t>
+  </si>
+  <si>
+    <t>Картой онлайн или WhatsApp лоджа</t>
+  </si>
+  <si>
+    <t>Подтверждение сьюта с приватной купелью</t>
+  </si>
+  <si>
+    <t>Выбрать панорамный сьют с индивидуальной термальной минеральной ванной на террасе. Заказать прогрев купели к моменту заезда (17:00).</t>
+  </si>
+  <si>
+    <t>8. Приватная океанская вилла у пляжа (Санур)</t>
+  </si>
+  <si>
+    <t>Прямой контракт / бронь виллы</t>
+  </si>
+  <si>
+    <t>Имена гостей, даты проживания (2 ночи)</t>
+  </si>
+  <si>
+    <t>5 800 000 IDR/ночь (~340 €/н)</t>
+  </si>
+  <si>
+    <t>Предоплата картой или банковский перевод</t>
+  </si>
+  <si>
+    <t>Подтверждение приватной пляжной виллы</t>
+  </si>
+  <si>
+    <t>Забронировать виллу на первой линии с приватным садом и прямым выходом к спокойной лагуне для купания без волн.</t>
+  </si>
+  <si>
+    <t>9. Ресторан Mozaic Gastronomic (Убуд)</t>
+  </si>
+  <si>
+    <t>https://mozaic-bali.com</t>
+  </si>
+  <si>
+    <t>За 7–14 дней до тура</t>
+  </si>
+  <si>
+    <t>Количество гостей (2 чел), диетические ограничения</t>
+  </si>
+  <si>
+    <t>Дегустационный сет (~150 €/чел)</t>
+  </si>
+  <si>
+    <t>Депозит картой на сайте Chope/Mozaic</t>
+  </si>
+  <si>
+    <t>Бронь столика в саду шефа</t>
+  </si>
+  <si>
+    <t>Забронировать дегустационное меню Tasting Menu от шеф-повара Блейка Торнли. Указать вегетарианские/аллергические предпочтения гостий заранее.</t>
+  </si>
+  <si>
+    <t>10. Священник Манку (Мелукат и Агнихотра)</t>
+  </si>
+  <si>
+    <t>Прямой контакт Валерия</t>
+  </si>
+  <si>
+    <t>За 7 дней до тура</t>
+  </si>
+  <si>
+    <t>Дата проведения церемонии в Себату</t>
+  </si>
+  <si>
+    <t>3 400 000 IDR (~200 € за комплекс)</t>
+  </si>
+  <si>
+    <t>Наличными после завершения ритуала</t>
+  </si>
+  <si>
+    <t>Подготовленные подношения Чананг Сари и Агни-хотра</t>
+  </si>
+  <si>
+    <t>Согласовать с Манку утреннее приватное время (08:30) у источников водопада Genah Melukat до появления других людей.</t>
+  </si>
+  <si>
+    <t>11. Pyramids of Chi (Сессия на водных кроватях)</t>
+  </si>
+  <si>
+    <t>https://pyramidsofchi.com</t>
+  </si>
+  <si>
+    <t>Имена 2 гостей, выбор сессии LSV</t>
+  </si>
+  <si>
+    <t>750 000 IDR/чел (~45 €)</t>
+  </si>
+  <si>
+    <t>Онлайн картой на сайте pyramidsofchi.com</t>
+  </si>
+  <si>
+    <t>Билеты/ваучер на Light Sound Vibration</t>
+  </si>
+  <si>
+    <t>Зайти на сайт pyramidsofchi.com, раздел Sound Healing -&gt; Light Sound Vibration (LSV). Забронировать 2 акустические водные кровати на согласованное время.</t>
+  </si>
+  <si>
+    <t>12. Вудкарвинг (Династия резчиков по дереву, Мас)</t>
+  </si>
+  <si>
+    <t>Прямой контакт мастера Мас</t>
+  </si>
+  <si>
+    <t>За 3–5 дней до визита</t>
+  </si>
+  <si>
+    <t>Время посещения в Убуде (день 2 или 3)</t>
+  </si>
+  <si>
+    <t>Донат / покупка изделий</t>
+  </si>
+  <si>
+    <t>Наличными мастеру при покупке</t>
+  </si>
+  <si>
+    <t>Приватный показ сакральной резьбы</t>
+  </si>
+  <si>
+    <t>Согласовать с мастером дневной визит без туристических групп. Показ вековых техник резьбы из сандала, эбена и тика.</t>
+  </si>
+  <si>
+    <t>13. Батик (Batik Tulis canting мастер-класс)</t>
+  </si>
+  <si>
+    <t>Прямой контакт текстильной студии</t>
+  </si>
+  <si>
+    <t>2 человека, выбор шелка/хлопка</t>
+  </si>
+  <si>
+    <t>450 000 IDR/чел (~27 €)</t>
+  </si>
+  <si>
+    <t>Наличными или картой в студии</t>
+  </si>
+  <si>
+    <t>Готовый авторский шелковый платок</t>
+  </si>
+  <si>
+    <t>Забронировать 1.5-часовой камерный мастер-класс росписи горячим воском чантинг для 2 гостей.</t>
+  </si>
+  <si>
+    <t>14. Урок балийского гамелана (Оркестр Секехе)</t>
+  </si>
+  <si>
+    <t>Прямой контакт наставника секехе</t>
+  </si>
+  <si>
+    <t>2 человека, 1 час урока</t>
+  </si>
+  <si>
+    <t>500 000 IDR на двоих (~30 €)</t>
+  </si>
+  <si>
+    <t>Наличными наставнику после урока</t>
+  </si>
+  <si>
+    <t>Индивидуальный урок полиритмии гамелана</t>
+  </si>
+  <si>
+    <t>Согласовать с наставником урок игры на бронзовых ганса и гонгах в тихом деревенском павильоне.</t>
+  </si>
+  <si>
+    <t>СПРАВОЧНИК ОФИЦИАЛЬНЫХ ТАРИФОВ И ПРЯМЫХ ССЫЛОК (БАЛИ 2026)</t>
+  </si>
+  <si>
+    <t>Все цены проверены по государственным порталам и прямым контрактам операторов</t>
+  </si>
+  <si>
+    <t>Услуга / Объект</t>
+  </si>
+  <si>
+    <t>Официальный оператор / Портал</t>
+  </si>
+  <si>
+    <t>Тариф в IDR / USD</t>
+  </si>
+  <si>
+    <t>Тариф в EUR (€)</t>
+  </si>
+  <si>
+    <t>Ссылка на официальный сайт</t>
+  </si>
+  <si>
+    <t>Включено в услугу</t>
+  </si>
+  <si>
+    <t>Как оплачивать</t>
+  </si>
+  <si>
+    <t>Рекомендация для VIP</t>
+  </si>
+  <si>
+    <t>VIP Fast-Track (Прилет)</t>
+  </si>
+  <si>
+    <t>PT Gapura Angkasa (Garuda Group) / JOUMPA</t>
+  </si>
+  <si>
+    <t>1 350 000 IDR/чел</t>
+  </si>
+  <si>
+    <t>80 €/чел</t>
+  </si>
+  <si>
+    <t>Meet &amp; Greet у рукава + дип-коридор + портье багажа + Concordia VIP Lounge</t>
+  </si>
+  <si>
+    <t>Онлайн картой на сайте JOUMPA</t>
+  </si>
+  <si>
+    <t>Бронировать за 5 дней до прилета</t>
+  </si>
+  <si>
+    <t>Электронная виза e-VOA (B1)</t>
+  </si>
+  <si>
+    <t>Иммиграционная служба Индонезии</t>
+  </si>
+  <si>
+    <t>500 000 IDR/чел</t>
+  </si>
+  <si>
+    <t>32 €/чел</t>
+  </si>
+  <si>
+    <t>Въездная туристическая виза на 30 дней</t>
+  </si>
+  <si>
+    <t>Онлайн на официальном госпортале</t>
+  </si>
+  <si>
+    <t>Оформить за 3-5 дней организатором</t>
+  </si>
+  <si>
+    <t>Туристический налог Love Bali</t>
+  </si>
+  <si>
+    <t>Правительство провинции Бали</t>
+  </si>
+  <si>
+    <t>150 000 IDR/чел</t>
+  </si>
+  <si>
+    <t>9 €/чел</t>
+  </si>
+  <si>
+    <t>Официальный туристический сбор</t>
+  </si>
+  <si>
+    <t>Онлайн на сайте lovebali.baliprov.go.id</t>
+  </si>
+  <si>
+    <t>Оплатить заранее, QR-код в телефон</t>
+  </si>
+  <si>
+    <t>Таможенная декларация e-CD</t>
+  </si>
+  <si>
+    <t>Таможенная служба Индонезии (Beacukai)</t>
+  </si>
+  <si>
+    <t>Электронная декларация на багаж</t>
+  </si>
+  <si>
+    <t>Бесплатно онлайн за 3 дня</t>
+  </si>
+  <si>
+    <t>Заполнить 1 общий QR-код на 2 чел</t>
+  </si>
+  <si>
+    <t>Автомобиль с водителем (Путу)</t>
+  </si>
+  <si>
+    <t>Частный контракт (Toyota Innova Zenix)</t>
+  </si>
+  <si>
+    <t>1 100 000 IDR/день</t>
+  </si>
+  <si>
+    <t>65 €/день</t>
+  </si>
+  <si>
+    <t>WhatsApp Путу</t>
+  </si>
+  <si>
+    <t>Автомобиль + бензин + водитель 24/7</t>
+  </si>
+  <si>
+    <t>Наличными IDR Путу</t>
+  </si>
+  <si>
+    <t>Личный проверенный водитель</t>
+  </si>
+  <si>
+    <t>Камерная резиденция в садах (Убуд)</t>
+  </si>
+  <si>
+    <t>Курортный фонд садов Убуда</t>
+  </si>
+  <si>
+    <t>5 500 000 IDR/ночь</t>
+  </si>
+  <si>
+    <t>320 €/ночь</t>
   </si>
   <si>
     <t>https://www.plataran.com/plataran-ubud/</t>
   </si>
   <si>
-    <t>За 14–30 дней до тура</t>
-  </si>
-  <si>
-    <t>Имена гостей, даты проживания (3 ночи)</t>
-  </si>
-  <si>
-    <t>5 500 000 IDR/ночь (~320 €/н)</t>
-  </si>
-  <si>
-    <t>Предоплата картой на сайте Plataran</t>
-  </si>
-  <si>
-    <t>Подтверждение брони Deluxe Suite</t>
-  </si>
-  <si>
-    <t>Забронировать номер категории Deluxe Suite с видом на террасы. Заказать заранее комплиментарную корзину фруктов и приветственный чай.</t>
-  </si>
-  <si>
-    <t>7. Глэмпинг Toteme Kintamani 4★+</t>
+    <t>Suite с видом на сады и террасы + завтрак</t>
+  </si>
+  <si>
+    <t>Прямое бронирование / VIP</t>
+  </si>
+  <si>
+    <t>Уединенный сьют в садах Убуда</t>
+  </si>
+  <si>
+    <t>Вулканический термальный лодж (Кинтамани)</t>
+  </si>
+  <si>
+    <t>Лодж геотермальных источников Батура</t>
+  </si>
+  <si>
+    <t>3 800 000 IDR/ночь</t>
+  </si>
+  <si>
+    <t>220 €/ночь</t>
   </si>
   <si>
     <t>https://totemeglamping.com</t>
   </si>
   <si>
-    <t>За 14–20 дней до тура</t>
-  </si>
-  <si>
-    <t>Даты проживания (1 ночь)</t>
-  </si>
-  <si>
-    <t>3 800 000 IDR/ночь (~220 €/н)</t>
-  </si>
-  <si>
-    <t>Картой на сайте или WhatsApp отеля</t>
-  </si>
-  <si>
-    <t>Подтверждение шатра с приватной купелью</t>
-  </si>
-  <si>
-    <t>Выбрать премиум-шатер с индивидуальной геотермальной минеральной ванной на террасе. Заказать растопку купели к моменту заезда (17:00).</t>
-  </si>
-  <si>
-    <t>8. Приватная вилла у пляжа (Санур)</t>
-  </si>
-  <si>
-    <t>Прямой контракт / Букинг виллы</t>
-  </si>
-  <si>
-    <t>Имена гостей, даты проживания (2 ночи)</t>
-  </si>
-  <si>
-    <t>5 800 000 IDR/ночь (~340 €/н)</t>
-  </si>
-  <si>
-    <t>Предоплата картой или банковский перевод</t>
-  </si>
-  <si>
-    <t>Подтверждение приватной пляжной виллы</t>
-  </si>
-  <si>
-    <t>Забронировать виллу на первой линии с приватным садом и прямым выходом к спокойной лагуне для купания без волн.</t>
-  </si>
-  <si>
-    <t>9. Ресторан Mozaic Gastronomic (Убуд)</t>
-  </si>
-  <si>
-    <t>https://mozaic-bali.com</t>
-  </si>
-  <si>
-    <t>За 7–14 дней до тура</t>
-  </si>
-  <si>
-    <t>Количество гостей (2 чел), диетические ограничения</t>
-  </si>
-  <si>
-    <t>Дегустационный сет (~150 €/чел)</t>
-  </si>
-  <si>
-    <t>Депозит картой на сайте Chope/Mozaic</t>
-  </si>
-  <si>
-    <t>Бронь столика в саду шефа</t>
-  </si>
-  <si>
-    <t>Забронировать дегустационное меню Tasting Menu от шеф-повара Блейка Торнли. Указать вегетарианские/аллергические предпочтения гостий заранее.</t>
-  </si>
-  <si>
-    <t>10. Священник Манку (Мелукат и Агнихотра)</t>
-  </si>
-  <si>
-    <t>Прямой контакт Валерия</t>
-  </si>
-  <si>
-    <t>За 7 дней до тура</t>
-  </si>
-  <si>
-    <t>Дата проведения церемонии в Себату</t>
-  </si>
-  <si>
-    <t>3 400 000 IDR (~200 € за комплекс)</t>
-  </si>
-  <si>
-    <t>Наличными после завершения ритуала</t>
-  </si>
-  <si>
-    <t>Подготовленные подношения Чананг Сари и Агни-хотра</t>
-  </si>
-  <si>
-    <t>Согласовать с Манку утреннее приватное время (08:30) у источников водопада Genah Melukat до появления других людей.</t>
-  </si>
-  <si>
-    <t>11. Pyramids of Chi (Сессия на водных кроватях)</t>
-  </si>
-  <si>
-    <t>https://pyramidsofchi.com</t>
-  </si>
-  <si>
-    <t>Имена 2 гостей, выбор сессии LSV</t>
-  </si>
-  <si>
-    <t>750 000 IDR/чел (~45 €)</t>
-  </si>
-  <si>
-    <t>Онлайн картой на сайте pyramidsofchi.com</t>
-  </si>
-  <si>
-    <t>Билеты/ваучер на Light Sound Vibration</t>
-  </si>
-  <si>
-    <t>Зайти на сайт pyramidsofchi.com, раздел Sound Healing -&gt; Light Sound Vibration (LSV). Забронировать 2 акустические водные кровати на согласованное время.</t>
-  </si>
-  <si>
-    <t>СПРАВОЧНИК ОФИЦИАЛЬНЫХ ТАРИФОВ И ПРЯМЫХ ССЫЛОК (БАЛИ 2026)</t>
-  </si>
-  <si>
-    <t>Все цены проверены по государственным порталам и прямым контрактам операторов</t>
-  </si>
-  <si>
-    <t>Услуга / Объект</t>
-  </si>
-  <si>
-    <t>Официальный оператор / Портал</t>
-  </si>
-  <si>
-    <t>Тариф в IDR / USD</t>
-  </si>
-  <si>
-    <t>Тариф в EUR (€)</t>
-  </si>
-  <si>
-    <t>Ссылка на официальный сайт</t>
-  </si>
-  <si>
-    <t>Включено в услугу</t>
-  </si>
-  <si>
-    <t>Как оплачивать</t>
-  </si>
-  <si>
-    <t>Рекомендация для VIP</t>
-  </si>
-  <si>
-    <t>VIP Fast-Track (Прилет)</t>
-  </si>
-  <si>
-    <t>PT Gapura Angkasa (Garuda Group) / JOUMPA</t>
-  </si>
-  <si>
-    <t>1 350 000 IDR/чел</t>
-  </si>
-  <si>
-    <t>80 €/чел</t>
-  </si>
-  <si>
-    <t>Meet &amp; Greet у рукава + дип-коридор + портье багажа + Concordia VIP Lounge</t>
-  </si>
-  <si>
-    <t>Онлайн картой на сайте JOUMPA</t>
-  </si>
-  <si>
-    <t>Бронировать за 5 дней до прилета</t>
-  </si>
-  <si>
-    <t>Электронная виза e-VOA (B1)</t>
-  </si>
-  <si>
-    <t>Иммиграционная служба Индонезии</t>
-  </si>
-  <si>
-    <t>500 000 IDR/чел</t>
-  </si>
-  <si>
-    <t>32 €/чел</t>
-  </si>
-  <si>
-    <t>Въездная туристическая виза на 30 дней</t>
-  </si>
-  <si>
-    <t>Онлайн на официальном госпортале</t>
-  </si>
-  <si>
-    <t>Оформить за 3-5 дней организатором</t>
-  </si>
-  <si>
-    <t>Туристический налог Love Bali</t>
-  </si>
-  <si>
-    <t>Правительство провинции Бали</t>
-  </si>
-  <si>
-    <t>150 000 IDR/чел</t>
-  </si>
-  <si>
-    <t>9 €/чел</t>
-  </si>
-  <si>
-    <t>Официальный туристический сбор</t>
-  </si>
-  <si>
-    <t>Онлайн на сайте lovebali.baliprov.go.id</t>
-  </si>
-  <si>
-    <t>Оплатить заранее, QR-код в телефон</t>
-  </si>
-  <si>
-    <t>Таможенная декларация e-CD</t>
-  </si>
-  <si>
-    <t>Таможенная служба Индонезии (Beacukai)</t>
-  </si>
-  <si>
-    <t>Электронная декларация на багаж</t>
-  </si>
-  <si>
-    <t>Бесплатно онлайн за 3 дня</t>
-  </si>
-  <si>
-    <t>Заполнить 1 общий QR-код на 2 чел</t>
-  </si>
-  <si>
-    <t>Автомобиль с водителем (Путу)</t>
-  </si>
-  <si>
-    <t>Частный контракт (Toyota Innova Zenix)</t>
-  </si>
-  <si>
-    <t>1 100 000 IDR/день</t>
-  </si>
-  <si>
-    <t>65 €/день</t>
-  </si>
-  <si>
-    <t>WhatsApp Путу</t>
-  </si>
-  <si>
-    <t>Автомобиль + бензин + водитель 24/7</t>
-  </si>
-  <si>
-    <t>Наличными IDR Путу</t>
-  </si>
-  <si>
-    <t>Личный проверенный водитель</t>
-  </si>
-  <si>
-    <t>Отель Plataran Ubud Hotel 4★+</t>
-  </si>
-  <si>
-    <t>Plataran Hotels &amp; Resorts</t>
-  </si>
-  <si>
-    <t>5 500 000 IDR/ночь</t>
-  </si>
-  <si>
-    <t>320 €/ночь</t>
-  </si>
-  <si>
-    <t>Deluxe Suite с видом на террасы + завтрак</t>
-  </si>
-  <si>
-    <t>Прямое бронирование / Agoda VIP</t>
-  </si>
-  <si>
-    <t>Камерный бутик в садах Убуда</t>
-  </si>
-  <si>
-    <t>Глэмпинг Toteme Kintamani 4★+</t>
-  </si>
-  <si>
-    <t>Toteme Glamping &amp; Hot Spring</t>
-  </si>
-  <si>
-    <t>3 800 000 IDR/ночь</t>
-  </si>
-  <si>
-    <t>220 €/ночь</t>
-  </si>
-  <si>
-    <t>Шатер с термальной минеральной ванной на террасе</t>
+    <t>Сьют с индивидуальной термальной купелью</t>
   </si>
   <si>
     <t>Прямой сайт / WhatsApp</t>
   </si>
   <si>
-    <t>Вулканические горячие источники 38-40°C</t>
-  </si>
-  <si>
-    <t>Приватная вилла у пляжа (Санур)</t>
-  </si>
-  <si>
-    <t>Бутик-коллекция Sanur Beachfront</t>
+    <t>Вулканические минеральные ванны 38-40°C</t>
+  </si>
+  <si>
+    <t>Приватная вилла у океана (Санур)</t>
+  </si>
+  <si>
+    <t>Коллекция вилл первой линии</t>
   </si>
   <si>
     <t>5 800 000 IDR/ночь</t>
@@ -1059,7 +1158,7 @@
     <t>340 €/ночь</t>
   </si>
   <si>
-    <t>Бутик-вилла у кромки воды</t>
+    <t>Вилла у кромки воды</t>
   </si>
   <si>
     <t>Вилла с садом у лагуны + завтраки от шефа</t>
@@ -1176,10 +1275,10 @@
     <t>Реликтовые древовидные папоротники и орхидеи</t>
   </si>
   <si>
-    <t>Спа Padma в Plataran</t>
-  </si>
-  <si>
-    <t>Padma Spa Plataran</t>
+    <t>Спа-ритуал в садах Убуда</t>
+  </si>
+  <si>
+    <t>Спа-санктуарий Убуда</t>
   </si>
   <si>
     <t>1 600 000 IDR/чел</t>
@@ -1188,13 +1287,13 @@
     <t>95 €/чел</t>
   </si>
   <si>
-    <t>https://www.plataran.com</t>
+    <t>Спа-комплекс в садах</t>
   </si>
   <si>
     <t>3-часовой ритуал: ванна роз, массаж, скраб Lulur</t>
   </si>
   <si>
-    <t>В отеле Plataran</t>
+    <t>На месте</t>
   </si>
   <si>
     <t>Королевский балийский уход</t>
@@ -1219,6 +1318,75 @@
   </si>
   <si>
     <t>Сакральная геометрия, акустический резонанс через воду прямо в ткани тела</t>
+  </si>
+  <si>
+    <t>Вудкарвинг (Сакральная резьба)</t>
+  </si>
+  <si>
+    <t>Династические мастера деревни Мас</t>
+  </si>
+  <si>
+    <t>Донат / 0 IDR вход</t>
+  </si>
+  <si>
+    <t>Мастерские деревни Мас (Джаньяр)</t>
+  </si>
+  <si>
+    <t>Демонстрация вековых техник резьбы по дереву</t>
+  </si>
+  <si>
+    <t>На месте при покупке скульптур</t>
+  </si>
+  <si>
+    <t>Потомственные резчики сандала и тика</t>
+  </si>
+  <si>
+    <t>Батик Tulis (Роспись воском)</t>
+  </si>
+  <si>
+    <t>Аутентичные студии Тохпати и Убуда</t>
+  </si>
+  <si>
+    <t>450 000 IDR/чел</t>
+  </si>
+  <si>
+    <t>27 €/чел</t>
+  </si>
+  <si>
+    <t>Традиционные студии батика Бали</t>
+  </si>
+  <si>
+    <t>Индивидуальный мастер-класс росписи кантингом + материалы</t>
+  </si>
+  <si>
+    <t>В студии картой или наличными</t>
+  </si>
+  <si>
+    <t>Создание авторского шелкового платка</t>
+  </si>
+  <si>
+    <t>Урок балийского гамелана</t>
+  </si>
+  <si>
+    <t>Музыкальное сообщество Секехе (Убуд)</t>
+  </si>
+  <si>
+    <t>500 000 IDR / 2 чел</t>
+  </si>
+  <si>
+    <t>30 € на двоих</t>
+  </si>
+  <si>
+    <t>Деревенские павильоны балийской музыки</t>
+  </si>
+  <si>
+    <t>1 час практики игры на бронзовых металлофонах ганса и гонгах</t>
+  </si>
+  <si>
+    <t>Наличными учителю</t>
+  </si>
+  <si>
+    <t>Глубокая звуковая медитация и полиритм</t>
   </si>
   <si>
     <t>The Blanco Renaissance Museum</t>
@@ -2659,91 +2827,169 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="0"/>
-      <c r="B34" s="0"/>
-      <c r="C34" s="0"/>
-      <c r="D34" s="0"/>
-      <c r="E34" s="0"/>
-      <c r="F34" s="0"/>
-      <c r="G34" s="0"/>
-      <c r="H34" s="0"/>
+      <c r="A34" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>111</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="3">
+      <c r="A35" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B35" t="s" s="3">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s" s="3">
+      <c r="B35" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D35" s="0">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0"/>
+      <c r="B37" s="0"/>
+      <c r="C37" s="0"/>
+      <c r="D37" s="0"/>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0"/>
+      <c r="G37" s="0"/>
+      <c r="H37" s="0"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="B38" t="s" s="3">
+        <v>117</v>
+      </c>
+      <c r="C38" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D38" s="3">
         <v>7188</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E38" s="3">
         <v>4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F38" s="3">
         <v>81800000</v>
       </c>
-      <c r="G35" t="s" s="3">
-        <v>110</v>
-      </c>
-      <c r="H35" t="s" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="7">
-        <v>112</v>
-      </c>
-      <c r="B36" t="s" s="7">
-        <v>113</v>
-      </c>
-      <c r="C36" t="s" s="7">
+      <c r="G38" t="s" s="3">
+        <v>118</v>
+      </c>
+      <c r="H38" t="s" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="7">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s" s="7">
+        <v>121</v>
+      </c>
+      <c r="C39" t="s" s="7">
         <v>29</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D39" s="7">
         <v>2512</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E39" s="7">
         <v>7200</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F39" s="7">
         <v>122700000</v>
       </c>
-      <c r="G36" t="s" s="7">
-        <v>114</v>
-      </c>
-      <c r="H36" t="s" s="7">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C37" t="s" s="2">
+      <c r="G39" t="s" s="7">
+        <v>122</v>
+      </c>
+      <c r="H39" t="s" s="7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D40" s="2">
         <v>9700</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E40" s="2">
         <v>12000</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F40" s="2">
         <v>204500000</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>119</v>
+      <c r="G40" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2755,7 +3001,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2767,7 +3013,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2798,16 +3044,16 @@
         <v>4</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s" s="1">
         <v>6</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H4" t="s" s="1">
         <v>9</v>
@@ -2815,10 +3061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>20</v>
@@ -2833,18 +3079,18 @@
         <v>11000000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>20</v>
@@ -2859,21 +3105,21 @@
         <v>11600000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s" s="5">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s" s="5">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D7" s="5">
         <v>3700</v>
@@ -2885,10 +3131,10 @@
         <v>22600000</v>
       </c>
       <c r="G7" t="s" s="5">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H7" t="s" s="5">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -2896,10 +3142,10 @@
         <v>27</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D8" s="0">
         <v>400</v>
@@ -2911,10 +3157,10 @@
         <v>5500000</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
@@ -2922,10 +3168,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D9" s="0">
         <v>100</v>
@@ -2937,10 +3183,10 @@
         <v>1800000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -2948,10 +3194,10 @@
         <v>27</v>
       </c>
       <c r="B10" t="s" s="5">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s" s="5">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D10" s="5">
         <v>500</v>
@@ -2963,7 +3209,7 @@
         <v>7300000</v>
       </c>
       <c r="G10" t="s" s="5">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H10" t="s" s="5">
         <v>37</v>
@@ -2974,7 +3220,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>40</v>
@@ -2989,10 +3235,10 @@
         <v>2700000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
@@ -3015,7 +3261,7 @@
         <v>1000000</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>45</v>
@@ -3041,7 +3287,7 @@
         <v>300000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>48</v>
@@ -3052,7 +3298,7 @@
         <v>38</v>
       </c>
       <c r="B14" t="s" s="5">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s" s="5">
         <v>40</v>
@@ -3067,7 +3313,7 @@
         <v>4000000</v>
       </c>
       <c r="G14" t="s" s="5">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H14" t="s" s="5">
         <v>51</v>
@@ -3075,10 +3321,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>40</v>
@@ -3093,15 +3339,15 @@
         <v>2550000</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>55</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>56</v>
@@ -3119,18 +3365,18 @@
         <v>1500000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>40</v>
@@ -3145,7 +3391,7 @@
         <v>850000</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>62</v>
@@ -3153,10 +3399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="5">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s" s="5">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s" s="5">
         <v>64</v>
@@ -3171,7 +3417,7 @@
         <v>4900000</v>
       </c>
       <c r="G18" t="s" s="5">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H18" t="s" s="5">
         <v>66</v>
@@ -3182,7 +3428,7 @@
         <v>67</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>40</v>
@@ -3197,7 +3443,7 @@
         <v>1800000</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>70</v>
@@ -3208,7 +3454,7 @@
         <v>67</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>40</v>
@@ -3223,10 +3469,10 @@
         <v>850000</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21">
@@ -3234,7 +3480,7 @@
         <v>67</v>
       </c>
       <c r="B21" t="s" s="5">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C21" t="s" s="5">
         <v>64</v>
@@ -3249,10 +3495,10 @@
         <v>2650000</v>
       </c>
       <c r="G21" t="s" s="5">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22">
@@ -3260,10 +3506,10 @@
         <v>80</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D22" s="0">
         <v>150</v>
@@ -3275,10 +3521,10 @@
         <v>2550000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
@@ -3286,7 +3532,7 @@
         <v>80</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>40</v>
@@ -3301,10 +3547,10 @@
         <v>4250000</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24">
@@ -3312,7 +3558,7 @@
         <v>80</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>40</v>
@@ -3327,10 +3573,10 @@
         <v>3400000</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25">
@@ -3338,7 +3584,7 @@
         <v>80</v>
       </c>
       <c r="B25" t="s" s="5">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s" s="5">
         <v>64</v>
@@ -3353,7 +3599,7 @@
         <v>10200000</v>
       </c>
       <c r="G25" t="s" s="5">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s" s="5">
         <v>88</v>
@@ -3364,7 +3610,7 @@
         <v>89</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>95</v>
@@ -3468,10 +3714,10 @@
         <v>89</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D30" s="0">
         <v>0</v>
@@ -3490,91 +3736,169 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-      <c r="C31" s="0"/>
-      <c r="D31" s="0"/>
-      <c r="E31" s="0"/>
-      <c r="F31" s="0"/>
-      <c r="G31" s="0"/>
-      <c r="H31" s="0"/>
+      <c r="A31" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>111</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="s" s="3">
+      <c r="A32" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="B32" t="s" s="3">
-        <v>182</v>
-      </c>
-      <c r="C32" t="s" s="3">
-        <v>137</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="B32" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+      <c r="C34" s="0"/>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="B35" t="s" s="3">
+        <v>191</v>
+      </c>
+      <c r="C35" t="s" s="3">
+        <v>145</v>
+      </c>
+      <c r="D35" s="3">
         <v>5398</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E35" s="3">
         <v>3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F35" s="3">
         <v>57950000</v>
       </c>
-      <c r="G32" t="s" s="3">
-        <v>183</v>
-      </c>
-      <c r="H32" t="s" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="7">
-        <v>112</v>
-      </c>
-      <c r="B33" t="s" s="7">
-        <v>113</v>
-      </c>
-      <c r="C33" t="s" s="7">
-        <v>137</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="G35" t="s" s="3">
+        <v>192</v>
+      </c>
+      <c r="H35" t="s" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="7">
+        <v>120</v>
+      </c>
+      <c r="B36" t="s" s="7">
+        <v>121</v>
+      </c>
+      <c r="C36" t="s" s="7">
+        <v>145</v>
+      </c>
+      <c r="D36" s="7">
         <v>2102</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E36" s="7">
         <v>5100</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F36" s="7">
         <v>86925000</v>
       </c>
-      <c r="G33" t="s" s="7">
-        <v>184</v>
-      </c>
-      <c r="H33" t="s" s="7">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="G36" t="s" s="7">
+        <v>193</v>
+      </c>
+      <c r="H36" t="s" s="7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D37" s="2">
         <v>7500</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E37" s="2">
         <v>8500</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F37" s="2">
         <v>144875000</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>186</v>
+      <c r="G37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3586,7 +3910,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3598,7 +3922,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3620,314 +3944,392 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>293</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>295</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>294</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3939,7 +4341,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3951,7 +4353,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3973,548 +4375,626 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>292</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>299</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>306</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>313</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>47</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>318</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>326</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>238</v>
+        <v>362</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>333</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>246</v>
+        <v>370</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>340</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>348</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>354</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>361</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>368</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>375</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>383</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>386</v>
+        <v>419</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>391</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>392</v>
+        <v>425</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>398</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>309</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>310</v>
+        <v>397</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>404</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>309</v>
+        <v>441</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>310</v>
+        <v>442</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>409</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>309</v>
+        <v>449</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>403</v>
+        <v>453</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>414</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>417</v>
+        <v>340</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>422</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>425</v>
+        <v>340</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>418</v>
+        <v>341</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>427</v>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>466</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>467</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>469</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>471</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>472</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>473</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>476</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>479</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>481</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>475</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>482</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4526,7 +5006,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4538,7 +5018,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -4566,33 +5046,33 @@
         <v>3</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>431</v>
+        <v>487</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>432</v>
+        <v>488</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>433</v>
+        <v>489</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>434</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>436</v>
+        <v>492</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="D5" s="0">
         <v>1050</v>
@@ -4604,21 +5084,21 @@
         <v>17850000</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>439</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>440</v>
+        <v>496</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="D6" s="0">
         <v>1150</v>
@@ -4630,21 +5110,21 @@
         <v>19550000</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>442</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>443</v>
+        <v>499</v>
       </c>
       <c r="C7" t="s" s="9">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="D7" s="9">
         <v>1100</v>
@@ -4656,21 +5136,21 @@
         <v>18700000</v>
       </c>
       <c r="G7" t="s" s="9">
-        <v>444</v>
+        <v>500</v>
       </c>
       <c r="H7" t="s" s="9">
-        <v>445</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="5">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="B8" t="s" s="5">
-        <v>446</v>
+        <v>502</v>
       </c>
       <c r="C8" t="s" s="5">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="D8" s="5">
         <v>1050</v>
@@ -4682,21 +5162,21 @@
         <v>17850000</v>
       </c>
       <c r="G8" t="s" s="5">
-        <v>447</v>
+        <v>503</v>
       </c>
       <c r="H8" t="s" s="5">
-        <v>448</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D9" s="0">
         <v>90</v>
@@ -4708,21 +5188,21 @@
         <v>1500000</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>452</v>
+        <v>508</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>453</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>454</v>
+        <v>510</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>455</v>
+        <v>511</v>
       </c>
       <c r="D10" s="0">
         <v>64</v>
@@ -4734,21 +5214,21 @@
         <v>1000000</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>452</v>
+        <v>508</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>456</v>
+        <v>512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="D11" s="0">
         <v>9</v>
@@ -4760,21 +5240,21 @@
         <v>150000</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>459</v>
+        <v>515</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>460</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="5">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B12" t="s" s="5">
-        <v>461</v>
+        <v>517</v>
       </c>
       <c r="C12" t="s" s="5">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D12" s="5">
         <v>99</v>
@@ -4786,21 +5266,21 @@
         <v>1650000</v>
       </c>
       <c r="G12" t="s" s="5">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="H12" t="s" s="5">
-        <v>463</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>465</v>
+        <v>521</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="D13" s="0">
         <v>470</v>
@@ -4812,21 +5292,21 @@
         <v>8000000</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>468</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>465</v>
+        <v>521</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="D14" s="0">
         <v>470</v>
@@ -4838,21 +5318,21 @@
         <v>8000000</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>470</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="5">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="B15" t="s" s="5">
-        <v>471</v>
+        <v>527</v>
       </c>
       <c r="C15" t="s" s="5">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="D15" s="5">
         <v>940</v>
@@ -4864,21 +5344,21 @@
         <v>16000000</v>
       </c>
       <c r="G15" t="s" s="5">
-        <v>473</v>
+        <v>529</v>
       </c>
       <c r="H15" t="s" s="5">
-        <v>474</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="D16" s="0">
         <v>190</v>
@@ -4890,21 +5370,21 @@
         <v>3200000</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>477</v>
+        <v>533</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>478</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>479</v>
+        <v>535</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="D17" s="0">
         <v>35</v>
@@ -4916,21 +5396,21 @@
         <v>600000</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>481</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="5">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="B18" t="s" s="5">
-        <v>482</v>
+        <v>538</v>
       </c>
       <c r="C18" t="s" s="5">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="D18" s="5">
         <v>225</v>
@@ -4942,21 +5422,21 @@
         <v>3800000</v>
       </c>
       <c r="G18" t="s" s="5">
-        <v>483</v>
+        <v>539</v>
       </c>
       <c r="H18" t="s" s="5">
-        <v>484</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D19" s="0">
         <v>1060</v>
@@ -4968,21 +5448,21 @@
         <v>18000000</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>488</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D20" s="0">
         <v>70</v>
@@ -4994,21 +5474,21 @@
         <v>1200000</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>490</v>
+        <v>546</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>491</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="5">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="B21" t="s" s="5">
-        <v>492</v>
+        <v>548</v>
       </c>
       <c r="C21" t="s" s="5">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D21" s="5">
         <v>1130</v>
@@ -5020,21 +5500,21 @@
         <v>19200000</v>
       </c>
       <c r="G21" t="s" s="5">
-        <v>493</v>
+        <v>549</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>494</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="D22" s="0">
         <v>35</v>
@@ -5046,21 +5526,21 @@
         <v>600000</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>498</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>499</v>
+        <v>555</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="D23" s="0">
         <v>140</v>
@@ -5072,21 +5552,21 @@
         <v>2400000</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>501</v>
+        <v>557</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>502</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="5">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="B24" t="s" s="5">
-        <v>503</v>
+        <v>559</v>
       </c>
       <c r="C24" t="s" s="5">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D24" s="5">
         <v>175</v>
@@ -5098,10 +5578,10 @@
         <v>3000000</v>
       </c>
       <c r="G24" t="s" s="5">
-        <v>504</v>
+        <v>560</v>
       </c>
       <c r="H24" t="s" s="5">
-        <v>505</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25">
@@ -5116,13 +5596,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="7">
-        <v>506</v>
+        <v>562</v>
       </c>
       <c r="B26" t="s" s="7">
+        <v>563</v>
+      </c>
+      <c r="C26" t="s" s="7">
         <v>507</v>
-      </c>
-      <c r="C26" t="s" s="7">
-        <v>451</v>
       </c>
       <c r="D26" s="7">
         <v>3619</v>
@@ -5134,21 +5614,21 @@
         <v>61500000</v>
       </c>
       <c r="G26" t="s" s="7">
-        <v>508</v>
+        <v>564</v>
       </c>
       <c r="H26" t="s" s="7">
-        <v>509</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="7">
-        <v>510</v>
+        <v>566</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>511</v>
+        <v>567</v>
       </c>
       <c r="C27" t="s" s="7">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="D27" s="7">
         <v>6369</v>
@@ -5160,10 +5640,10 @@
         <v>108250000</v>
       </c>
       <c r="G27" t="s" s="7">
-        <v>512</v>
+        <v>568</v>
       </c>
       <c r="H27" t="s" s="7">
-        <v>513</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
@@ -5175,7 +5655,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>514</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5187,7 +5667,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>515</v>
+        <v>571</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -5209,33 +5689,33 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>516</v>
+        <v>572</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>517</v>
+        <v>573</v>
       </c>
       <c r="C4" t="s" s="1">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>519</v>
+        <v>575</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="F4" t="s" s="1">
-        <v>521</v>
+        <v>577</v>
       </c>
       <c r="G4" t="s" s="1">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>523</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>524</v>
+        <v>580</v>
       </c>
       <c r="B5" s="0">
         <v>105</v>
@@ -5250,18 +5730,18 @@
         <v>530000</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>525</v>
+        <v>581</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>526</v>
+        <v>582</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>527</v>
+        <v>583</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>528</v>
+        <v>584</v>
       </c>
       <c r="B6" s="0">
         <v>25</v>
@@ -5276,18 +5756,18 @@
         <v>200000</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>529</v>
+        <v>585</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>530</v>
+        <v>586</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>531</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="B7" s="0">
         <v>165</v>
@@ -5302,18 +5782,18 @@
         <v>3600000</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>533</v>
+        <v>589</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>534</v>
+        <v>590</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>535</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>536</v>
+        <v>592</v>
       </c>
       <c r="B8" s="0">
         <v>55</v>
@@ -5328,18 +5808,18 @@
         <v>950000</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>537</v>
+        <v>593</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>539</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>540</v>
+        <v>596</v>
       </c>
       <c r="B9" s="0">
         <v>70</v>
@@ -5354,18 +5834,18 @@
         <v>1600000</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>541</v>
+        <v>597</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>542</v>
+        <v>598</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>543</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="B10" s="0">
         <v>40</v>
@@ -5380,13 +5860,13 @@
         <v>700000</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>547</v>
+        <v>603</v>
       </c>
     </row>
     <row r="11">
@@ -5401,7 +5881,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="7">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B12" s="7">
         <v>460</v>
@@ -5416,13 +5896,13 @@
         <v>7580000</v>
       </c>
       <c r="F12" t="s" s="7">
-        <v>549</v>
+        <v>605</v>
       </c>
       <c r="G12" t="s" s="7">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="H12" t="s" s="7">
-        <v>551</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13">
@@ -5437,7 +5917,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -5449,7 +5929,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="4">
-        <v>553</v>
+        <v>609</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -5461,7 +5941,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>554</v>
+        <v>610</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5473,7 +5953,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5485,7 +5965,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5497,7 +5977,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>557</v>
+        <v>613</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>

--- a/Bali Sanctuary Смета 4 звезды.xlsx
+++ b/Bali Sanctuary Смета 4 звезды.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="860">
   <si>
     <t>ПОЛНАЯ ПРОГРАММА РЕТРИТА «BALI SANCTUARY» ПО ДНЯМ (7 ДНЕЙ / 6 НОЧЕЙ)</t>
   </si>
@@ -1237,16 +1237,16 @@
     <t>Включено</t>
   </si>
   <si>
-    <t>Авторская практика мастера (йогин 20+ лет)</t>
-  </si>
-  <si>
-    <t>Авторская fine-art портретная фотосъемка на закатном побережье</t>
+    <t>Авторская практика мастера (йогин и энергопрактик с 20-летним стажем)</t>
+  </si>
+  <si>
+    <t>Авторская сессия алхимического портрета на закатном побережье</t>
   </si>
   <si>
     <t>1 сессия</t>
   </si>
   <si>
-    <t>Fine-art фотосессия для гостий от Валерия</t>
+    <t>Валерий Латыпов: алхимический портрет (съемки Peter Gabriel, Depeche Mode, Dubai Opera)</t>
   </si>
   <si>
     <t>Интеллектуальный салон: встреча с д-ром Лоуренсом Блэром («Ring of Fire»)</t>
@@ -1255,7 +1255,7 @@
     <t>1 встреча</t>
   </si>
   <si>
-    <t>Эксклюзивный доступ автора (35 лет экспедиций)</t>
+    <t>Эксклюзивный доступ автора (35 лет экспедиций по Индонезии)</t>
   </si>
   <si>
     <t>Частный визит в резиденцию Брюса Карпентера (сакральные крисы и маски)</t>
@@ -1264,7 +1264,7 @@
     <t>1 визит</t>
   </si>
   <si>
-    <t>Эксперт Christie's / автор монографий</t>
+    <t>Эксперт Christie's / автор фундаментальных монографий</t>
   </si>
   <si>
     <t>Арт-маршрут Убуда: музей Бланко, Neka Art Museum (павильон крисов), ARMA</t>
@@ -1276,10 +1276,10 @@
     <t>Билеты включены в общую сакральную программу</t>
   </si>
   <si>
-    <t>Непрерывное кураторство 24/7 (индонезийский и английский языки)</t>
-  </si>
-  <si>
-    <t>Личное ведение без посредников</t>
+    <t>Непрерывное кураторство 24/7 (Bahasa Indonesia, 2+ года жизни на Бали)</t>
+  </si>
+  <si>
+    <t>Личное ведение мастера (ученик Чёгьяла Намкая Норбу, благословение короля Мустанга)</t>
   </si>
   <si>
     <t>8. Живые ремесла</t>
@@ -1526,12 +1526,6 @@
   </si>
   <si>
     <t>Звукотерапия тибетскими чашами от Валерия на вилле</t>
-  </si>
-  <si>
-    <t>Авторская практика мастера</t>
-  </si>
-  <si>
-    <t>Непрерывное кураторство 24/7 (индонезийский язык)</t>
   </si>
   <si>
     <t>Все прямые расходы на 2 гостей (резиденции 4★+, авто, спа, храмы, еда, VIP)</t>
@@ -7355,7 +7349,7 @@
         <v>406</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>504</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34">
@@ -7441,7 +7435,7 @@
         <v>403</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>459</v>
@@ -7547,7 +7541,7 @@
         <v>430</v>
       </c>
       <c r="B43" t="s" s="3">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C43" t="s" s="3">
         <v>459</v>
@@ -7562,7 +7556,7 @@
         <v>57950000</v>
       </c>
       <c r="G43" t="s" s="3">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H43" t="s" s="3">
         <v>433</v>
@@ -7589,7 +7583,7 @@
         <v>86925000</v>
       </c>
       <c r="G45" t="s" s="7">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H45" t="s" s="7">
         <v>437</v>
@@ -7616,10 +7610,10 @@
         <v>144875000</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -7641,7 +7635,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7653,7 +7647,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="8">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -7666,420 +7660,420 @@
     <row r="3" ht="16" customHeight="1"/>
     <row r="4">
       <c r="A4" t="s" s="1">
+        <v>511</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>512</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>513</v>
       </c>
-      <c r="B4" t="s" s="1">
+      <c r="D4" t="s" s="1">
         <v>514</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="E4" t="s" s="1">
         <v>515</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="F4" t="s" s="1">
         <v>516</v>
       </c>
-      <c r="E4" t="s" s="1">
+      <c r="G4" t="s" s="1">
         <v>517</v>
       </c>
-      <c r="F4" t="s" s="1">
+      <c r="H4" t="s" s="1">
         <v>518</v>
-      </c>
-      <c r="G4" t="s" s="1">
-        <v>519</v>
-      </c>
-      <c r="H4" t="s" s="1">
-        <v>520</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1"/>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>519</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>521</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="D6" t="s" s="0">
         <v>522</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="E6" t="s" s="0">
         <v>523</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="F6" t="s" s="0">
         <v>524</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="G6" t="s" s="0">
         <v>525</v>
       </c>
-      <c r="F6" t="s" s="0">
+      <c r="H6" t="s" s="0">
         <v>526</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>527</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>528</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>528</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>529</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="D7" t="s" s="0">
         <v>530</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="E7" t="s" s="0">
         <v>531</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="F7" t="s" s="0">
         <v>532</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="G7" t="s" s="0">
         <v>533</v>
       </c>
-      <c r="F7" t="s" s="0">
+      <c r="H7" t="s" s="0">
         <v>534</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>535</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>536</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>535</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>536</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>537</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="D8" t="s" s="0">
         <v>538</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="E8" t="s" s="0">
         <v>539</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="F8" t="s" s="0">
         <v>540</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="G8" t="s" s="0">
         <v>541</v>
       </c>
-      <c r="F8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>542</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>543</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>543</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="C9" t="s" s="0">
         <v>545</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="D9" t="s" s="0">
         <v>546</v>
       </c>
-      <c r="C9" t="s" s="0">
+      <c r="E9" t="s" s="0">
         <v>547</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="F9" t="s" s="0">
         <v>548</v>
       </c>
-      <c r="E9" t="s" s="0">
+      <c r="G9" t="s" s="0">
         <v>549</v>
       </c>
-      <c r="F9" t="s" s="0">
+      <c r="H9" t="s" s="0">
         <v>550</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>551</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>551</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="C10" t="s" s="0">
         <v>553</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="D10" t="s" s="0">
         <v>554</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="E10" t="s" s="0">
         <v>555</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="F10" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="E10" t="s" s="0">
+      <c r="G10" t="s" s="0">
         <v>557</v>
       </c>
-      <c r="F10" t="s" s="0">
+      <c r="H10" t="s" s="0">
         <v>558</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>559</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>560</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="C11" t="s" s="0">
         <v>561</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="D11" t="s" s="0">
         <v>562</v>
       </c>
-      <c r="C11" t="s" s="0">
+      <c r="E11" t="s" s="0">
         <v>563</v>
       </c>
-      <c r="D11" t="s" s="0">
+      <c r="F11" t="s" s="0">
         <v>564</v>
       </c>
-      <c r="E11" t="s" s="0">
+      <c r="G11" t="s" s="0">
         <v>565</v>
       </c>
-      <c r="F11" t="s" s="0">
+      <c r="H11" t="s" s="0">
         <v>566</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>567</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>568</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>567</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>568</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>569</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="D12" t="s" s="0">
         <v>570</v>
       </c>
-      <c r="C12" t="s" s="0">
+      <c r="E12" t="s" s="0">
         <v>571</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>572</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="G12" t="s" s="0">
         <v>573</v>
       </c>
-      <c r="F12" t="s" s="0">
+      <c r="H12" t="s" s="0">
         <v>574</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>575</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>577</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="D13" t="s" s="0">
         <v>578</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="E13" t="s" s="0">
         <v>579</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>580</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="G13" t="s" s="0">
         <v>581</v>
       </c>
-      <c r="F13" t="s" s="0">
+      <c r="H13" t="s" s="0">
         <v>582</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>583</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>584</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
+        <v>583</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>585</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="D14" t="s" s="0">
         <v>586</v>
       </c>
-      <c r="C14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>587</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>588</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="G14" t="s" s="0">
         <v>589</v>
       </c>
-      <c r="F14" t="s" s="0">
+      <c r="H14" t="s" s="0">
         <v>590</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>591</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>592</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
+        <v>591</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="C15" t="s" s="0">
         <v>593</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="D15" t="s" s="0">
         <v>594</v>
       </c>
-      <c r="C15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>595</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>596</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="G15" t="s" s="0">
         <v>597</v>
       </c>
-      <c r="F15" t="s" s="0">
+      <c r="H15" t="s" s="0">
         <v>598</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>599</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>599</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>600</v>
+      </c>
+      <c r="C16" t="s" s="0">
         <v>601</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="D16" t="s" s="0">
         <v>602</v>
       </c>
-      <c r="C16" t="s" s="0">
+      <c r="E16" t="s" s="0">
         <v>603</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>604</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="G16" t="s" s="0">
         <v>605</v>
       </c>
-      <c r="F16" t="s" s="0">
+      <c r="H16" t="s" s="0">
         <v>606</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>607</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>608</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>607</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="C17" t="s" s="0">
         <v>609</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="D17" t="s" s="0">
         <v>610</v>
       </c>
-      <c r="C17" t="s" s="0">
+      <c r="E17" t="s" s="0">
         <v>611</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>612</v>
       </c>
-      <c r="E17" t="s" s="0">
+      <c r="G17" t="s" s="0">
         <v>613</v>
       </c>
-      <c r="F17" t="s" s="0">
+      <c r="H17" t="s" s="0">
         <v>614</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>615</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>616</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>615</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>616</v>
+      </c>
+      <c r="C18" t="s" s="0">
         <v>617</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="D18" t="s" s="0">
         <v>618</v>
       </c>
-      <c r="C18" t="s" s="0">
+      <c r="E18" t="s" s="0">
         <v>619</v>
       </c>
-      <c r="D18" t="s" s="0">
+      <c r="F18" t="s" s="0">
         <v>620</v>
       </c>
-      <c r="E18" t="s" s="0">
+      <c r="G18" t="s" s="0">
         <v>621</v>
       </c>
-      <c r="F18" t="s" s="0">
+      <c r="H18" t="s" s="0">
         <v>622</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>623</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>624</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>623</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>624</v>
+      </c>
+      <c r="C19" t="s" s="0">
         <v>625</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="D19" t="s" s="0">
         <v>626</v>
       </c>
-      <c r="C19" t="s" s="0">
+      <c r="E19" t="s" s="0">
         <v>627</v>
       </c>
-      <c r="D19" t="s" s="0">
+      <c r="F19" t="s" s="0">
         <v>628</v>
       </c>
-      <c r="E19" t="s" s="0">
+      <c r="G19" t="s" s="0">
         <v>629</v>
       </c>
-      <c r="F19" t="s" s="0">
+      <c r="H19" t="s" s="0">
         <v>630</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>631</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>632</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1"/>
     <row r="21">
       <c r="A21" t="s" s="7">
+        <v>631</v>
+      </c>
+      <c r="B21" t="s" s="7">
+        <v>632</v>
+      </c>
+      <c r="C21" t="s" s="7">
         <v>633</v>
       </c>
-      <c r="B21" t="s" s="7">
+      <c r="D21" t="s" s="7">
         <v>634</v>
       </c>
-      <c r="C21" t="s" s="7">
+      <c r="E21" t="s" s="7">
         <v>635</v>
       </c>
-      <c r="D21" t="s" s="7">
+      <c r="F21" t="s" s="7">
         <v>636</v>
       </c>
-      <c r="E21" t="s" s="7">
+      <c r="G21" t="s" s="7">
         <v>637</v>
       </c>
-      <c r="F21" t="s" s="7">
+      <c r="H21" t="s" s="7">
         <v>638</v>
-      </c>
-      <c r="G21" t="s" s="7">
-        <v>639</v>
-      </c>
-      <c r="H21" t="s" s="7">
-        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -8101,7 +8095,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8113,7 +8107,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8126,446 +8120,446 @@
     <row r="3" ht="16" customHeight="1"/>
     <row r="4">
       <c r="A4" t="s" s="1">
+        <v>641</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>642</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>643</v>
       </c>
-      <c r="B4" t="s" s="1">
+      <c r="D4" t="s" s="1">
         <v>644</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="E4" t="s" s="1">
         <v>645</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="F4" t="s" s="1">
         <v>646</v>
       </c>
-      <c r="E4" t="s" s="1">
+      <c r="G4" t="s" s="1">
         <v>647</v>
       </c>
-      <c r="F4" t="s" s="1">
+      <c r="H4" t="s" s="1">
         <v>648</v>
-      </c>
-      <c r="G4" t="s" s="1">
-        <v>649</v>
-      </c>
-      <c r="H4" t="s" s="1">
-        <v>650</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1"/>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>649</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>650</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>651</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>522</v>
-      </c>
-      <c r="C6" t="s" s="0">
+      <c r="E6" t="s" s="0">
         <v>652</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="F6" t="s" s="0">
         <v>653</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="G6" t="s" s="0">
         <v>654</v>
       </c>
-      <c r="F6" t="s" s="0">
+      <c r="H6" t="s" s="0">
         <v>655</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>656</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>657</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>656</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>528</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>657</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>658</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>530</v>
-      </c>
-      <c r="C7" t="s" s="0">
+      <c r="E7" t="s" s="0">
         <v>659</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="F7" t="s" s="0">
         <v>660</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="G7" t="s" s="0">
         <v>661</v>
       </c>
-      <c r="F7" t="s" s="0">
+      <c r="H7" t="s" s="0">
         <v>662</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>663</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>361</v>
       </c>
       <c r="E8" t="s" s="0">
+        <v>665</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>666</v>
+      </c>
+      <c r="G8" t="s" s="0">
         <v>667</v>
       </c>
-      <c r="F8" t="s" s="0">
+      <c r="H8" t="s" s="0">
         <v>668</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>669</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>670</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>670</v>
+      </c>
+      <c r="D9" t="s" s="0">
         <v>671</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>546</v>
-      </c>
-      <c r="C9" t="s" s="0">
+      <c r="E9" t="s" s="0">
         <v>672</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="F9" t="s" s="0">
         <v>673</v>
       </c>
-      <c r="E9" t="s" s="0">
+      <c r="G9" t="s" s="0">
         <v>674</v>
       </c>
-      <c r="F9" t="s" s="0">
+      <c r="H9" t="s" s="0">
         <v>675</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>676</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>677</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
+        <v>676</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>677</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>658</v>
+      </c>
+      <c r="E10" t="s" s="0">
         <v>678</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>554</v>
-      </c>
-      <c r="C10" t="s" s="0">
+      <c r="F10" t="s" s="0">
         <v>679</v>
       </c>
-      <c r="D10" t="s" s="0">
-        <v>660</v>
-      </c>
-      <c r="E10" t="s" s="0">
+      <c r="G10" t="s" s="0">
         <v>680</v>
       </c>
-      <c r="F10" t="s" s="0">
+      <c r="H10" t="s" s="0">
         <v>681</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>682</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>682</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>683</v>
+      </c>
+      <c r="D11" t="s" s="0">
         <v>684</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>586</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>685</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>686</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>222</v>
       </c>
       <c r="F11" t="s" s="0">
+        <v>685</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>686</v>
+      </c>
+      <c r="H11" t="s" s="0">
         <v>687</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>688</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>689</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
+        <v>688</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>689</v>
+      </c>
+      <c r="C12" t="s" s="0">
         <v>690</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="D12" t="s" s="0">
         <v>691</v>
       </c>
-      <c r="C12" t="s" s="0">
+      <c r="E12" t="s" s="0">
         <v>692</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>693</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="G12" t="s" s="0">
         <v>694</v>
       </c>
-      <c r="F12" t="s" s="0">
+      <c r="H12" t="s" s="0">
         <v>695</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>696</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>697</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
+        <v>696</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>697</v>
+      </c>
+      <c r="C13" t="s" s="0">
         <v>698</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="D13" t="s" s="0">
         <v>699</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="E13" t="s" s="0">
         <v>700</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>701</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="G13" t="s" s="0">
         <v>702</v>
       </c>
-      <c r="F13" t="s" s="0">
+      <c r="H13" t="s" s="0">
         <v>703</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>704</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>705</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
+        <v>704</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>705</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>706</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="D14" t="s" s="0">
         <v>707</v>
       </c>
-      <c r="C14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>708</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>709</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="G14" t="s" s="0">
         <v>710</v>
       </c>
-      <c r="F14" t="s" s="0">
+      <c r="H14" t="s" s="0">
         <v>711</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>712</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
+        <v>712</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>713</v>
+      </c>
+      <c r="C15" t="s" s="0">
         <v>714</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="D15" t="s" s="0">
         <v>715</v>
       </c>
-      <c r="C15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>716</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>717</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="G15" t="s" s="0">
         <v>718</v>
       </c>
-      <c r="F15" t="s" s="0">
+      <c r="H15" t="s" s="0">
         <v>719</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>720</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>721</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>720</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>721</v>
+      </c>
+      <c r="C16" t="s" s="0">
         <v>722</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="D16" t="s" s="0">
         <v>723</v>
       </c>
-      <c r="C16" t="s" s="0">
+      <c r="E16" t="s" s="0">
         <v>724</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>725</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="G16" t="s" s="0">
         <v>726</v>
       </c>
-      <c r="F16" t="s" s="0">
+      <c r="H16" t="s" s="0">
         <v>727</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>728</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>729</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>728</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>729</v>
+      </c>
+      <c r="C17" t="s" s="0">
         <v>730</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="D17" t="s" s="0">
         <v>731</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>732</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>733</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>104</v>
       </c>
       <c r="F17" t="s" s="0">
+        <v>732</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>733</v>
+      </c>
+      <c r="H17" t="s" s="0">
         <v>734</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>735</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>736</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>735</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>736</v>
+      </c>
+      <c r="C18" t="s" s="0">
         <v>737</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="D18" t="s" s="0">
         <v>738</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>739</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>740</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>104</v>
       </c>
       <c r="F18" t="s" s="0">
+        <v>739</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>740</v>
+      </c>
+      <c r="H18" t="s" s="0">
         <v>741</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>742</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>743</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>742</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>743</v>
+      </c>
+      <c r="C19" t="s" s="0">
         <v>744</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="D19" t="s" s="0">
         <v>745</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>746</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>747</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>131</v>
       </c>
       <c r="F19" t="s" s="0">
+        <v>746</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>747</v>
+      </c>
+      <c r="H19" t="s" s="0">
         <v>748</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>749</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>750</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>749</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>750</v>
+      </c>
+      <c r="C20" t="s" s="0">
         <v>751</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="D20" t="s" s="0">
         <v>752</v>
       </c>
-      <c r="C20" t="s" s="0">
+      <c r="E20" t="s" s="0">
         <v>753</v>
       </c>
-      <c r="D20" t="s" s="0">
+      <c r="F20" t="s" s="0">
         <v>754</v>
       </c>
-      <c r="E20" t="s" s="0">
+      <c r="G20" t="s" s="0">
         <v>755</v>
       </c>
-      <c r="F20" t="s" s="0">
+      <c r="H20" t="s" s="0">
         <v>756</v>
-      </c>
-      <c r="G20" t="s" s="0">
-        <v>757</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>758</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1"/>
     <row r="22">
       <c r="A22" t="s" s="7">
+        <v>757</v>
+      </c>
+      <c r="B22" t="s" s="7">
+        <v>758</v>
+      </c>
+      <c r="C22" t="s" s="7">
         <v>759</v>
       </c>
-      <c r="B22" t="s" s="7">
+      <c r="D22" t="s" s="7">
         <v>760</v>
       </c>
-      <c r="C22" t="s" s="7">
+      <c r="E22" t="s" s="7">
         <v>761</v>
       </c>
-      <c r="D22" t="s" s="7">
+      <c r="F22" t="s" s="7">
         <v>762</v>
       </c>
-      <c r="E22" t="s" s="7">
+      <c r="G22" t="s" s="7">
         <v>763</v>
       </c>
-      <c r="F22" t="s" s="7">
+      <c r="H22" t="s" s="7">
         <v>764</v>
-      </c>
-      <c r="G22" t="s" s="7">
-        <v>765</v>
-      </c>
-      <c r="H22" t="s" s="7">
-        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -8587,7 +8581,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8599,7 +8593,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8612,34 +8606,34 @@
     <row r="3" ht="16" customHeight="1"/>
     <row r="4">
       <c r="A4" t="s" s="1">
+        <v>767</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>769</v>
       </c>
-      <c r="B4" t="s" s="1">
+      <c r="D4" t="s" s="1">
         <v>770</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="E4" t="s" s="1">
         <v>771</v>
       </c>
-      <c r="D4" t="s" s="1">
+      <c r="F4" t="s" s="1">
         <v>772</v>
-      </c>
-      <c r="E4" t="s" s="1">
-        <v>773</v>
-      </c>
-      <c r="F4" t="s" s="1">
-        <v>774</v>
       </c>
       <c r="G4" t="s" s="1">
         <v>324</v>
       </c>
       <c r="H4" t="s" s="1">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1"/>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B6" s="10">
         <v>980</v>
@@ -8654,18 +8648,18 @@
         <v>26400000</v>
       </c>
       <c r="F6" t="s" s="0">
+        <v>775</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>776</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>777</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>778</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>779</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B7" s="10">
         <v>160</v>
@@ -8680,18 +8674,18 @@
         <v>2750000</v>
       </c>
       <c r="F7" t="s" s="0">
+        <v>779</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>780</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>781</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>782</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>783</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B8" s="10">
         <v>1400</v>
@@ -8706,18 +8700,18 @@
         <v>37500000</v>
       </c>
       <c r="F8" t="s" s="0">
+        <v>783</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>784</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>785</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>786</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B9" s="10">
         <v>220</v>
@@ -8732,18 +8726,18 @@
         <v>4800000</v>
       </c>
       <c r="F9" t="s" s="0">
+        <v>787</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>788</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>789</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>790</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>791</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B10" s="10">
         <v>900</v>
@@ -8758,18 +8752,18 @@
         <v>23800000</v>
       </c>
       <c r="F10" t="s" s="0">
+        <v>791</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>792</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>793</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>794</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B11" s="10">
         <v>800</v>
@@ -8784,18 +8778,18 @@
         <v>27200000</v>
       </c>
       <c r="F11" t="s" s="0">
+        <v>795</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>796</v>
+      </c>
+      <c r="H11" t="s" s="0">
         <v>797</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>798</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B12" s="10">
         <v>180</v>
@@ -8810,18 +8804,18 @@
         <v>4300000</v>
       </c>
       <c r="F12" t="s" s="0">
+        <v>799</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>800</v>
+      </c>
+      <c r="H12" t="s" s="0">
         <v>801</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>802</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>803</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B13" s="10">
         <v>80</v>
@@ -8836,19 +8830,19 @@
         <v>2400000</v>
       </c>
       <c r="F13" t="s" s="0">
+        <v>803</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>804</v>
+      </c>
+      <c r="H13" t="s" s="0">
         <v>805</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>806</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>807</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1"/>
     <row r="15">
       <c r="A15" t="s" s="7">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B15" s="7">
         <v>4720</v>
@@ -8863,40 +8857,40 @@
         <v>129200000</v>
       </c>
       <c r="F15" t="s" s="7">
+        <v>807</v>
+      </c>
+      <c r="G15" t="s" s="7">
+        <v>808</v>
+      </c>
+      <c r="H15" t="s" s="7">
         <v>809</v>
-      </c>
-      <c r="G15" t="s" s="7">
-        <v>810</v>
-      </c>
-      <c r="H15" t="s" s="7">
-        <v>811</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1"/>
     <row r="17">
       <c r="A17" t="s" s="5">
+        <v>810</v>
+      </c>
+      <c r="B17" t="s" s="5">
+        <v>811</v>
+      </c>
+      <c r="C17" t="s" s="5">
         <v>812</v>
       </c>
-      <c r="B17" t="s" s="5">
+      <c r="D17" t="s" s="5">
         <v>813</v>
       </c>
-      <c r="C17" t="s" s="5">
+      <c r="E17" t="s" s="5">
         <v>814</v>
       </c>
-      <c r="D17" t="s" s="5">
+      <c r="F17" t="s" s="5">
         <v>815</v>
       </c>
-      <c r="E17" t="s" s="5">
+      <c r="G17" t="s" s="5">
         <v>816</v>
       </c>
-      <c r="F17" t="s" s="5">
+      <c r="H17" t="s" s="5">
         <v>817</v>
-      </c>
-      <c r="G17" t="s" s="5">
-        <v>818</v>
-      </c>
-      <c r="H17" t="s" s="5">
-        <v>819</v>
       </c>
     </row>
   </sheetData>
@@ -8918,7 +8912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8930,7 +8924,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8943,34 +8937,34 @@
     <row r="3" ht="16" customHeight="1"/>
     <row r="4">
       <c r="A4" t="s" s="1">
+        <v>820</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>821</v>
+      </c>
+      <c r="C4" t="s" s="1">
         <v>822</v>
       </c>
-      <c r="B4" t="s" s="1">
+      <c r="D4" t="s" s="1">
+        <v>770</v>
+      </c>
+      <c r="E4" t="s" s="1">
+        <v>771</v>
+      </c>
+      <c r="F4" t="s" s="1">
         <v>823</v>
       </c>
-      <c r="C4" t="s" s="1">
+      <c r="G4" t="s" s="1">
         <v>824</v>
       </c>
-      <c r="D4" t="s" s="1">
-        <v>772</v>
-      </c>
-      <c r="E4" t="s" s="1">
-        <v>773</v>
-      </c>
-      <c r="F4" t="s" s="1">
+      <c r="H4" t="s" s="1">
         <v>825</v>
-      </c>
-      <c r="G4" t="s" s="1">
-        <v>826</v>
-      </c>
-      <c r="H4" t="s" s="1">
-        <v>827</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1"/>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B6" s="10">
         <v>140</v>
@@ -8985,18 +8979,18 @@
         <v>1300000</v>
       </c>
       <c r="F6" t="s" s="0">
+        <v>827</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>828</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>829</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>830</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B7" s="10">
         <v>40</v>
@@ -9011,18 +9005,18 @@
         <v>0</v>
       </c>
       <c r="F7" t="s" s="0">
+        <v>831</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>832</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>833</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>834</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>835</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B8" s="10">
         <v>120</v>
@@ -9037,18 +9031,18 @@
         <v>2750000</v>
       </c>
       <c r="F8" t="s" s="0">
+        <v>835</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>836</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>837</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>838</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B9" s="10">
         <v>90</v>
@@ -9063,18 +9057,18 @@
         <v>1230000</v>
       </c>
       <c r="F9" t="s" s="0">
+        <v>839</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>840</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>841</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>842</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>843</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B10" s="10">
         <v>70</v>
@@ -9089,18 +9083,18 @@
         <v>1600000</v>
       </c>
       <c r="F10" t="s" s="0">
+        <v>843</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>844</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>845</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>846</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B11" s="10">
         <v>40</v>
@@ -9115,19 +9109,19 @@
         <v>700000</v>
       </c>
       <c r="F11" t="s" s="0">
+        <v>847</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>848</v>
+      </c>
+      <c r="H11" t="s" s="0">
         <v>849</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>850</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>851</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1"/>
     <row r="13">
       <c r="A13" t="s" s="7">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B13" s="7">
         <v>460</v>
@@ -9142,19 +9136,19 @@
         <v>7580000</v>
       </c>
       <c r="F13" t="s" s="7">
+        <v>851</v>
+      </c>
+      <c r="G13" t="s" s="7">
+        <v>852</v>
+      </c>
+      <c r="H13" t="s" s="7">
         <v>853</v>
-      </c>
-      <c r="G13" t="s" s="7">
-        <v>854</v>
-      </c>
-      <c r="H13" t="s" s="7">
-        <v>855</v>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1"/>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9166,7 +9160,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -9178,7 +9172,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="4">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -9190,7 +9184,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -9202,7 +9196,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="4">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -9214,7 +9208,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
